--- a/Luban/Config/Datas/Levels/L01/EnemyList.xlsx
+++ b/Luban/Config/Datas/Levels/L01/EnemyList.xlsx
@@ -1169,7 +1169,7 @@
       </c>
       <c r="F4" s="0" t="inlineStr">
         <is>
-          <t>L1 W1/25; N=31; EHP=170.500000; normal:17x31</t>
+          <t>L1 W1/25; N=31; EHP=341.000000; normal:17x31 | manual: hp x2, air x2 from W5</t>
         </is>
       </c>
     </row>
@@ -1190,7 +1190,7 @@
       </c>
       <c r="F5" s="0" t="inlineStr">
         <is>
-          <t>L1 W2/25; N=37; EHP=213.084850; normal:17x19,normal:18x18</t>
+          <t>L1 W2/25; N=37; EHP=426.169700; normal:17x19,normal:18x18 | manual: hp x2, air x2 from W5</t>
         </is>
       </c>
     </row>
@@ -1200,7 +1200,7 @@
       </c>
       <c r="C6" s="0" t="inlineStr">
         <is>
-          <t>3104136,3104673,3104107,3104136,3104673,3104107,3104136,3104673,3104107,3104136,3104673,3104107,3104136,3104673,3104107,3104136,3104673,3104136,3104673,3104136,3104673,3104136,3104673,3104136,3104673,3104136,3104673,3104136,3104673,3104136,3104144,3104144,3104144,3104144,3104144,3104144,3104144,3104144,3104144,3104144,3104144,3104144,3104144</t>
+          <t>3104136,3104673,3104136,3104673,3104136,3104673,3104136,3104673,3104136,3104673,3104136,3104673,3104136,3104673,3104136,3104673,3104136,3104673,3104136,3104673,3104136,3104673,3104136,3104673,3104136,3104144,3104144,3104144,3104144,3104144,3104144,3104144,3104144,3104144,3104144,3104144,3104144,3104144,3104136,3104136,3104136,3104136,3104136</t>
         </is>
       </c>
       <c r="D6" s="3" t="n">
@@ -1211,7 +1211,7 @@
       </c>
       <c r="F6" s="0" t="inlineStr">
         <is>
-          <t>L1 W3/25; N=43; EHP=273.961600; air:13x5,normal:17x13,normal:18x13,swarm:84x12</t>
+          <t>L1 W3/25; N=43; EHP=589.720393; air:13x5,normal:17x13,normal:18x13,swarm:84x12 | manual: hp x2, air x2 from W5</t>
         </is>
       </c>
     </row>
@@ -1221,7 +1221,7 @@
       </c>
       <c r="C7" s="0" t="inlineStr">
         <is>
-          <t>3106136,3106673,3106091,3106136,3106673,3106091,3106136,3106673,3106091,3106136,3106673,3106107,3106136,3106673,3106107,3106136,3106673,3106107,3106136,3106673,3106136,3106673,3106136,3106673,3106136,3106673,3106136,3106673,3106136,3106673,3106136,3106673,3106136,3106136,3106144,3106144,3106144,3106144,3106144,3106144,3106144,3106144,3106144,3106144,3106144,3106144,3106144,3106144,3106144</t>
+          <t>3106136,3106673,3106136,3106673,3106136,3106673,3106136,3106673,3106136,3106673,3106136,3106673,3106136,3106673,3106136,3106673,3106136,3106673,3106136,3106673,3106136,3106673,3106136,3106673,3106136,3106673,3106136,3106136,3106144,3106144,3106144,3106144,3106144,3106144,3106144,3106144,3106144,3106144,3106144,3106144,3106144,3106144,3106144,3106136,3106136,3106136,3106136,3106136,3106136</t>
         </is>
       </c>
       <c r="D7" s="3" t="n">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="F7" s="0" t="inlineStr">
         <is>
-          <t>L1 W4/25; N=49; EHP=359.486050; air:11x3,air:13x3,normal:17x15,normal:18x15,swarm:84x13</t>
+          <t>L1 W4/25; N=49; EHP=776.629644; air:11x3,air:13x3,normal:17x15,normal:18x15,swarm:84x13 | manual: hp x2, air x2 from W5</t>
         </is>
       </c>
     </row>
@@ -1242,7 +1242,7 @@
       </c>
       <c r="C8" s="0" t="inlineStr">
         <is>
-          <t>3108136,3108673,3108091,3108668,3108136,3108673,3108091,3108668,3108136,3108673,3108107,3108668,3108136,3108673,3108107,3108668,3108136,3108673,3108115,3108668,3108136,3108673,3108115,3108668,3108136,3108673,3108115,3108668,3108136,3108673,3108668,3108136,3108673,3108136,3108673,3108136,3108673,3108136,3108673,3108144,3108673,3108144,3108673,3108144,3108673,3108144,3108144,3108144,3108144,3108144,3108144,3108144,3108144,3108144,3108144</t>
+          <t>3108136,3108091,3108091,3108668,3108136,3108091,3108091,3108668,3108136,3108107,3108107,3108668,3108136,3108107,3108107,3108668,3108136,3108115,3108115,3108668,3108136,3108115,3108115,3108668,3108136,3108115,3108115,3108668,3108136,3108673,3108668,3108136,3108673,3108136,3108673,3108136,3108673,3108136,3108673,3108144,3108673,3108144,3108673,3108144,3108673,3108144,3108144,3108144,3108144,3108144,3108144,3108144,3108144,3108144,3108144</t>
         </is>
       </c>
       <c r="D8" s="3" t="n">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="F8" s="0" t="inlineStr">
         <is>
-          <t>L1 W5/25; N=55; EHP=694.980440; air:11x2,air:13x2,air:14x3,normal:17x12,normal:18x13,medium:83x8,swarm:84x15</t>
+          <t>L1 W5/25; N=55; EHP=1352.175536; air:11x2,air:13x2,air:14x3,normal:17x12,normal:18x13,medium:83x8,swarm:84x15 | manual: hp x2, air x2 from W5</t>
         </is>
       </c>
     </row>
@@ -1263,7 +1263,7 @@
       </c>
       <c r="C9" s="0" t="inlineStr">
         <is>
-          <t>3110136,3110673,3110091,3110668,3110136,3110673,3110091,3110668,3110136,3110673,3110107,3110668,3110136,3110673,3110107,3110668,3110136,3110673,3110107,3110668,3110136,3110673,3110115,3110668,3110136,3110673,3110115,3110668,3110136,3110673,3110668,3110136,3110673,3110668,3110136,3110673,3110136,3110673,3110136,3110673,3110136,3110673,3110136,3110673,3110144,3110673,3110144,3110673,3110144,3110673,3110144,3110144,3110144,3110144,3110144,3110144,3110144,3110144,3110144,3110144,3110144</t>
+          <t>3110136,3110091,3110091,3110668,3110136,3110091,3110091,3110668,3110136,3110107,3110107,3110668,3110136,3110107,3110107,3110668,3110136,3110107,3110107,3110668,3110136,3110115,3110115,3110668,3110136,3110115,3110115,3110668,3110136,3110673,3110668,3110136,3110673,3110668,3110136,3110673,3110136,3110673,3110136,3110673,3110136,3110673,3110136,3110673,3110144,3110673,3110144,3110673,3110144,3110673,3110144,3110144,3110144,3110144,3110144,3110144,3110144,3110144,3110144,3110144,3110144</t>
         </is>
       </c>
       <c r="D9" s="3" t="n">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="F9" s="0" t="inlineStr">
         <is>
-          <t>L1 W6/25; N=61; EHP=709.000000; air:11x2,air:13x3,air:14x2,normal:17x14,normal:18x14,medium:83x9,swarm:84x17</t>
+          <t>L1 W6/25; N=61; EHP=1383.474783; air:11x2,air:13x3,air:14x2,normal:17x14,normal:18x14,medium:83x9,swarm:84x17 | manual: hp x2, air x2 from W5</t>
         </is>
       </c>
     </row>
@@ -1284,7 +1284,7 @@
       </c>
       <c r="C10" s="0" t="inlineStr">
         <is>
-          <t>3112136,3112673,3112091,3112668,3112136,3112673,3112091,3112668,3112136,3112673,3112091,3112668,3112136,3112673,3112107,3112668,3112136,3112673,3112107,3112668,3112136,3112673,3112115,3112668,3112136,3112673,3112115,3112668,3112136,3112673,3112115,3112668,3112136,3112673,3112668,3112136,3112673,3112668,3112136,3112673,3112136,3112673,3112136,3112673,3112136,3112673,3112136,3112673,3112144,3112673,3112144,3112673,3112144,3112673,3112144,3112144,3112144,3112144,3112144,3112144,3112144,3112144,3112144,3112144,3112144,3112144,3112144</t>
+          <t>3112136,3112091,3112091,3112668,3112136,3112091,3112091,3112668,3112136,3112091,3112091,3112668,3112136,3112107,3112107,3112668,3112136,3112107,3112107,3112668,3112136,3112115,3112115,3112668,3112136,3112115,3112115,3112668,3112136,3112115,3112115,3112668,3112136,3112673,3112668,3112136,3112673,3112668,3112136,3112673,3112136,3112673,3112136,3112673,3112136,3112673,3112136,3112673,3112144,3112673,3112144,3112673,3112144,3112673,3112144,3112144,3112144,3112144,3112144,3112144,3112144,3112144,3112144,3112144,3112144,3112144,3112144</t>
         </is>
       </c>
       <c r="D10" s="3" t="n">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="F10" s="0" t="inlineStr">
         <is>
-          <t>L1 W7/25; N=67; EHP=827.503600; air:11x3,air:13x2,air:14x3,normal:17x15,normal:18x16,medium:83x10,swarm:84x18</t>
+          <t>L1 W7/25; N=67; EHP=1613.174475; air:11x3,air:13x2,air:14x3,normal:17x15,normal:18x16,medium:83x10,swarm:84x18 | manual: hp x2, air x2 from W5</t>
         </is>
       </c>
     </row>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="C11" s="0" t="inlineStr">
         <is>
-          <t>3114136,3114673,3114091,3114668,3114136,3114673,3114091,3114668,3114136,3114673,3114099,3114668,3114136,3114673,3114099,3114668,3114136,3114673,3114107,3114668,3114136,3114673,3114107,3114668,3114136,3114673,3114107,3114668,3114136,3114673,3114115,3114668,3114136,3114673,3114115,3114668,3114136,3114673,3114668,3114136,3114673,3114136,3114673,3114136,3114673,3114136,3114673,3114136,3114673,3114136,3114673,3114136,3114673,3114144,3114673,3114144,3114673,3114144,3114673,3114144,3114144,3114144,3114144,3114144,3114144,3114144,3114144,3114144,3114144,3114144,3114144,3114144,3114144</t>
+          <t>3114136,3114091,3114091,3114668,3114136,3114091,3114091,3114668,3114136,3114099,3114099,3114668,3114136,3114099,3114099,3114668,3114136,3114107,3114107,3114668,3114136,3114107,3114107,3114668,3114136,3114107,3114107,3114668,3114136,3114115,3114115,3114668,3114136,3114115,3114115,3114668,3114136,3114673,3114668,3114136,3114673,3114136,3114673,3114136,3114673,3114136,3114673,3114136,3114673,3114136,3114673,3114136,3114673,3114144,3114673,3114144,3114673,3114144,3114673,3114144,3114144,3114144,3114144,3114144,3114144,3114144,3114144,3114144,3114144,3114144,3114144,3114144,3114144</t>
         </is>
       </c>
       <c r="D11" s="3" t="n">
@@ -1316,7 +1316,7 @@
       </c>
       <c r="F11" s="0" t="inlineStr">
         <is>
-          <t>L1 W8/25; N=73; EHP=1075.176850; air:11x2,air:12x2,air:13x3,air:14x2,normal:17x17,normal:18x17,medium:83x10,swarm:84x20</t>
+          <t>L1 W8/25; N=73; EHP=2093.474396; air:11x2,air:12x2,air:13x3,air:14x2,normal:17x17,normal:18x17,medium:83x10,swarm:84x20 | manual: hp x2, air x2 from W5</t>
         </is>
       </c>
     </row>
@@ -1326,7 +1326,7 @@
       </c>
       <c r="C12" s="0" t="inlineStr">
         <is>
-          <t>3116136,3116673,3116091,3116668,3116136,3116673,3116091,3116668,3116136,3116673,3116091,3116668,3116136,3116673,3116099,3116668,3116136,3116673,3116099,3116668,3116136,3116673,3116107,3116668,3116136,3116673,3116107,3116668,3116136,3116673,3116115,3116668,3116136,3116673,3116115,3116668,3116136,3116673,3116668,3116136,3116673,3116668,3116136,3116673,3116136,3116673,3116136,3116673,3116136,3116673,3116136,3116673,3116136,3116673,3116136,3116673,3116144,3116673,3116144,3116673,3116144,3116673,3116144,3116673,3116144,3116144,3116144,3116144,3116144,3116144,3116144,3116144,3116144,3116144,3116144,3116144,3116144,3116144,3116144</t>
+          <t>3116136,3116091,3116091,3116668,3116136,3116091,3116091,3116668,3116136,3116091,3116091,3116668,3116136,3116099,3116099,3116668,3116136,3116099,3116099,3116668,3116136,3116107,3116107,3116668,3116136,3116107,3116107,3116668,3116136,3116115,3116115,3116668,3116136,3116115,3116115,3116668,3116136,3116673,3116668,3116136,3116673,3116668,3116136,3116673,3116136,3116673,3116136,3116673,3116136,3116673,3116136,3116673,3116136,3116673,3116136,3116673,3116144,3116673,3116144,3116673,3116144,3116673,3116144,3116673,3116144,3116144,3116144,3116144,3116144,3116144,3116144,3116144,3116144,3116144,3116144,3116144,3116144,3116144,3116144</t>
         </is>
       </c>
       <c r="D12" s="3" t="n">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="F12" s="0" t="inlineStr">
         <is>
-          <t>L1 W9/25; N=79; EHP=1379.276800; air:11x3,air:12x2,air:13x2,air:14x2,normal:17x18,normal:18x19,medium:83x11,swarm:84x22</t>
+          <t>L1 W9/25; N=79; EHP=2691.498955; air:11x3,air:12x2,air:13x2,air:14x2,normal:17x18,normal:18x19,medium:83x11,swarm:84x22 | manual: hp x2, air x2 from W5</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="C13" s="0" t="inlineStr">
         <is>
-          <t>3118136,3118673,3118091,3118668,3118136,3118673,3118091,3118668,3118136,3118673,3118099,3118668,3118136,3118673,3118099,3118668,3118136,3118673,3118099,3118668,3118136,3118673,3118107,3118668,3118136,3118673,3118107,3118668,3118136,3118673,3118115,3118668,3118136,3118673,3118115,3118668,3118136,3118673,3118115,3118668,3118136,3118673,3118668,3118136,3118673,3118668,3118136,3118673,3118136,3118673,3118136,3118673,3118136,3118673,3118136,3118673,3118136,3118673,3118136,3118673,3118136,3118673,3118144,3118673,3118144,3118673,3118144,3118673,3118144,3118144,3118144,3118144,3118144,3118144,3118144,3118144,3118144,3118144,3118144,3118144,3118144,3118144,3118144,3118144,3118144</t>
+          <t>3118136,3118091,3118091,3118668,3118136,3118091,3118091,3118668,3118136,3118099,3118099,3118668,3118136,3118099,3118099,3118668,3118136,3118099,3118099,3118668,3118136,3118107,3118107,3118668,3118136,3118107,3118107,3118668,3118136,3118115,3118115,3118668,3118136,3118115,3118115,3118668,3118136,3118115,3118115,3118668,3118136,3118673,3118668,3118136,3118673,3118668,3118136,3118673,3118136,3118673,3118136,3118673,3118136,3118673,3118136,3118673,3118136,3118673,3118136,3118673,3118136,3118673,3118144,3118673,3118144,3118673,3118144,3118673,3118144,3118144,3118144,3118144,3118144,3118144,3118144,3118144,3118144,3118144,3118144,3118144,3118144,3118144,3118144,3118144,3118144</t>
         </is>
       </c>
       <c r="D13" s="3" t="n">
@@ -1358,7 +1358,7 @@
       </c>
       <c r="F13" s="0" t="inlineStr">
         <is>
-          <t>L1 W10/25; N=85; EHP=2549.392505; air:11x2,air:12x3,air:13x2,air:14x3,normal:17x20,normal:18x20,medium:83x12,swarm:84x23</t>
+          <t>L1 W10/25; N=85; EHP=4971.075930; air:11x2,air:12x3,air:13x2,air:14x3,normal:17x20,normal:18x20,medium:83x12,swarm:84x23 | manual: hp x2, air x2 from W5</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       </c>
       <c r="C14" s="0" t="inlineStr">
         <is>
-          <t>3120136,3120673,3120091,3120668,3120709,3120136,3120673,3120091,3120668,3120709,3120136,3120673,3120091,3120668,3120709,3120136,3120673,3120099,3120668,3120709,3120136,3120673,3120099,3120668,3120709,3120136,3120673,3120099,3120668,3120709,3120136,3120673,3120107,3120668,3120709,3120136,3120673,3120107,3120668,3120709,3120136,3120673,3120107,3120668,3120709,3120136,3120673,3120115,3120668,3120136,3120673,3120115,3120668,3120136,3120673,3120668,3120136,3120673,3120668,3120136,3120673,3120136,3120673,3120136,3120673,3120144,3120673,3120144,3120673,3120144,3120673,3120144,3120673,3120144,3120673,3120144,3120673,3120144,3120673,3120144,3120673,3120144,3120673,3120144,3120144,3120144,3120144,3120144,3120144,3120144,3120144</t>
+          <t>3120136,3120091,3120091,3120668,3120709,3120136,3120091,3120091,3120668,3120709,3120136,3120091,3120091,3120668,3120709,3120136,3120099,3120099,3120668,3120709,3120136,3120099,3120099,3120668,3120709,3120136,3120099,3120099,3120668,3120709,3120136,3120107,3120107,3120668,3120709,3120136,3120107,3120107,3120668,3120709,3120136,3120107,3120107,3120668,3120709,3120136,3120115,3120115,3120668,3120136,3120115,3120115,3120668,3120136,3120673,3120668,3120136,3120673,3120668,3120136,3120673,3120136,3120673,3120136,3120673,3120144,3120673,3120144,3120673,3120144,3120673,3120144,3120673,3120144,3120673,3120144,3120673,3120144,3120673,3120144,3120673,3120144,3120673,3120144,3120144,3120144,3120144,3120144,3120144,3120144,3120144</t>
         </is>
       </c>
       <c r="D14" s="3" t="n">
@@ -1379,7 +1379,7 @@
       </c>
       <c r="F14" s="0" t="inlineStr">
         <is>
-          <t>L1 W11/25; N=91; EHP=2601.000000; air:11x3,air:12x3,air:13x3,air:14x2,normal:17x16,normal:18x17,medium:83x13,swarm:84x25,heavy:88x9</t>
+          <t>L1 W11/25; N=91; EHP=5082.911550; air:11x3,air:12x3,air:13x3,air:14x2,normal:17x16,normal:18x17,medium:83x13,swarm:84x25,heavy:88x9 | manual: hp x2, air x2 from W5</t>
         </is>
       </c>
     </row>
@@ -1389,7 +1389,7 @@
       </c>
       <c r="C15" s="0" t="inlineStr">
         <is>
-          <t>3122136,3122673,3122091,3122668,3122709,3122136,3122673,3122091,3122668,3122709,3122136,3122673,3122091,3122668,3122709,3122136,3122673,3122099,3122668,3122709,3122136,3122673,3122099,3122668,3122709,3122136,3122673,3122099,3122668,3122709,3122136,3122673,3122107,3122668,3122709,3122136,3122673,3122107,3122668,3122709,3122136,3122673,3122107,3122668,3122709,3122136,3122673,3122115,3122668,3122136,3122673,3122115,3122668,3122136,3122673,3122115,3122668,3122136,3122673,3122668,3122136,3122673,3122668,3122136,3122673,3122136,3122673,3122136,3122673,3122136,3122673,3122144,3122673,3122144,3122673,3122144,3122673,3122144,3122673,3122144,3122673,3122144,3122673,3122144,3122673,3122144,3122673,3122144,3122673,3122144,3122144,3122144,3122144,3122144,3122144,3122144,3122144</t>
+          <t>3122136,3122091,3122091,3122668,3122709,3122136,3122091,3122091,3122668,3122709,3122136,3122091,3122091,3122668,3122709,3122136,3122099,3122099,3122668,3122709,3122136,3122099,3122099,3122668,3122709,3122136,3122099,3122099,3122668,3122709,3122136,3122107,3122107,3122668,3122709,3122136,3122107,3122107,3122668,3122709,3122136,3122107,3122107,3122668,3122709,3122136,3122115,3122115,3122668,3122136,3122115,3122115,3122668,3122136,3122115,3122115,3122668,3122136,3122673,3122668,3122136,3122673,3122668,3122136,3122673,3122136,3122673,3122136,3122673,3122136,3122673,3122144,3122673,3122144,3122673,3122144,3122673,3122144,3122673,3122144,3122673,3122144,3122673,3122144,3122673,3122144,3122673,3122144,3122673,3122144,3122144,3122144,3122144,3122144,3122144,3122144,3122144</t>
         </is>
       </c>
       <c r="D15" s="3" t="n">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="F15" s="0" t="inlineStr">
         <is>
-          <t>L1 W12/25; N=97; EHP=2693.694850; air:11x3,air:12x3,air:13x3,air:14x3,normal:17x18,normal:18x17,medium:83x14,swarm:84x27,heavy:88x9</t>
+          <t>L1 W12/25; N=97; EHP=5260.065867; air:11x3,air:12x3,air:13x3,air:14x3,normal:17x18,normal:18x17,medium:83x14,swarm:84x27,heavy:88x9 | manual: hp x2, air x2 from W5</t>
         </is>
       </c>
     </row>
@@ -1410,7 +1410,7 @@
       </c>
       <c r="C16" s="0" t="inlineStr">
         <is>
-          <t>3124136,3124673,3124019,3124668,3124709,3124136,3124673,3124019,3124668,3124709,3124136,3124673,3124019,3124668,3124709,3124136,3124673,3124091,3124668,3124709,3124136,3124673,3124091,3124668,3124709,3124136,3124673,3124099,3124668,3124709,3124136,3124673,3124099,3124668,3124709,3124136,3124673,3124099,3124668,3124709,3124136,3124673,3124107,3124668,3124709,3124136,3124673,3124107,3124668,3124709,3124136,3124673,3124115,3124668,3124136,3124673,3124115,3124668,3124136,3124673,3124668,3124136,3124673,3124668,3124136,3124673,3124668,3124136,3124673,3124136,3124673,3124136,3124673,3124136,3124673,3124144,3124673,3124144,3124673,3124144,3124673,3124144,3124673,3124144,3124673,3124144,3124673,3124144,3124673,3124144,3124673,3124144,3124673,3124144,3124144,3124144,3124144,3124144,3124144,3124144,3124144,3124144,3124144</t>
+          <t>3124136,3124019,3124019,3124668,3124709,3124136,3124019,3124019,3124668,3124709,3124136,3124019,3124019,3124668,3124709,3124136,3124091,3124091,3124668,3124709,3124136,3124091,3124091,3124668,3124709,3124136,3124099,3124099,3124668,3124709,3124136,3124099,3124099,3124668,3124709,3124136,3124099,3124099,3124668,3124709,3124136,3124107,3124107,3124668,3124709,3124136,3124107,3124107,3124668,3124709,3124136,3124115,3124115,3124668,3124136,3124115,3124115,3124668,3124136,3124673,3124668,3124136,3124673,3124668,3124136,3124673,3124668,3124136,3124673,3124136,3124673,3124136,3124673,3124136,3124673,3124144,3124673,3124144,3124673,3124144,3124673,3124144,3124673,3124144,3124673,3124144,3124673,3124144,3124673,3124144,3124673,3124144,3124673,3124144,3124144,3124144,3124144,3124144,3124144,3124144,3124144,3124144,3124144</t>
         </is>
       </c>
       <c r="D16" s="3" t="n">
@@ -1421,7 +1421,7 @@
       </c>
       <c r="F16" s="0" t="inlineStr">
         <is>
-          <t>L1 W13/25; N=103; EHP=3287.059600; air:2x3,air:11x2,air:12x3,air:13x2,air:14x2,normal:17x19,normal:18x19,medium:83x15,swarm:84x28,heavy:88x10</t>
+          <t>L1 W13/25; N=103; EHP=6429.500629; air:2x3,air:11x2,air:12x3,air:13x2,air:14x2,normal:17x19,normal:18x19,medium:83x15,swarm:84x28,heavy:88x10 | manual: hp x2, air x2 from W5</t>
         </is>
       </c>
     </row>
@@ -1431,7 +1431,7 @@
       </c>
       <c r="C17" s="0" t="inlineStr">
         <is>
-          <t>3126136,3126673,3126019,3126668,3126709,3126136,3126673,3126019,3126668,3126709,3126136,3126673,3126019,3126668,3126709,3126136,3126673,3126091,3126668,3126709,3126136,3126673,3126091,3126668,3126709,3126136,3126673,3126091,3126668,3126709,3126136,3126673,3126099,3126668,3126709,3126136,3126673,3126099,3126668,3126709,3126136,3126673,3126107,3126668,3126709,3126136,3126673,3126107,3126668,3126709,3126136,3126673,3126107,3126668,3126136,3126673,3126115,3126668,3126136,3126673,3126115,3126668,3126136,3126673,3126668,3126136,3126673,3126668,3126136,3126673,3126668,3126136,3126673,3126136,3126673,3126136,3126673,3126136,3126673,3126144,3126673,3126144,3126673,3126144,3126673,3126144,3126673,3126144,3126673,3126144,3126673,3126144,3126673,3126144,3126673,3126144,3126673,3126144,3126673,3126144,3126144,3126144,3126144,3126144,3126144,3126144,3126144,3126144,3126144</t>
+          <t>3126136,3126019,3126019,3126668,3126709,3126136,3126019,3126019,3126668,3126709,3126136,3126019,3126019,3126668,3126709,3126136,3126091,3126091,3126668,3126709,3126136,3126091,3126091,3126668,3126709,3126136,3126091,3126091,3126668,3126709,3126136,3126099,3126099,3126668,3126709,3126136,3126099,3126099,3126668,3126709,3126136,3126107,3126107,3126668,3126709,3126136,3126107,3126107,3126668,3126709,3126136,3126107,3126107,3126668,3126136,3126115,3126115,3126668,3126136,3126115,3126115,3126668,3126136,3126673,3126668,3126136,3126673,3126668,3126136,3126673,3126668,3126136,3126673,3126136,3126673,3126136,3126673,3126136,3126673,3126144,3126673,3126144,3126673,3126144,3126673,3126144,3126673,3126144,3126673,3126144,3126673,3126144,3126673,3126144,3126673,3126144,3126673,3126144,3126673,3126144,3126144,3126144,3126144,3126144,3126144,3126144,3126144,3126144,3126144</t>
         </is>
       </c>
       <c r="D17" s="3" t="n">
@@ -1442,7 +1442,7 @@
       </c>
       <c r="F17" s="0" t="inlineStr">
         <is>
-          <t>L1 W14/25; N=109; EHP=3968.630050; air:2x3,air:11x3,air:12x2,air:13x3,air:14x2,normal:17x20,normal:18x20,medium:83x16,swarm:84x30,heavy:88x10</t>
+          <t>L1 W14/25; N=109; EHP=7757.104044; air:2x3,air:11x3,air:12x2,air:13x3,air:14x2,normal:17x20,normal:18x20,medium:83x16,swarm:84x30,heavy:88x10 | manual: hp x2, air x2 from W5</t>
         </is>
       </c>
     </row>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="C18" s="0" t="inlineStr">
         <is>
-          <t>3128136,3128673,3128019,3128668,3128709,3128136,3128673,3128019,3128668,3128709,3128136,3128673,3128091,3128668,3128709,3128136,3128673,3128091,3128668,3128709,3128136,3128673,3128091,3128668,3128709,3128136,3128673,3128099,3128668,3128709,3128136,3128673,3128099,3128668,3128709,3128136,3128673,3128099,3128668,3128709,3128136,3128673,3128107,3128668,3128709,3128136,3128673,3128107,3128988,3128709,3128136,3128673,3128107,3128988,3128709,3128136,3128673,3128115,3128988,3128136,3128673,3128115,3128988,3128136,3128673,3128115,3128988,3128136,3128673,3128988,3128136,3128673,3128988,3128136,3128673,3128988,3128136,3128673,3128136,3128673,3128136,3128673,3128144,3128673,3128144,3128673,3128144,3128673,3128144,3128673,3128144,3128673,3128144,3128673,3128144,3128673,3128144,3128673,3128144,3128673,3128144,3128673,3128144,3128673,3128144,3128673,3128144,3128144,3128144,3128144,3128144,3128144,3128144,3128144,3128144</t>
+          <t>3128136,3128019,3128019,3128668,3128709,3128136,3128019,3128019,3128668,3128709,3128136,3128091,3128091,3128668,3128709,3128136,3128091,3128091,3128668,3128709,3128136,3128091,3128091,3128668,3128709,3128136,3128099,3128099,3128668,3128709,3128136,3128099,3128099,3128668,3128709,3128136,3128099,3128099,3128668,3128709,3128136,3128107,3128107,3128668,3128709,3128136,3128107,3128107,3128988,3128709,3128136,3128107,3128107,3128988,3128709,3128136,3128115,3128115,3128988,3128136,3128115,3128115,3128988,3128136,3128115,3128115,3128988,3128136,3128673,3128988,3128136,3128673,3128988,3128136,3128673,3128988,3128136,3128673,3128136,3128673,3128136,3128673,3128144,3128673,3128144,3128673,3128144,3128673,3128144,3128673,3128144,3128673,3128144,3128673,3128144,3128673,3128144,3128673,3128144,3128673,3128144,3128673,3128144,3128673,3128144,3128673,3128144,3128144,3128144,3128144,3128144,3128144,3128144,3128144,3128144</t>
         </is>
       </c>
       <c r="D18" s="3" t="n">
@@ -1463,7 +1463,7 @@
       </c>
       <c r="F18" s="0" t="inlineStr">
         <is>
-          <t>L1 W15/25; N=115; EHP=6927.352520; air:2x2,air:11x3,air:12x3,air:13x3,air:14x3,normal:17x20,normal:18x21,medium:83x9,swarm:84x32,heavy:88x11,medium:123x8</t>
+          <t>L1 W15/25; N=115; EHP=13534.629346; air:2x2,air:11x3,air:12x3,air:13x3,air:14x3,normal:17x20,normal:18x21,medium:83x9,swarm:84x32,heavy:88x11,medium:123x8 | manual: hp x2, air x2 from W5</t>
         </is>
       </c>
     </row>
@@ -1473,7 +1473,7 @@
       </c>
       <c r="C19" s="0" t="inlineStr">
         <is>
-          <t>10016742,10016745,10048470,10016744,10016746,10016742,10016745,10048470,10016744,10016746,10016742,10016745,10048470,10016744,10016746,10016742,10016745,10016740,10016744,10016746,10016742,10016745,10016740,10016744,10016746,10016742,10016745,10016740,10016744,10016746,10016742,10016745,10016740,10016744,10016746,10016742,10016745,10048471,10016744,10016746,10016742,10016745,10048471,10016744,10016746,10016742,10016745,10048471,10016744,10016746,10016742,10016745,10048471,10016744,10016746,10016742,10016745,10016741,10016747,10016746,10016742,10016745,10016741,10016747,10016746,10016742,10016745,10016741,10016747,10016746,10016742,10016745,10046035,10016747,10016746,10016742,10016745,10046035,10016747,10016742,10016745,10046035,10016747,10016742,10016745,10046035,10016747,10016742,10016745,10016747,10016742,10016745,10016747,10016742,10016745,10016747,10016742,10016745,10016747,10016742,10016745,10016742,10016745,10016742,10016745,10016742,10016745,10016742,10016745,10016743,10016745,10016743,10016745,10016743,10016745,10016743,10016745,10016743,10016745,10016743,10016745,10016743,10016745,10016743,10016745,10016743,10016745,10016743,10016745,10016743,10016745,10016743,10016745,10016743,10016745,10016743,10016745,10016743,10016745,10016743,10016743,10016743,10016743,10016743,10016743,10016743,10016743,10016743,10016743,10016743,10016743</t>
+          <t>10016742,10048470,10048470,10016744,10016746,10016742,10048470,10048470,10016744,10016746,10016742,10048470,10048470,10016744,10016746,10016742,10016740,10016740,10016744,10016746,10016742,10016740,10016740,10016744,10016746,10016742,10016740,10016740,10016744,10016746,10016742,10016740,10016740,10016744,10016746,10016742,10048471,10048471,10016744,10016746,10016742,10048471,10048471,10016744,10016746,10016742,10048471,10048471,10016744,10016746,10016742,10048471,10048471,10016744,10016746,10016742,10016741,10016741,10016747,10016746,10016742,10016741,10016741,10016747,10016746,10016742,10016741,10016741,10016747,10016746,10016742,10046035,10046035,10016747,10016746,10016742,10046035,10046035,10016747,10016742,10046035,10046035,10016747,10016742,10046035,10046035,10016747,10016742,10016745,10016747,10016742,10016745,10016747,10016742,10016745,10016747,10016742,10016745,10016747,10016742,10016745,10016742,10016745,10016742,10016745,10016742,10016745,10016742,10016745,10016743,10016745,10016743,10016745,10016743,10016745,10016743,10016745,10016743,10016745,10016743,10016745,10016743,10016745,10016743,10016745,10016743,10016745,10016743,10016745,10016743,10016745,10016743,10016745,10016743,10016745,10016743,10016745,10016743,10016745,10016743,10016743,10016743,10016743,10016743,10016743,10016743,10016743,10016743,10016743,10016743,10016743</t>
         </is>
       </c>
       <c r="D19" s="3" t="n">
@@ -1484,7 +1484,7 @@
       </c>
       <c r="F19" s="0" t="inlineStr">
         <is>
-          <t>L1 W21/25; N=151; EHP=15289.000000; air:2x3,air:11x4,air:12x4,air:13x3,air:14x4,normal:17x27,normal:18x27,medium:83x11,swarm:84x42,heavy:88x15,medium:123x11</t>
+          <t>L1 W21/25; N=151; EHP=29889.133917; air:2x3,air:11x4,air:12x4,air:13x3,air:14x4,normal:17x27,normal:18x27,medium:83x11,swarm:84x42,heavy:88x15,medium:123x11 | manual: hp x2, air x2 from W5</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="C20" s="0" t="inlineStr">
         <is>
-          <t>10016751,10016754,10048472,10016753,10016755,10016751,10016754,10048472,10016753,10016755,10016751,10016754,10048472,10016753,10016755,10016751,10016754,10048472,10016753,10016755,10016751,10016754,10016748,10016753,10016755,10016751,10016754,10016748,10016753,10016755,10016751,10016754,10016748,10016753,10016755,10016751,10016754,10048473,10016753,10016755,10016751,10016754,10048473,10016753,10016755,10016751,10016754,10048473,10016753,10016755,10016751,10016754,10048473,10016753,10016755,10016751,10016754,10016749,10016756,10016755,10016751,10016754,10016749,10016756,10016755,10016751,10016754,10016749,10016756,10016755,10016751,10016754,10016749,10016756,10016755,10016751,10016754,10016750,10016756,10016751,10016754,10016750,10016756,10016751,10016754,10016750,10016756,10016751,10016754,10016750,10016756,10016751,10016754,10016756,10016751,10016754,10016756,10016751,10016754,10016756,10016751,10016754,10016756,10016751,10016754,10016751,10016754,10016751,10016754,10016751,10016754,10016751,10016754,10016751,10016754,10016752,10016754,10016752,10016754,10016752,10016754,10016752,10016754,10016752,10016754,10016752,10016754,10016752,10016754,10016752,10016754,10016752,10016754,10016752,10016754,10016752,10016754,10016752,10016754,10016752,10016754,10016752,10016754,10016752,10016752,10016752,10016752,10016752,10016752,10016752,10016752,10016752,10016752,10016752,10016752,10016752,10016752</t>
+          <t>10016751,10048472,10048472,10016753,10016755,10016751,10048472,10048472,10016753,10016755,10016751,10048472,10048472,10016753,10016755,10016751,10048472,10048472,10016753,10016755,10016751,10016748,10016748,10016753,10016755,10016751,10016748,10016748,10016753,10016755,10016751,10016748,10016748,10016753,10016755,10016751,10048473,10048473,10016753,10016755,10016751,10048473,10048473,10016753,10016755,10016751,10048473,10048473,10016753,10016755,10016751,10048473,10048473,10016753,10016755,10016751,10016749,10016749,10016756,10016755,10016751,10016749,10016749,10016756,10016755,10016751,10016749,10016749,10016756,10016755,10016751,10016749,10016749,10016756,10016755,10016751,10016750,10016750,10016756,10016751,10016750,10016750,10016756,10016751,10016750,10016750,10016756,10016751,10016750,10016750,10016756,10016751,10016754,10016756,10016751,10016754,10016756,10016751,10016754,10016756,10016751,10016754,10016756,10016751,10016754,10016751,10016754,10016751,10016754,10016751,10016754,10016751,10016754,10016751,10016754,10016752,10016754,10016752,10016754,10016752,10016754,10016752,10016754,10016752,10016754,10016752,10016754,10016752,10016754,10016752,10016754,10016752,10016754,10016752,10016754,10016752,10016754,10016752,10016754,10016752,10016754,10016752,10016754,10016752,10016752,10016752,10016752,10016752,10016752,10016752,10016752,10016752,10016752,10016752,10016752,10016752,10016752</t>
         </is>
       </c>
       <c r="D20" s="3" t="n">
@@ -1505,7 +1505,7 @@
       </c>
       <c r="F20" s="0" t="inlineStr">
         <is>
-          <t>L1 W22/25; N=157; EHP=15595.000000; air:2x4,air:11x3,air:12x4,air:13x4,air:14x4,normal:17x29,normal:18x28,medium:83x11,swarm:84x43,heavy:88x15,medium:123x12</t>
+          <t>L1 W22/25; N=157; EHP=30474.287440; air:2x4,air:11x3,air:12x4,air:13x4,air:14x4,normal:17x29,normal:18x28,medium:83x11,swarm:84x43,heavy:88x15,medium:123x12 | manual: hp x2, air x2 from W5</t>
         </is>
       </c>
     </row>
@@ -1515,7 +1515,7 @@
       </c>
       <c r="C21" s="0" t="inlineStr">
         <is>
-          <t>10016760,10016763,10048474,10016762,10016764,10016760,10016763,10048474,10016762,10016764,10016760,10016763,10048474,10016762,10016764,10016760,10016763,10048474,10016762,10016764,10016760,10016763,10016757,10016762,10016764,10016760,10016763,10016757,10016762,10016764,10016760,10016763,10016757,10016762,10016764,10016760,10016763,10016757,10016762,10016764,10016760,10016763,10048475,10016762,10016764,10016760,10016763,10048475,10016762,10016764,10016760,10016763,10048475,10016762,10016764,10016760,10016763,10048475,10016762,10016764,10016760,10016763,10016758,10016765,10016764,10016760,10016763,10016758,10016765,10016764,10016760,10016763,10016758,10016765,10016764,10016760,10016763,10016758,10016765,10016764,10016760,10016763,10016759,10016765,10016760,10016763,10016759,10016765,10016760,10016763,10016759,10016765,10016760,10016763,10016759,10016765,10016760,10016763,10016765,10016760,10016763,10016765,10016760,10016763,10016765,10016760,10016763,10016765,10016760,10016763,10016760,10016763,10016760,10016763,10016760,10016763,10016760,10016763,10016761,10016763,10016761,10016763,10016761,10016763,10016761,10016763,10016761,10016763,10016761,10016763,10016761,10016763,10016761,10016763,10016761,10016763,10016761,10016763,10016761,10016763,10016761,10016763,10016761,10016763,10016761,10016763,10016761,10016763,10016761,10016763,10016761,10016761,10016761,10016761,10016761,10016761,10016761,10016761,10016761,10016761,10016761,10016761,10016761</t>
+          <t>10016760,10048474,10048474,10016762,10016764,10016760,10048474,10048474,10016762,10016764,10016760,10048474,10048474,10016762,10016764,10016760,10048474,10048474,10016762,10016764,10016760,10016757,10016757,10016762,10016764,10016760,10016757,10016757,10016762,10016764,10016760,10016757,10016757,10016762,10016764,10016760,10016757,10016757,10016762,10016764,10016760,10048475,10048475,10016762,10016764,10016760,10048475,10048475,10016762,10016764,10016760,10048475,10048475,10016762,10016764,10016760,10048475,10048475,10016762,10016764,10016760,10016758,10016758,10016765,10016764,10016760,10016758,10016758,10016765,10016764,10016760,10016758,10016758,10016765,10016764,10016760,10016758,10016758,10016765,10016764,10016760,10016759,10016759,10016765,10016760,10016759,10016759,10016765,10016760,10016759,10016759,10016765,10016760,10016759,10016759,10016765,10016760,10016763,10016765,10016760,10016763,10016765,10016760,10016763,10016765,10016760,10016763,10016765,10016760,10016763,10016760,10016763,10016760,10016763,10016760,10016763,10016760,10016763,10016761,10016763,10016761,10016763,10016761,10016763,10016761,10016763,10016761,10016763,10016761,10016763,10016761,10016763,10016761,10016763,10016761,10016763,10016761,10016763,10016761,10016763,10016761,10016763,10016761,10016763,10016761,10016763,10016761,10016763,10016761,10016763,10016761,10016761,10016761,10016761,10016761,10016761,10016761,10016761,10016761,10016761,10016761,10016761,10016761</t>
         </is>
       </c>
       <c r="D21" s="3" t="n">
@@ -1526,7 +1526,7 @@
       </c>
       <c r="F21" s="0" t="inlineStr">
         <is>
-          <t>L1 W23/25; N=163; EHP=15907.000000; air:2x4,air:11x4,air:12x4,air:13x4,air:14x4,normal:17x29,normal:18x29,medium:83x12,swarm:84x45,heavy:88x16,medium:123x12</t>
+          <t>L1 W23/25; N=163; EHP=31075.213353; air:2x4,air:11x4,air:12x4,air:13x4,air:14x4,normal:17x29,normal:18x29,medium:83x12,swarm:84x45,heavy:88x16,medium:123x12 | manual: hp x2, air x2 from W5</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C22" s="0" t="inlineStr">
         <is>
-          <t>10016769,10016772,10048476,10016771,10016773,10016769,10016772,10048476,10016771,10016773,10016769,10016772,10048476,10016771,10016773,10016769,10016772,10048476,10016771,10016773,10016769,10016772,10016766,10016771,10016773,10016769,10016772,10016766,10016771,10016773,10016769,10016772,10016766,10016771,10016773,10016769,10016772,10016766,10016771,10016773,10016769,10016772,10048477,10016771,10016773,10016769,10016772,10048477,10016771,10016773,10016769,10016772,10048477,10016771,10016773,10016769,10016772,10048477,10016771,10016773,10016769,10016772,10016767,10016774,10016773,10016769,10016772,10016767,10016774,10016773,10016769,10016772,10016767,10016774,10016773,10016769,10016772,10016767,10016774,10016773,10016769,10016772,10016768,10016774,10016769,10016772,10016768,10016774,10016769,10016772,10016768,10016774,10016769,10016772,10016768,10016774,10016769,10016772,10016774,10016769,10016772,10016774,10016769,10016772,10016774,10016769,10016772,10016774,10016769,10016772,10016774,10016769,10016772,10016769,10016772,10016769,10016772,10016769,10016772,10016769,10016772,10016769,10016772,10016770,10016772,10016770,10016772,10016770,10016772,10016770,10016772,10016770,10016772,10016770,10016772,10016770,10016772,10016770,10016772,10016770,10016772,10016770,10016772,10016770,10016772,10016770,10016772,10016770,10016772,10016770,10016772,10016770,10016772,10016770,10016772,10016770,10016770,10016770,10016770,10016770,10016770,10016770,10016770,10016770,10016770,10016770,10016770,10016770,10016770</t>
+          <t>10016769,10048476,10048476,10016771,10016773,10016769,10048476,10048476,10016771,10016773,10016769,10048476,10048476,10016771,10016773,10016769,10048476,10048476,10016771,10016773,10016769,10016766,10016766,10016771,10016773,10016769,10016766,10016766,10016771,10016773,10016769,10016766,10016766,10016771,10016773,10016769,10016766,10016766,10016771,10016773,10016769,10048477,10048477,10016771,10016773,10016769,10048477,10048477,10016771,10016773,10016769,10048477,10048477,10016771,10016773,10016769,10048477,10048477,10016771,10016773,10016769,10016767,10016767,10016774,10016773,10016769,10016767,10016767,10016774,10016773,10016769,10016767,10016767,10016774,10016773,10016769,10016767,10016767,10016774,10016773,10016769,10016768,10016768,10016774,10016769,10016768,10016768,10016774,10016769,10016768,10016768,10016774,10016769,10016768,10016768,10016774,10016769,10016772,10016774,10016769,10016772,10016774,10016769,10016772,10016774,10016769,10016772,10016774,10016769,10016772,10016774,10016769,10016772,10016769,10016772,10016769,10016772,10016769,10016772,10016769,10016772,10016769,10016772,10016770,10016772,10016770,10016772,10016770,10016772,10016770,10016772,10016770,10016772,10016770,10016772,10016770,10016772,10016770,10016772,10016770,10016772,10016770,10016772,10016770,10016772,10016770,10016772,10016770,10016772,10016770,10016772,10016770,10016772,10016770,10016772,10016770,10016770,10016770,10016770,10016770,10016770,10016770,10016770,10016770,10016770,10016770,10016770,10016770,10016770</t>
         </is>
       </c>
       <c r="D22" s="3" t="n">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="F22" s="0" t="inlineStr">
         <is>
-          <t>L1 W24/25; N=169; EHP=17033.924050; air:2x4,air:11x4,air:12x4,air:13x4,air:14x4,normal:17x31,normal:18x30,medium:83x12,swarm:84x47,heavy:88x16,medium:123x13</t>
+          <t>L1 W24/25; N=169; EHP=33303.352210; air:2x4,air:11x4,air:12x4,air:13x4,air:14x4,normal:17x31,normal:18x30,medium:83x12,swarm:84x47,heavy:88x16,medium:123x13 | manual: hp x2, air x2 from W5</t>
         </is>
       </c>
     </row>
@@ -1557,7 +1557,7 @@
       </c>
       <c r="C23" s="0" t="inlineStr">
         <is>
-          <t>10016778,10016781,10048478,10016780,10016782,10016783,10016778,10016781,10048478,10016780,10016782,10016778,10016781,10048478,10016780,10016782,10016778,10016781,10048478,10016780,10016782,10016778,10016781,10016775,10016780,10016782,10016778,10016781,10016775,10016780,10016782,10016778,10016781,10016775,10016780,10016782,10016778,10016781,10016775,10016780,10016782,10016778,10016781,10048479,10016780,10016782,10016778,10016781,10048479,10016780,10016782,10016778,10016781,10048479,10016780,10016782,10016778,10016781,10048479,10016780,10016782,10016778,10016781,10016776,10016780,10016782,10016778,10016781,10016776,10016784,10016782,10016778,10016781,10016776,10016784,10016782,10016778,10016781,10016776,10016784,10016782,10016778,10016781,10016776,10016784,10016782,10016778,10016781,10016777,10016784,10016778,10016781,10016777,10016784,10016778,10016781,10016777,10016784,10016778,10016781,10016777,10016784,10016778,10016781,10016784,10016778,10016781,10016784,10016778,10016781,10016784,10016778,10016781,10016784,10016778,10016781,10016784,10016778,10016781,10016778,10016781,10016778,10016781,10016778,10016781,10016779,10016781,10016779,10016781,10016779,10016781,10016779,10016781,10016779,10016781,10016779,10016781,10016779,10016781,10016779,10016781,10016779,10016781,10016779,10016781,10016779,10016781,10016779,10016781,10016779,10016781,10016779,10016781,10016779,10016781,10016779,10016781,10016779,10016781,10016779,10016781,10016779,10016781,10016779,10016779,10016779,10016779,10016779,10016779,10016779,10016779,10016779,10016779,10016779,10016779</t>
+          <t>10016778,10048478,10048478,10016780,10016782,10016783,10016778,10048478,10048478,10016780,10016782,10016778,10048478,10048478,10016780,10016782,10016778,10048478,10048478,10016780,10016782,10016778,10016775,10016775,10016780,10016782,10016778,10016775,10016775,10016780,10016782,10016778,10016775,10016775,10016780,10016782,10016778,10016775,10016775,10016780,10016782,10016778,10048479,10048479,10016780,10016782,10016778,10048479,10048479,10016780,10016782,10016778,10048479,10048479,10016780,10016782,10016778,10048479,10048479,10016780,10016782,10016778,10016776,10016776,10016780,10016782,10016778,10016776,10016776,10016784,10016782,10016778,10016776,10016776,10016784,10016782,10016778,10016776,10016776,10016784,10016782,10016778,10016776,10016776,10016784,10016782,10016778,10016777,10016777,10016784,10016778,10016777,10016777,10016784,10016778,10016777,10016777,10016784,10016778,10016777,10016777,10016784,10016778,10016781,10016784,10016778,10016781,10016784,10016778,10016781,10016784,10016778,10016781,10016784,10016778,10016781,10016784,10016778,10016781,10016778,10016781,10016778,10016781,10016778,10016781,10016779,10016781,10016779,10016781,10016779,10016781,10016779,10016781,10016779,10016781,10016779,10016781,10016779,10016781,10016779,10016781,10016779,10016781,10016779,10016781,10016779,10016781,10016779,10016781,10016779,10016781,10016779,10016781,10016779,10016781,10016779,10016781,10016779,10016781,10016779,10016781,10016779,10016781,10016779,10016779,10016779,10016779,10016779,10016779,10016779,10016779,10016779,10016779,10016779,10016779</t>
         </is>
       </c>
       <c r="D23" s="3" t="n">
@@ -1568,7 +1568,7 @@
       </c>
       <c r="F23" s="0" t="inlineStr">
         <is>
-          <t>L1 W25/25; N=175; EHP=34007.327200; air:2x4,air:11x4,air:12x4,air:13x5,air:14x4,normal:17x30,normal:18x31,medium:83x13,swarm:84x49,heavy:88x17,elite:123x1,medium:123x13</t>
+          <t>L1 W25/25; N=175; EHP=66500.814715; air:2x4,air:11x4,air:12x4,air:13x5,air:14x4,normal:17x30,normal:18x31,medium:83x13,swarm:84x49,heavy:88x17,elite:123x1,medium:123x13 | manual: hp x2, air x2 from W5</t>
         </is>
       </c>
     </row>
@@ -1578,7 +1578,7 @@
       </c>
       <c r="C24" s="0" t="inlineStr">
         <is>
-          <t>3130136,3130673,3130019,3130668,3130709,3130136,3130673,3130019,3130668,3130709,3130136,3130673,3130019,3130668,3130709,3130136,3130673,3130091,3130668,3130709,3130136,3130673,3130091,3130668,3130709,3130136,3130673,3130091,3130668,3130709,3130136,3130673,3130099,3130668,3130709,3130136,3130673,3130099,3130668,3130709,3130136,3130673,3130099,3130668,3130709,3130136,3130673,3130107,3130988,3130709,3130136,3130673,3130107,3130988,3130709,3130136,3130673,3130107,3130988,3130709,3130136,3130673,3130115,3130988,3130136,3130673,3130115,3130988,3130136,3130673,3130115,3130988,3130136,3130673,3130988,3130136,3130673,3130988,3130136,3130673,3130988,3130136,3130673,3130136,3130673,3130136,3130673,3130136,3130673,3130144,3130673,3130144,3130673,3130144,3130673,3130144,3130673,3130144,3130673,3130144,3130673,3130144,3130673,3130144,3130673,3130144,3130673,3130144,3130673,3130144,3130673,3130144,3130144,3130144,3130144,3130144,3130144,3130144,3130144,3130144,3130144</t>
+          <t>3130136,3130019,3130019,3130668,3130709,3130136,3130019,3130019,3130668,3130709,3130136,3130019,3130019,3130668,3130709,3130136,3130091,3130091,3130668,3130709,3130136,3130091,3130091,3130668,3130709,3130136,3130091,3130091,3130668,3130709,3130136,3130099,3130099,3130668,3130709,3130136,3130099,3130099,3130668,3130709,3130136,3130099,3130099,3130668,3130709,3130136,3130107,3130107,3130988,3130709,3130136,3130107,3130107,3130988,3130709,3130136,3130107,3130107,3130988,3130709,3130136,3130115,3130115,3130988,3130136,3130115,3130115,3130988,3130136,3130115,3130115,3130988,3130136,3130673,3130988,3130136,3130673,3130988,3130136,3130673,3130988,3130136,3130673,3130136,3130673,3130136,3130673,3130136,3130673,3130144,3130673,3130144,3130673,3130144,3130673,3130144,3130673,3130144,3130673,3130144,3130673,3130144,3130673,3130144,3130673,3130144,3130673,3130144,3130673,3130144,3130673,3130144,3130144,3130144,3130144,3130144,3130144,3130144,3130144,3130144,3130144</t>
         </is>
       </c>
       <c r="D24" s="0" t="n">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="F24" s="0" t="inlineStr">
         <is>
-          <t>L1 W16/25; N=121; EHP=7066.000000; air:2x3,air:11x3,air:12x3,air:13x3,air:14x3,normal:17x22,normal:18x21,medium:83x9,swarm:84x33,heavy:88x12,medium:123x9</t>
+          <t>L1 W16/25; N=121; EHP=13801.297972; air:2x3,air:11x3,air:12x3,air:13x3,air:14x3,normal:17x22,normal:18x21,medium:83x9,swarm:84x33,heavy:88x12,medium:123x9 | manual: hp x2, air x2 from W5</t>
         </is>
       </c>
     </row>
@@ -1599,7 +1599,7 @@
       </c>
       <c r="C25" s="0" t="inlineStr">
         <is>
-          <t>3132136,3132673,3132019,3132668,3132709,3132136,3132673,3132019,3132668,3132709,3132136,3132673,3132019,3132668,3132709,3132136,3132673,3132091,3132668,3132709,3132136,3132673,3132091,3132668,3132709,3132136,3132673,3132091,3132668,3132709,3132136,3132673,3132099,3132668,3132709,3132136,3132673,3132099,3132668,3132709,3132136,3132673,3132099,3132668,3132709,3132136,3132673,3132107,3132668,3132709,3132136,3132673,3132107,3132988,3132709,3132136,3132673,3132107,3132988,3132709,3132136,3132673,3132115,3132988,3132136,3132673,3132115,3132988,3132136,3132673,3132115,3132988,3132136,3132673,3132988,3132136,3132673,3132988,3132136,3132673,3132988,3132136,3132673,3132988,3132136,3132673,3132136,3132673,3132136,3132673,3132136,3132673,3132144,3132673,3132144,3132673,3132144,3132673,3132144,3132673,3132144,3132673,3132144,3132673,3132144,3132673,3132144,3132673,3132144,3132673,3132144,3132673,3132144,3132673,3132144,3132673,3132144,3132144,3132144,3132144,3132144,3132144,3132144,3132144,3132144,3132144,3132144</t>
+          <t>3132136,3132019,3132019,3132668,3132709,3132136,3132019,3132019,3132668,3132709,3132136,3132019,3132019,3132668,3132709,3132136,3132091,3132091,3132668,3132709,3132136,3132091,3132091,3132668,3132709,3132136,3132091,3132091,3132668,3132709,3132136,3132099,3132099,3132668,3132709,3132136,3132099,3132099,3132668,3132709,3132136,3132099,3132099,3132668,3132709,3132136,3132107,3132107,3132668,3132709,3132136,3132107,3132107,3132988,3132709,3132136,3132107,3132107,3132988,3132709,3132136,3132115,3132115,3132988,3132136,3132115,3132115,3132988,3132136,3132115,3132115,3132988,3132136,3132673,3132988,3132136,3132673,3132988,3132136,3132673,3132988,3132136,3132673,3132988,3132136,3132673,3132136,3132673,3132136,3132673,3132136,3132673,3132144,3132673,3132144,3132673,3132144,3132673,3132144,3132673,3132144,3132673,3132144,3132673,3132144,3132673,3132144,3132673,3132144,3132673,3132144,3132673,3132144,3132673,3132144,3132673,3132144,3132144,3132144,3132144,3132144,3132144,3132144,3132144,3132144,3132144,3132144</t>
         </is>
       </c>
       <c r="D25" s="0" t="n">
@@ -1610,7 +1610,7 @@
       </c>
       <c r="F25" s="0" t="inlineStr">
         <is>
-          <t>L1 W17/25; N=127; EHP=7208.000000; air:2x3,air:11x3,air:12x3,air:13x3,air:14x3,normal:17x23,normal:18x23,medium:83x10,swarm:84x35,heavy:88x12,medium:123x9</t>
+          <t>L1 W17/25; N=127; EHP=14093.734724; air:2x3,air:11x3,air:12x3,air:13x3,air:14x3,normal:17x23,normal:18x23,medium:83x10,swarm:84x35,heavy:88x12,medium:123x9 | manual: hp x2, air x2 from W5</t>
         </is>
       </c>
     </row>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="C26" s="0" t="inlineStr">
         <is>
-          <t>3134136,3134673,3134019,3134668,3134709,3134136,3134673,3134019,3134668,3134709,3134136,3134673,3134019,3134668,3134709,3134136,3134673,3134091,3134668,3134709,3134136,3134673,3134091,3134668,3134709,3134136,3134673,3134091,3134668,3134709,3134136,3134673,3134099,3134668,3134709,3134136,3134673,3134099,3134668,3134709,3134136,3134673,3134099,3134668,3134709,3134136,3134673,3134099,3134988,3134709,3134136,3134673,3134107,3134988,3134709,3134136,3134673,3134107,3134988,3134709,3134136,3134673,3134107,3134988,3134709,3134136,3134673,3134115,3134988,3134136,3134673,3134115,3134988,3134136,3134673,3134115,3134988,3134136,3134673,3134988,3134136,3134673,3134988,3134136,3134673,3134988,3134136,3134673,3134136,3134673,3134136,3134673,3134136,3134673,3134136,3134673,3134144,3134673,3134144,3134673,3134144,3134673,3134144,3134673,3134144,3134673,3134144,3134673,3134144,3134673,3134144,3134673,3134144,3134673,3134144,3134673,3134144,3134673,3134144,3134673,3134144,3134673,3134144,3134144,3134144,3134144,3134144,3134144,3134144,3134144,3134144,3134144,3134144</t>
+          <t>3134136,3134019,3134019,3134668,3134709,3134136,3134019,3134019,3134668,3134709,3134136,3134019,3134019,3134668,3134709,3134136,3134091,3134091,3134668,3134709,3134136,3134091,3134091,3134668,3134709,3134136,3134091,3134091,3134668,3134709,3134136,3134099,3134099,3134668,3134709,3134136,3134099,3134099,3134668,3134709,3134136,3134099,3134099,3134668,3134709,3134136,3134099,3134099,3134988,3134709,3134136,3134107,3134107,3134988,3134709,3134136,3134107,3134107,3134988,3134709,3134136,3134107,3134107,3134988,3134709,3134136,3134115,3134115,3134988,3134136,3134115,3134115,3134988,3134136,3134115,3134115,3134988,3134136,3134673,3134988,3134136,3134673,3134988,3134136,3134673,3134988,3134136,3134673,3134136,3134673,3134136,3134673,3134136,3134673,3134136,3134673,3134144,3134673,3134144,3134673,3134144,3134673,3134144,3134673,3134144,3134673,3134144,3134673,3134144,3134673,3134144,3134673,3134144,3134673,3134144,3134673,3134144,3134673,3134144,3134673,3134144,3134673,3134144,3134144,3134144,3134144,3134144,3134144,3134144,3134144,3134144,3134144,3134144</t>
         </is>
       </c>
       <c r="D26" s="0" t="n">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="F26" s="0" t="inlineStr">
         <is>
-          <t>L1 W18/25; N=133; EHP=7704.084850; air:2x3,air:11x3,air:12x4,air:13x3,air:14x3,normal:17x24,normal:18x24,medium:83x9,swarm:84x37,heavy:88x13,medium:123x10</t>
+          <t>L1 W18/25; N=133; EHP=15056.359903; air:2x3,air:11x3,air:12x4,air:13x3,air:14x3,normal:17x24,normal:18x24,medium:83x9,swarm:84x37,heavy:88x13,medium:123x10 | manual: hp x2, air x2 from W5</t>
         </is>
       </c>
     </row>
@@ -1641,7 +1641,7 @@
       </c>
       <c r="C27" s="0" t="inlineStr">
         <is>
-          <t>3136136,3136673,3136019,3136668,3136709,3136136,3136673,3136019,3136668,3136709,3136136,3136673,3136019,3136668,3136709,3136136,3136673,3136019,3136668,3136709,3136136,3136673,3136091,3136668,3136709,3136136,3136673,3136091,3136668,3136709,3136136,3136673,3136091,3136668,3136709,3136136,3136673,3136099,3136668,3136709,3136136,3136673,3136099,3136668,3136709,3136136,3136673,3136099,3136668,3136709,3136136,3136673,3136107,3136988,3136709,3136136,3136673,3136107,3136988,3136709,3136136,3136673,3136107,3136988,3136709,3136136,3136673,3136107,3136988,3136136,3136673,3136115,3136988,3136136,3136673,3136115,3136988,3136136,3136673,3136115,3136988,3136136,3136673,3136988,3136136,3136673,3136988,3136136,3136673,3136988,3136136,3136673,3136136,3136673,3136136,3136673,3136136,3136673,3136136,3136673,3136144,3136673,3136144,3136673,3136144,3136673,3136144,3136673,3136144,3136673,3136144,3136673,3136144,3136673,3136144,3136673,3136144,3136673,3136144,3136673,3136144,3136673,3136144,3136673,3136144,3136673,3136144,3136144,3136144,3136144,3136144,3136144,3136144,3136144,3136144,3136144,3136144,3136144,3136144</t>
+          <t>3136136,3136019,3136019,3136668,3136709,3136136,3136019,3136019,3136668,3136709,3136136,3136019,3136019,3136668,3136709,3136136,3136019,3136019,3136668,3136709,3136136,3136091,3136091,3136668,3136709,3136136,3136091,3136091,3136668,3136709,3136136,3136091,3136091,3136668,3136709,3136136,3136099,3136099,3136668,3136709,3136136,3136099,3136099,3136668,3136709,3136136,3136099,3136099,3136668,3136709,3136136,3136107,3136107,3136988,3136709,3136136,3136107,3136107,3136988,3136709,3136136,3136107,3136107,3136988,3136709,3136136,3136107,3136107,3136988,3136136,3136115,3136115,3136988,3136136,3136115,3136115,3136988,3136136,3136115,3136115,3136988,3136136,3136673,3136988,3136136,3136673,3136988,3136136,3136673,3136988,3136136,3136673,3136136,3136673,3136136,3136673,3136136,3136673,3136136,3136673,3136144,3136673,3136144,3136673,3136144,3136673,3136144,3136673,3136144,3136673,3136144,3136673,3136144,3136673,3136144,3136673,3136144,3136673,3136144,3136673,3136144,3136673,3136144,3136673,3136144,3136673,3136144,3136144,3136144,3136144,3136144,3136144,3136144,3136144,3136144,3136144,3136144,3136144,3136144</t>
         </is>
       </c>
       <c r="D27" s="0" t="n">
@@ -1652,7 +1652,7 @@
       </c>
       <c r="F27" s="0" t="inlineStr">
         <is>
-          <t>L1 W19/25; N=139; EHP=8922.020800; air:2x4,air:11x3,air:12x3,air:13x4,air:14x3,normal:17x25,normal:18x26,medium:83x10,swarm:84x38,heavy:88x13,medium:123x10</t>
+          <t>L1 W19/25; N=139; EHP=17428.353067; air:2x4,air:11x3,air:12x3,air:13x4,air:14x3,normal:17x25,normal:18x26,medium:83x10,swarm:84x38,heavy:88x13,medium:123x10 | manual: hp x2, air x2 from W5</t>
         </is>
       </c>
     </row>
@@ -1662,7 +1662,7 @@
       </c>
       <c r="C28" s="0" t="inlineStr">
         <is>
-          <t>3138136,3138673,3138019,3138668,3138709,3138136,3138673,3138019,3138668,3138709,3138136,3138673,3138019,3138668,3138709,3138136,3138673,3138091,3138668,3138709,3138136,3138673,3138091,3138668,3138709,3138136,3138673,3138091,3138668,3138709,3138136,3138673,3138091,3138668,3138709,3138136,3138673,3138099,3138668,3138709,3138136,3138673,3138099,3138668,3138709,3138136,3138673,3138099,3138668,3138709,3138136,3138673,3138107,3138988,3138709,3138136,3138673,3138107,3138988,3138709,3138136,3138673,3138107,3138988,3138709,3138136,3138673,3138107,3138988,3138709,3138136,3138673,3138115,3138988,3138136,3138673,3138115,3138988,3138136,3138673,3138115,3138988,3138136,3138673,3138988,3138136,3138673,3138988,3138136,3138673,3138988,3138136,3138673,3138988,3138136,3138673,3138136,3138673,3138136,3138673,3138136,3138673,3138136,3138673,3138136,3138673,3138144,3138673,3138144,3138673,3138144,3138673,3138144,3138673,3138144,3138673,3138144,3138673,3138144,3138673,3138144,3138673,3138144,3138673,3138144,3138673,3138144,3138673,3138144,3138673,3138144,3138673,3138144,3138144,3138144,3138144,3138144,3138144,3138144,3138144,3138144,3138144,3138144,3138144,3138144</t>
+          <t>3138136,3138019,3138019,3138668,3138709,3138136,3138019,3138019,3138668,3138709,3138136,3138019,3138019,3138668,3138709,3138136,3138091,3138091,3138668,3138709,3138136,3138091,3138091,3138668,3138709,3138136,3138091,3138091,3138668,3138709,3138136,3138091,3138091,3138668,3138709,3138136,3138099,3138099,3138668,3138709,3138136,3138099,3138099,3138668,3138709,3138136,3138099,3138099,3138668,3138709,3138136,3138107,3138107,3138988,3138709,3138136,3138107,3138107,3138988,3138709,3138136,3138107,3138107,3138988,3138709,3138136,3138107,3138107,3138988,3138709,3138136,3138115,3138115,3138988,3138136,3138115,3138115,3138988,3138136,3138115,3138115,3138988,3138136,3138673,3138988,3138136,3138673,3138988,3138136,3138673,3138988,3138136,3138673,3138988,3138136,3138673,3138136,3138673,3138136,3138673,3138136,3138673,3138136,3138673,3138136,3138673,3138144,3138673,3138144,3138673,3138144,3138673,3138144,3138673,3138144,3138673,3138144,3138673,3138144,3138673,3138144,3138673,3138144,3138673,3138144,3138673,3138144,3138673,3138144,3138673,3138144,3138673,3138144,3138144,3138144,3138144,3138144,3138144,3138144,3138144,3138144,3138144,3138144,3138144,3138144</t>
         </is>
       </c>
       <c r="D28" s="0" t="n">
@@ -1673,7 +1673,7 @@
       </c>
       <c r="F28" s="0" t="inlineStr">
         <is>
-          <t>L1 W20/25; N=145; EHP=14988.793985; air:2x3,air:11x4,air:12x3,air:13x4,air:14x3,normal:17x27,normal:18x26,medium:83x10,swarm:84x40,heavy:88x14,medium:123x11</t>
+          <t>L1 W20/25; N=145; EHP=29312.071815; air:2x3,air:11x4,air:12x3,air:13x4,air:14x3,normal:17x27,normal:18x26,medium:83x10,swarm:84x40,heavy:88x14,medium:123x11 | manual: hp x2, air x2 from W5</t>
         </is>
       </c>
     </row>

--- a/Luban/Config/Datas/Levels/L01/EnemyList.xlsx
+++ b/Luban/Config/Datas/Levels/L01/EnemyList.xlsx
@@ -1169,7 +1169,7 @@
       </c>
       <c r="F4" s="0" t="inlineStr">
         <is>
-          <t>L1 W1/25; N=31; EHP=341.000000; normal:17x31 | manual: hp x2, air x2 from W5</t>
+          <t>L1 W1/25; N=31; EHP=255.750000; normal:17x31 | manual: hp x1.5 (air x2.0), air x2 from W5</t>
         </is>
       </c>
     </row>
@@ -1190,7 +1190,7 @@
       </c>
       <c r="F5" s="0" t="inlineStr">
         <is>
-          <t>L1 W2/25; N=37; EHP=426.169700; normal:17x19,normal:18x18 | manual: hp x2, air x2 from W5</t>
+          <t>L1 W2/25; N=37; EHP=319.627275; normal:17x19,normal:18x18 | manual: hp x1.5 (air x2.0), air x2 from W5</t>
         </is>
       </c>
     </row>
@@ -1211,7 +1211,7 @@
       </c>
       <c r="F6" s="0" t="inlineStr">
         <is>
-          <t>L1 W3/25; N=43; EHP=589.720393; air:13x5,normal:17x13,normal:18x13,swarm:84x12 | manual: hp x2, air x2 from W5</t>
+          <t>L1 W3/25; N=43; EHP=442.290295; air:13x5,normal:17x13,normal:18x13,swarm:84x12 | manual: hp x1.5 (air x2.0), air x2 from W5</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="F7" s="0" t="inlineStr">
         <is>
-          <t>L1 W4/25; N=49; EHP=776.629644; air:11x3,air:13x3,normal:17x15,normal:18x15,swarm:84x13 | manual: hp x2, air x2 from W5</t>
+          <t>L1 W4/25; N=49; EHP=582.472233; air:11x3,air:13x3,normal:17x15,normal:18x15,swarm:84x13 | manual: hp x1.5 (air x2.0), air x2 from W5</t>
         </is>
       </c>
     </row>
@@ -1253,7 +1253,7 @@
       </c>
       <c r="F8" s="0" t="inlineStr">
         <is>
-          <t>L1 W5/25; N=55; EHP=1352.175536; air:11x2,air:13x2,air:14x3,normal:17x12,normal:18x13,medium:83x8,swarm:84x15 | manual: hp x2, air x2 from W5</t>
+          <t>L1 W5/25; N=55; EHP=1056.640164; air:11x2,air:13x2,air:14x3,normal:17x12,normal:18x13,medium:83x8,swarm:84x15 | manual: hp x1.5 (air x2.0), air x2 from W5</t>
         </is>
       </c>
     </row>
@@ -1274,7 +1274,7 @@
       </c>
       <c r="F9" s="0" t="inlineStr">
         <is>
-          <t>L1 W6/25; N=61; EHP=1383.474783; air:11x2,air:13x3,air:14x2,normal:17x14,normal:18x14,medium:83x9,swarm:84x17 | manual: hp x2, air x2 from W5</t>
+          <t>L1 W6/25; N=61; EHP=1076.446957; air:11x2,air:13x3,air:14x2,normal:17x14,normal:18x14,medium:83x9,swarm:84x17 | manual: hp x1.5 (air x2.0), air x2 from W5</t>
         </is>
       </c>
     </row>
@@ -1295,7 +1295,7 @@
       </c>
       <c r="F10" s="0" t="inlineStr">
         <is>
-          <t>L1 W7/25; N=67; EHP=1613.174475; air:11x3,air:13x2,air:14x3,normal:17x15,normal:18x16,medium:83x10,swarm:84x18 | manual: hp x2, air x2 from W5</t>
+          <t>L1 W7/25; N=67; EHP=1256.942672; air:11x3,air:13x2,air:14x3,normal:17x15,normal:18x16,medium:83x10,swarm:84x18 | manual: hp x1.5 (air x2.0), air x2 from W5</t>
         </is>
       </c>
     </row>
@@ -1316,7 +1316,7 @@
       </c>
       <c r="F11" s="0" t="inlineStr">
         <is>
-          <t>L1 W8/25; N=73; EHP=2093.474396; air:11x2,air:12x2,air:13x3,air:14x2,normal:17x17,normal:18x17,medium:83x10,swarm:84x20 | manual: hp x2, air x2 from W5</t>
+          <t>L1 W8/25; N=73; EHP=1634.095014; air:11x2,air:12x2,air:13x3,air:14x2,normal:17x17,normal:18x17,medium:83x10,swarm:84x20 | manual: hp x1.5 (air x2.0), air x2 from W5</t>
         </is>
       </c>
     </row>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="F12" s="0" t="inlineStr">
         <is>
-          <t>L1 W9/25; N=79; EHP=2691.498955; air:11x3,air:12x2,air:13x2,air:14x2,normal:17x18,normal:18x19,medium:83x11,swarm:84x22 | manual: hp x2, air x2 from W5</t>
+          <t>L1 W9/25; N=79; EHP=2094.060692; air:11x3,air:12x2,air:13x2,air:14x2,normal:17x18,normal:18x19,medium:83x11,swarm:84x22 | manual: hp x1.5 (air x2.0), air x2 from W5</t>
         </is>
       </c>
     </row>
@@ -1358,7 +1358,7 @@
       </c>
       <c r="F13" s="0" t="inlineStr">
         <is>
-          <t>L1 W10/25; N=85; EHP=4971.075930; air:11x2,air:12x3,air:13x2,air:14x3,normal:17x20,normal:18x20,medium:83x12,swarm:84x23 | manual: hp x2, air x2 from W5</t>
+          <t>L1 W10/25; N=85; EHP=3871.979662; air:11x2,air:12x3,air:13x2,air:14x3,normal:17x20,normal:18x20,medium:83x12,swarm:84x23 | manual: hp x1.5 (air x2.0), air x2 from W5</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="F14" s="0" t="inlineStr">
         <is>
-          <t>L1 W11/25; N=91; EHP=5082.911550; air:11x3,air:12x3,air:13x3,air:14x2,normal:17x16,normal:18x17,medium:83x13,swarm:84x25,heavy:88x9 | manual: hp x2, air x2 from W5</t>
+          <t>L1 W11/25; N=91; EHP=3946.158169; air:11x3,air:12x3,air:13x3,air:14x2,normal:17x16,normal:18x17,medium:83x13,swarm:84x25,heavy:88x9 | manual: hp x1.5 (air x2.0), air x2 from W5</t>
         </is>
       </c>
     </row>
@@ -1400,7 +1400,7 @@
       </c>
       <c r="F15" s="0" t="inlineStr">
         <is>
-          <t>L1 W12/25; N=97; EHP=5260.065867; air:11x3,air:12x3,air:13x3,air:14x3,normal:17x18,normal:18x17,medium:83x14,swarm:84x27,heavy:88x9 | manual: hp x2, air x2 from W5</t>
+          <t>L1 W12/25; N=97; EHP=4088.288713; air:11x3,air:12x3,air:13x3,air:14x3,normal:17x18,normal:18x17,medium:83x14,swarm:84x27,heavy:88x9 | manual: hp x1.5 (air x2.0), air x2 from W5</t>
         </is>
       </c>
     </row>
@@ -1421,7 +1421,7 @@
       </c>
       <c r="F16" s="0" t="inlineStr">
         <is>
-          <t>L1 W13/25; N=103; EHP=6429.500629; air:2x3,air:11x2,air:12x3,air:13x2,air:14x2,normal:17x19,normal:18x19,medium:83x15,swarm:84x28,heavy:88x10 | manual: hp x2, air x2 from W5</t>
+          <t>L1 W13/25; N=103; EHP=4984.821364; air:2x3,air:11x2,air:12x3,air:13x2,air:14x2,normal:17x19,normal:18x19,medium:83x15,swarm:84x28,heavy:88x10 | manual: hp x1.5 (air x2.0), air x2 from W5</t>
         </is>
       </c>
     </row>
@@ -1442,7 +1442,7 @@
       </c>
       <c r="F17" s="0" t="inlineStr">
         <is>
-          <t>L1 W14/25; N=109; EHP=7757.104044; air:2x3,air:11x3,air:12x2,air:13x3,air:14x2,normal:17x20,normal:18x20,medium:83x16,swarm:84x30,heavy:88x10 | manual: hp x2, air x2 from W5</t>
+          <t>L1 W14/25; N=109; EHP=6020.503596; air:2x3,air:11x3,air:12x2,air:13x3,air:14x2,normal:17x20,normal:18x20,medium:83x16,swarm:84x30,heavy:88x10 | manual: hp x1.5 (air x2.0), air x2 from W5</t>
         </is>
       </c>
     </row>
@@ -1463,7 +1463,7 @@
       </c>
       <c r="F18" s="0" t="inlineStr">
         <is>
-          <t>L1 W15/25; N=115; EHP=13534.629346; air:2x2,air:11x3,air:12x3,air:13x3,air:14x3,normal:17x20,normal:18x21,medium:83x9,swarm:84x32,heavy:88x11,medium:123x8 | manual: hp x2, air x2 from W5</t>
+          <t>L1 W15/25; N=115; EHP=10511.057165; air:2x2,air:11x3,air:12x3,air:13x3,air:14x3,normal:17x20,normal:18x21,medium:83x9,swarm:84x32,heavy:88x11,medium:123x8 | manual: hp x1.5 (air x2.0), air x2 from W5</t>
         </is>
       </c>
     </row>
@@ -1484,7 +1484,7 @@
       </c>
       <c r="F19" s="0" t="inlineStr">
         <is>
-          <t>L1 W21/25; N=151; EHP=29889.133917; air:2x3,air:11x4,air:12x4,air:13x3,air:14x4,normal:17x27,normal:18x27,medium:83x11,swarm:84x42,heavy:88x15,medium:123x11 | manual: hp x2, air x2 from W5</t>
+          <t>L1 W21/25; N=151; EHP=23191.824781; air:2x3,air:11x4,air:12x4,air:13x3,air:14x4,normal:17x27,normal:18x27,medium:83x11,swarm:84x42,heavy:88x15,medium:123x11 | manual: hp x1.5 (air x2.0), air x2 from W5</t>
         </is>
       </c>
     </row>
@@ -1505,7 +1505,7 @@
       </c>
       <c r="F20" s="0" t="inlineStr">
         <is>
-          <t>L1 W22/25; N=157; EHP=30474.287440; air:2x4,air:11x3,air:12x4,air:13x4,air:14x4,normal:17x29,normal:18x28,medium:83x11,swarm:84x43,heavy:88x15,medium:123x12 | manual: hp x2, air x2 from W5</t>
+          <t>L1 W22/25; N=157; EHP=23660.892210; air:2x4,air:11x3,air:12x4,air:13x4,air:14x4,normal:17x29,normal:18x28,medium:83x11,swarm:84x43,heavy:88x15,medium:123x12 | manual: hp x1.5 (air x2.0), air x2 from W5</t>
         </is>
       </c>
     </row>
@@ -1526,7 +1526,7 @@
       </c>
       <c r="F21" s="0" t="inlineStr">
         <is>
-          <t>L1 W23/25; N=163; EHP=31075.213353; air:2x4,air:11x4,air:12x4,air:13x4,air:14x4,normal:17x29,normal:18x29,medium:83x12,swarm:84x45,heavy:88x16,medium:123x12 | manual: hp x2, air x2 from W5</t>
+          <t>L1 W23/25; N=163; EHP=24137.544993; air:2x4,air:11x4,air:12x4,air:13x4,air:14x4,normal:17x29,normal:18x29,medium:83x12,swarm:84x45,heavy:88x16,medium:123x12 | manual: hp x1.5 (air x2.0), air x2 from W5</t>
         </is>
       </c>
     </row>
@@ -1547,7 +1547,7 @@
       </c>
       <c r="F22" s="0" t="inlineStr">
         <is>
-          <t>L1 W24/25; N=169; EHP=33303.352210; air:2x4,air:11x4,air:12x4,air:13x4,air:14x4,normal:17x31,normal:18x30,medium:83x12,swarm:84x47,heavy:88x16,medium:123x13 | manual: hp x2, air x2 from W5</t>
+          <t>L1 W24/25; N=169; EHP=25837.572034; air:2x4,air:11x4,air:12x4,air:13x4,air:14x4,normal:17x31,normal:18x30,medium:83x12,swarm:84x47,heavy:88x16,medium:123x13 | manual: hp x1.5 (air x2.0), air x2 from W5</t>
         </is>
       </c>
     </row>
@@ -1568,7 +1568,7 @@
       </c>
       <c r="F23" s="0" t="inlineStr">
         <is>
-          <t>L1 W25/25; N=175; EHP=66500.814715; air:2x4,air:11x4,air:12x4,air:13x5,air:14x4,normal:17x30,normal:18x31,medium:83x13,swarm:84x49,heavy:88x17,elite:123x1,medium:123x13 | manual: hp x2, air x2 from W5</t>
+          <t>L1 W25/25; N=175; EHP=51578.680682; air:2x4,air:11x4,air:12x4,air:13x5,air:14x4,normal:17x30,normal:18x31,medium:83x13,swarm:84x49,heavy:88x17,elite:123x1,medium:123x13 | manual: hp x1.5 (air x2.0), air x2 from W5</t>
         </is>
       </c>
     </row>
@@ -1589,7 +1589,7 @@
       </c>
       <c r="F24" s="0" t="inlineStr">
         <is>
-          <t>L1 W16/25; N=121; EHP=13801.297972; air:2x3,air:11x3,air:12x3,air:13x3,air:14x3,normal:17x22,normal:18x21,medium:83x9,swarm:84x33,heavy:88x12,medium:123x9 | manual: hp x2, air x2 from W5</t>
+          <t>L1 W16/25; N=121; EHP=10723.013261; air:2x3,air:11x3,air:12x3,air:13x3,air:14x3,normal:17x22,normal:18x21,medium:83x9,swarm:84x33,heavy:88x12,medium:123x9 | manual: hp x1.5 (air x2.0), air x2 from W5</t>
         </is>
       </c>
     </row>
@@ -1610,7 +1610,7 @@
       </c>
       <c r="F25" s="0" t="inlineStr">
         <is>
-          <t>L1 W17/25; N=127; EHP=14093.734724; air:2x3,air:11x3,air:12x3,air:13x3,air:14x3,normal:17x23,normal:18x23,medium:83x10,swarm:84x35,heavy:88x12,medium:123x9 | manual: hp x2, air x2 from W5</t>
+          <t>L1 W17/25; N=127; EHP=10932.849478; air:2x3,air:11x3,air:12x3,air:13x3,air:14x3,normal:17x23,normal:18x23,medium:83x10,swarm:84x35,heavy:88x12,medium:123x9 | manual: hp x1.5 (air x2.0), air x2 from W5</t>
         </is>
       </c>
     </row>
@@ -1631,7 +1631,7 @@
       </c>
       <c r="F26" s="0" t="inlineStr">
         <is>
-          <t>L1 W18/25; N=133; EHP=15056.359903; air:2x3,air:11x3,air:12x4,air:13x3,air:14x3,normal:17x24,normal:18x24,medium:83x9,swarm:84x37,heavy:88x13,medium:123x10 | manual: hp x2, air x2 from W5</t>
+          <t>L1 W18/25; N=133; EHP=11688.055949; air:2x3,air:11x3,air:12x4,air:13x3,air:14x3,normal:17x24,normal:18x24,medium:83x9,swarm:84x37,heavy:88x13,medium:123x10 | manual: hp x1.5 (air x2.0), air x2 from W5</t>
         </is>
       </c>
     </row>
@@ -1652,7 +1652,7 @@
       </c>
       <c r="F27" s="0" t="inlineStr">
         <is>
-          <t>L1 W19/25; N=139; EHP=17428.353067; air:2x4,air:11x3,air:12x3,air:13x4,air:14x3,normal:17x25,normal:18x26,medium:83x10,swarm:84x38,heavy:88x13,medium:123x10 | manual: hp x2, air x2 from W5</t>
+          <t>L1 W19/25; N=139; EHP=13538.914400; air:2x4,air:11x3,air:12x3,air:13x4,air:14x3,normal:17x25,normal:18x26,medium:83x10,swarm:84x38,heavy:88x13,medium:123x10 | manual: hp x1.5 (air x2.0), air x2 from W5</t>
         </is>
       </c>
     </row>
@@ -1673,7 +1673,7 @@
       </c>
       <c r="F28" s="0" t="inlineStr">
         <is>
-          <t>L1 W20/25; N=145; EHP=29312.071815; air:2x3,air:11x4,air:12x3,air:13x4,air:14x3,normal:17x27,normal:18x26,medium:83x10,swarm:84x40,heavy:88x14,medium:123x11 | manual: hp x2, air x2 from W5</t>
+          <t>L1 W20/25; N=145; EHP=22732.759536; air:2x3,air:11x4,air:12x3,air:13x4,air:14x3,normal:17x27,normal:18x26,medium:83x10,swarm:84x40,heavy:88x14,medium:123x11 | manual: hp x1.5 (air x2.0), air x2 from W5</t>
         </is>
       </c>
     </row>

--- a/Luban/Config/Datas/Levels/L01/EnemyList.xlsx
+++ b/Luban/Config/Datas/Levels/L01/EnemyList.xlsx
@@ -1158,7 +1158,7 @@
       </c>
       <c r="C4" s="0" t="inlineStr">
         <is>
-          <t>3100136,3100136,3100136,3100136,3100136,3100136,3100136,3100136,3100136,3100136,3100136,3100136,3100136,3100136,3100136,3100136,3100136,3100136,3100136,3100136,3100136,3100136,3100136,3100136,3100136,3100136,3100136,3100136,3100136,3100136,3100136</t>
+          <t>5000000,5000000,5000000,5000000,5000000,5000000,5000000,5000000,5000000,5000000,5000000,5000000,5000000,5000000,5000000,5000000,5000000,5000000,5000000,5000000,5000000,5000000,5000000,5000000,5000000,5000000,5000000,5000000,5000000,5000000,5000000</t>
         </is>
       </c>
       <c r="D4" s="3" t="n">
@@ -1169,7 +1169,7 @@
       </c>
       <c r="F4" s="0" t="inlineStr">
         <is>
-          <t>L1 W1/25; N=31; EHP=255.750000; normal:17x31 | manual: hp x1.5 (air x2.0), air x2 from W5</t>
+          <t>L1 W1/25; N=31; EHP=256.000015; normal:17x16,normal:18x15 | diagram-maze-20261028: air from W5 (Bat only), strictly increasing</t>
         </is>
       </c>
     </row>
@@ -1179,7 +1179,7 @@
       </c>
       <c r="C5" s="0" t="inlineStr">
         <is>
-          <t>3102136,3102136,3102136,3102136,3102136,3102136,3102136,3102136,3102136,3102136,3102136,3102136,3102136,3102136,3102136,3102136,3102136,3102136,3102136,3102144,3102144,3102144,3102144,3102144,3102144,3102144,3102144,3102144,3102144,3102144,3102144,3102144,3102144,3102144,3102144,3102144,3102144</t>
+          <t>5000010,5000010,5000010,5000010,5000010,5000010,5000010,5000010,5000010,5000010,5000010,5000010,5000010,5000010,5000010,5000010,5000010,5000010,5000010,5000010,5000010,5000010,5000010,5000010,5000010,5000010,5000010,5000010,5000010,5000010,5000010,5000010,5000010,5000010,5000010,5000010,5000010</t>
         </is>
       </c>
       <c r="D5" s="3" t="n">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="F5" s="0" t="inlineStr">
         <is>
-          <t>L1 W2/25; N=37; EHP=319.627275; normal:17x19,normal:18x18 | manual: hp x1.5 (air x2.0), air x2 from W5</t>
+          <t>L1 W2/25; N=37; EHP=320.000013; normal:17x18,normal:18x19 | diagram-maze-20261028: air from W5 (Bat only), strictly increasing</t>
         </is>
       </c>
     </row>
@@ -1200,7 +1200,7 @@
       </c>
       <c r="C6" s="0" t="inlineStr">
         <is>
-          <t>3104136,3104673,3104136,3104673,3104136,3104673,3104136,3104673,3104136,3104673,3104136,3104673,3104136,3104673,3104136,3104673,3104136,3104673,3104136,3104673,3104136,3104673,3104136,3104673,3104136,3104144,3104144,3104144,3104144,3104144,3104144,3104144,3104144,3104144,3104144,3104144,3104144,3104144,3104136,3104136,3104136,3104136,3104136</t>
+          <t>5000020,5000020,5000021,5000020,5000020,5000021,5000020,5000020,5000021,5000020,5000020,5000021,5000020,5000020,5000021,5000020,5000020,5000021,5000020,5000020,5000021,5000020,5000020,5000021,5000020,5000020,5000021,5000020,5000020,5000021,5000020,5000020,5000021,5000020,5000020,5000021,5000020,5000020,5000020,5000020,5000020,5000020,5000020</t>
         </is>
       </c>
       <c r="D6" s="3" t="n">
@@ -1211,7 +1211,7 @@
       </c>
       <c r="F6" s="0" t="inlineStr">
         <is>
-          <t>L1 W3/25; N=43; EHP=442.290295; air:13x5,normal:17x13,normal:18x13,swarm:84x12 | manual: hp x1.5 (air x2.0), air x2 from W5</t>
+          <t>L1 W3/25; N=43; EHP=442.000011; normal:17x16,normal:18x15,swarm:84x12 | diagram-maze-20261028: air from W5 (Bat only), strictly increasing</t>
         </is>
       </c>
     </row>
@@ -1221,7 +1221,7 @@
       </c>
       <c r="C7" s="0" t="inlineStr">
         <is>
-          <t>3106136,3106673,3106136,3106673,3106136,3106673,3106136,3106673,3106136,3106673,3106136,3106673,3106136,3106673,3106136,3106673,3106136,3106673,3106136,3106673,3106136,3106673,3106136,3106673,3106136,3106673,3106136,3106136,3106144,3106144,3106144,3106144,3106144,3106144,3106144,3106144,3106144,3106144,3106144,3106144,3106144,3106144,3106144,3106136,3106136,3106136,3106136,3106136,3106136</t>
+          <t>5000030,5000030,5000031,5000030,5000030,5000031,5000030,5000030,5000031,5000030,5000030,5000031,5000030,5000030,5000031,5000030,5000030,5000031,5000030,5000030,5000031,5000030,5000030,5000031,5000030,5000030,5000031,5000030,5000030,5000031,5000030,5000030,5000031,5000030,5000030,5000031,5000030,5000030,5000031,5000030,5000030,5000031,5000030,5000030,5000030,5000030,5000030,5000030,5000030</t>
         </is>
       </c>
       <c r="D7" s="3" t="n">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="F7" s="0" t="inlineStr">
         <is>
-          <t>L1 W4/25; N=49; EHP=582.472233; air:11x3,air:13x3,normal:17x15,normal:18x15,swarm:84x13 | manual: hp x1.5 (air x2.0), air x2 from W5</t>
+          <t>L1 W4/25; N=49; EHP=581.999999; normal:17x17,normal:18x18,swarm:84x14 | diagram-maze-20261028: air from W5 (Bat only), strictly increasing</t>
         </is>
       </c>
     </row>
@@ -1242,7 +1242,7 @@
       </c>
       <c r="C8" s="0" t="inlineStr">
         <is>
-          <t>3108136,3108091,3108091,3108668,3108136,3108091,3108091,3108668,3108136,3108107,3108107,3108668,3108136,3108107,3108107,3108668,3108136,3108115,3108115,3108668,3108136,3108115,3108115,3108668,3108136,3108115,3108115,3108668,3108136,3108673,3108668,3108136,3108673,3108136,3108673,3108136,3108673,3108136,3108673,3108144,3108673,3108144,3108673,3108144,3108673,3108144,3108144,3108144,3108144,3108144,3108144,3108144,3108144,3108144,3108144</t>
+          <t>5000040,5000040,5000041,5000042,5000045,5000040,5000040,5000041,5000042,5000045,5000040,5000040,5000041,5000042,5000040,5000040,5000041,5000042,5000040,5000040,5000041,5000042,5000040,5000040,5000041,5000042,5000040,5000040,5000041,5000042,5000040,5000040,5000041,5000042,5000040,5000040,5000041,5000042,5000040,5000040,5000041,5000042,5000040,5000040,5000041,5000040,5000040,5000041,5000040,5000040,5000041,5000040,5000040,5000041,5000041,5000040,5000040,5000041,5000042,5000045,5000040,5000040,5000041,5000042,5000045,5000040,5000040,5000041,5000042,5000040,5000040,5000041,5000042,5000040,5000040,5000041,5000042,5000040,5000040,5000041,5000042,5000040,5000040,5000041,5000042,5000040,5000040,5000041,5000042,5000040,5000040,5000041,5000042,5000040,5000040,5000041,5000042,5000040,5000040,5000041,5000040,5000040,5000041,5000040,5000040,5000041,5000040,5000040,5000041,5000041</t>
         </is>
       </c>
       <c r="D8" s="3" t="n">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="F8" s="0" t="inlineStr">
         <is>
-          <t>L1 W5/25; N=55; EHP=1056.640164; air:11x2,air:13x2,air:14x3,normal:17x12,normal:18x13,medium:83x8,swarm:84x15 | manual: hp x1.5 (air x2.0), air x2 from W5</t>
+          <t>L1 W5/25; N=110; EHP=3213.174621; variants:4 (counts doubled, hp x1.5/x2.0) | wavebuff-20261029</t>
         </is>
       </c>
     </row>
@@ -1263,7 +1263,7 @@
       </c>
       <c r="C9" s="0" t="inlineStr">
         <is>
-          <t>3110136,3110091,3110091,3110668,3110136,3110091,3110091,3110668,3110136,3110107,3110107,3110668,3110136,3110107,3110107,3110668,3110136,3110107,3110107,3110668,3110136,3110115,3110115,3110668,3110136,3110115,3110115,3110668,3110136,3110673,3110668,3110136,3110673,3110668,3110136,3110673,3110136,3110673,3110136,3110673,3110136,3110673,3110136,3110673,3110144,3110673,3110144,3110673,3110144,3110673,3110144,3110144,3110144,3110144,3110144,3110144,3110144,3110144,3110144,3110144,3110144</t>
+          <t>5000050,5000050,5000051,5000052,5000055,5000050,5000050,5000051,5000052,5000055,5000050,5000050,5000051,5000052,5000055,5000050,5000050,5000051,5000052,5000050,5000050,5000051,5000052,5000050,5000050,5000051,5000052,5000050,5000050,5000051,5000052,5000050,5000050,5000051,5000052,5000050,5000050,5000051,5000052,5000050,5000050,5000051,5000052,5000050,5000050,5000051,5000052,5000050,5000050,5000051,5000050,5000050,5000051,5000050,5000050,5000051,5000050,5000050,5000051,5000051,5000051,5000050,5000050,5000051,5000052,5000055,5000050,5000050,5000051,5000052,5000055,5000050,5000050,5000051,5000052,5000055,5000050,5000050,5000051,5000052,5000050,5000050,5000051,5000052,5000050,5000050,5000051,5000052,5000050,5000050,5000051,5000052,5000050,5000050,5000051,5000052,5000050,5000050,5000051,5000052,5000050,5000050,5000051,5000052,5000050,5000050,5000051,5000052,5000050,5000050,5000051,5000050,5000050,5000051,5000050,5000050,5000051,5000050,5000050,5000051,5000051,5000051</t>
         </is>
       </c>
       <c r="D9" s="3" t="n">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="F9" s="0" t="inlineStr">
         <is>
-          <t>L1 W6/25; N=61; EHP=1076.446957; air:11x2,air:13x3,air:14x2,normal:17x14,normal:18x14,medium:83x9,swarm:84x17 | manual: hp x1.5 (air x2.0), air x2 from W5</t>
+          <t>L1 W6/25; N=122; EHP=3286.118479; variants:4 (counts doubled, hp x1.5/x2.0) | wavebuff-20261029</t>
         </is>
       </c>
     </row>
@@ -1284,7 +1284,7 @@
       </c>
       <c r="C10" s="0" t="inlineStr">
         <is>
-          <t>3112136,3112091,3112091,3112668,3112136,3112091,3112091,3112668,3112136,3112091,3112091,3112668,3112136,3112107,3112107,3112668,3112136,3112107,3112107,3112668,3112136,3112115,3112115,3112668,3112136,3112115,3112115,3112668,3112136,3112115,3112115,3112668,3112136,3112673,3112668,3112136,3112673,3112668,3112136,3112673,3112136,3112673,3112136,3112673,3112136,3112673,3112136,3112673,3112144,3112673,3112144,3112673,3112144,3112673,3112144,3112144,3112144,3112144,3112144,3112144,3112144,3112144,3112144,3112144,3112144,3112144,3112144</t>
+          <t>5000060,5000060,5000061,5000062,5000065,5000060,5000060,5000061,5000062,5000065,5000060,5000060,5000061,5000062,5000065,5000060,5000060,5000061,5000062,5000065,5000060,5000060,5000061,5000062,5000060,5000060,5000061,5000062,5000060,5000060,5000061,5000062,5000060,5000060,5000061,5000062,5000060,5000060,5000061,5000062,5000060,5000060,5000061,5000062,5000060,5000060,5000061,5000062,5000060,5000060,5000061,5000062,5000060,5000060,5000061,5000060,5000060,5000061,5000060,5000060,5000061,5000060,5000060,5000061,5000060,5000061,5000061,5000060,5000060,5000061,5000062,5000065,5000060,5000060,5000061,5000062,5000065,5000060,5000060,5000061,5000062,5000065,5000060,5000060,5000061,5000062,5000065,5000060,5000060,5000061,5000062,5000060,5000060,5000061,5000062,5000060,5000060,5000061,5000062,5000060,5000060,5000061,5000062,5000060,5000060,5000061,5000062,5000060,5000060,5000061,5000062,5000060,5000060,5000061,5000062,5000060,5000060,5000061,5000062,5000060,5000060,5000061,5000060,5000060,5000061,5000060,5000060,5000061,5000060,5000060,5000061,5000060,5000061,5000061</t>
         </is>
       </c>
       <c r="D10" s="3" t="n">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="F10" s="0" t="inlineStr">
         <is>
-          <t>L1 W7/25; N=67; EHP=1256.942672; air:11x3,air:13x2,air:14x3,normal:17x15,normal:18x16,medium:83x10,swarm:84x18 | manual: hp x1.5 (air x2.0), air x2 from W5</t>
+          <t>L1 W7/25; N=134; EHP=3853.089834; variants:4 (counts doubled, hp x1.5/x2.0) | wavebuff-20261029</t>
         </is>
       </c>
     </row>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="C11" s="0" t="inlineStr">
         <is>
-          <t>3114136,3114091,3114091,3114668,3114136,3114091,3114091,3114668,3114136,3114099,3114099,3114668,3114136,3114099,3114099,3114668,3114136,3114107,3114107,3114668,3114136,3114107,3114107,3114668,3114136,3114107,3114107,3114668,3114136,3114115,3114115,3114668,3114136,3114115,3114115,3114668,3114136,3114673,3114668,3114136,3114673,3114136,3114673,3114136,3114673,3114136,3114673,3114136,3114673,3114136,3114673,3114136,3114673,3114144,3114673,3114144,3114673,3114144,3114673,3114144,3114144,3114144,3114144,3114144,3114144,3114144,3114144,3114144,3114144,3114144,3114144,3114144,3114144</t>
+          <t>5000070,5000070,5000071,5000072,5000075,5000070,5000070,5000071,5000072,5000075,5000070,5000070,5000071,5000072,5000075,5000070,5000070,5000071,5000072,5000075,5000070,5000070,5000071,5000072,5000075,5000070,5000070,5000071,5000072,5000070,5000070,5000071,5000072,5000070,5000070,5000071,5000072,5000070,5000070,5000071,5000072,5000070,5000070,5000071,5000072,5000070,5000070,5000071,5000072,5000070,5000070,5000071,5000072,5000070,5000070,5000071,5000072,5000070,5000070,5000071,5000070,5000070,5000071,5000070,5000070,5000071,5000070,5000070,5000071,5000070,5000071,5000071,5000071,5000070,5000070,5000071,5000072,5000075,5000070,5000070,5000071,5000072,5000075,5000070,5000070,5000071,5000072,5000075,5000070,5000070,5000071,5000072,5000075,5000070,5000070,5000071,5000072,5000075,5000070,5000070,5000071,5000072,5000070,5000070,5000071,5000072,5000070,5000070,5000071,5000072,5000070,5000070,5000071,5000072,5000070,5000070,5000071,5000072,5000070,5000070,5000071,5000072,5000070,5000070,5000071,5000072,5000070,5000070,5000071,5000072,5000070,5000070,5000071,5000070,5000070,5000071,5000070,5000070,5000071,5000070,5000070,5000071,5000070,5000071,5000071,5000071</t>
         </is>
       </c>
       <c r="D11" s="3" t="n">
@@ -1316,7 +1316,7 @@
       </c>
       <c r="F11" s="0" t="inlineStr">
         <is>
-          <t>L1 W8/25; N=73; EHP=1634.095014; air:11x2,air:12x2,air:13x3,air:14x2,normal:17x17,normal:18x17,medium:83x10,swarm:84x20 | manual: hp x1.5 (air x2.0), air x2 from W5</t>
+          <t>L1 W8/25; N=146; EHP=5024.550000; variants:4 (counts doubled, hp x1.5/x2.0) | wavebuff-20261029</t>
         </is>
       </c>
     </row>
@@ -1326,7 +1326,7 @@
       </c>
       <c r="C12" s="0" t="inlineStr">
         <is>
-          <t>3116136,3116091,3116091,3116668,3116136,3116091,3116091,3116668,3116136,3116091,3116091,3116668,3116136,3116099,3116099,3116668,3116136,3116099,3116099,3116668,3116136,3116107,3116107,3116668,3116136,3116107,3116107,3116668,3116136,3116115,3116115,3116668,3116136,3116115,3116115,3116668,3116136,3116673,3116668,3116136,3116673,3116668,3116136,3116673,3116136,3116673,3116136,3116673,3116136,3116673,3116136,3116673,3116136,3116673,3116136,3116673,3116144,3116673,3116144,3116673,3116144,3116673,3116144,3116673,3116144,3116144,3116144,3116144,3116144,3116144,3116144,3116144,3116144,3116144,3116144,3116144,3116144,3116144,3116144</t>
+          <t>5000080,5000080,5000081,5000082,5000085,5000080,5000080,5000081,5000082,5000085,5000080,5000080,5000081,5000082,5000085,5000080,5000080,5000081,5000082,5000085,5000080,5000080,5000081,5000082,5000085,5000080,5000080,5000081,5000082,5000085,5000080,5000080,5000081,5000082,5000080,5000080,5000081,5000082,5000080,5000080,5000081,5000082,5000080,5000080,5000081,5000082,5000080,5000080,5000081,5000082,5000080,5000080,5000081,5000082,5000080,5000080,5000081,5000082,5000080,5000080,5000081,5000082,5000080,5000080,5000081,5000080,5000080,5000081,5000080,5000080,5000081,5000080,5000080,5000081,5000080,5000080,5000081,5000081,5000081,5000080,5000080,5000081,5000082,5000085,5000080,5000080,5000081,5000082,5000085,5000080,5000080,5000081,5000082,5000085,5000080,5000080,5000081,5000082,5000085,5000080,5000080,5000081,5000082,5000085,5000080,5000080,5000081,5000082,5000085,5000080,5000080,5000081,5000082,5000080,5000080,5000081,5000082,5000080,5000080,5000081,5000082,5000080,5000080,5000081,5000082,5000080,5000080,5000081,5000082,5000080,5000080,5000081,5000082,5000080,5000080,5000081,5000082,5000080,5000080,5000081,5000082,5000080,5000080,5000081,5000080,5000080,5000081,5000080,5000080,5000081,5000080,5000080,5000081,5000080,5000080,5000081,5000081,5000081</t>
         </is>
       </c>
       <c r="D12" s="3" t="n">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="F12" s="0" t="inlineStr">
         <is>
-          <t>L1 W9/25; N=79; EHP=2094.060692; air:11x3,air:12x2,air:13x2,air:14x2,normal:17x18,normal:18x19,medium:83x11,swarm:84x22 | manual: hp x1.5 (air x2.0), air x2 from W5</t>
+          <t>L1 W9/25; N=158; EHP=6455.595767; variants:4 (counts doubled, hp x1.5/x2.0) | wavebuff-20261029</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="C13" s="0" t="inlineStr">
         <is>
-          <t>3118136,3118091,3118091,3118668,3118136,3118091,3118091,3118668,3118136,3118099,3118099,3118668,3118136,3118099,3118099,3118668,3118136,3118099,3118099,3118668,3118136,3118107,3118107,3118668,3118136,3118107,3118107,3118668,3118136,3118115,3118115,3118668,3118136,3118115,3118115,3118668,3118136,3118115,3118115,3118668,3118136,3118673,3118668,3118136,3118673,3118668,3118136,3118673,3118136,3118673,3118136,3118673,3118136,3118673,3118136,3118673,3118136,3118673,3118136,3118673,3118136,3118673,3118144,3118673,3118144,3118673,3118144,3118673,3118144,3118144,3118144,3118144,3118144,3118144,3118144,3118144,3118144,3118144,3118144,3118144,3118144,3118144,3118144,3118144,3118144</t>
+          <t>5000090,5000090,5000091,5000092,5000095,5000090,5000090,5000091,5000092,5000095,5000090,5000090,5000091,5000092,5000095,5000090,5000090,5000091,5000092,5000095,5000090,5000090,5000091,5000092,5000095,5000090,5000090,5000091,5000092,5000095,5000090,5000090,5000091,5000092,5000095,5000090,5000090,5000091,5000092,5000090,5000090,5000091,5000092,5000090,5000090,5000091,5000092,5000090,5000090,5000091,5000092,5000090,5000090,5000091,5000092,5000090,5000090,5000091,5000092,5000090,5000090,5000091,5000092,5000090,5000090,5000091,5000092,5000090,5000090,5000091,5000090,5000090,5000091,5000090,5000090,5000091,5000090,5000090,5000091,5000090,5000090,5000091,5000091,5000091,5000091,5000090,5000090,5000091,5000092,5000095,5000090,5000090,5000091,5000092,5000095,5000090,5000090,5000091,5000092,5000095,5000090,5000090,5000091,5000092,5000095,5000090,5000090,5000091,5000092,5000095,5000090,5000090,5000091,5000092,5000095,5000090,5000090,5000091,5000092,5000095,5000090,5000090,5000091,5000092,5000090,5000090,5000091,5000092,5000090,5000090,5000091,5000092,5000090,5000090,5000091,5000092,5000090,5000090,5000091,5000092,5000090,5000090,5000091,5000092,5000090,5000090,5000091,5000092,5000090,5000090,5000091,5000092,5000090,5000090,5000091,5000090,5000090,5000091,5000090,5000090,5000091,5000090,5000090,5000091,5000090,5000090,5000091,5000091,5000091,5000091</t>
         </is>
       </c>
       <c r="D13" s="3" t="n">
@@ -1358,7 +1358,7 @@
       </c>
       <c r="F13" s="0" t="inlineStr">
         <is>
-          <t>L1 W10/25; N=85; EHP=3871.979662; air:11x2,air:12x3,air:13x2,air:14x3,normal:17x20,normal:18x20,medium:83x12,swarm:84x23 | manual: hp x1.5 (air x2.0), air x2 from W5</t>
+          <t>L1 W10/25; N=170; EHP=11964.417797; variants:4 (counts doubled, hp x1.5/x2.0) | wavebuff-20261029</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       </c>
       <c r="C14" s="0" t="inlineStr">
         <is>
-          <t>3120136,3120091,3120091,3120668,3120709,3120136,3120091,3120091,3120668,3120709,3120136,3120091,3120091,3120668,3120709,3120136,3120099,3120099,3120668,3120709,3120136,3120099,3120099,3120668,3120709,3120136,3120099,3120099,3120668,3120709,3120136,3120107,3120107,3120668,3120709,3120136,3120107,3120107,3120668,3120709,3120136,3120107,3120107,3120668,3120709,3120136,3120115,3120115,3120668,3120136,3120115,3120115,3120668,3120136,3120673,3120668,3120136,3120673,3120668,3120136,3120673,3120136,3120673,3120136,3120673,3120144,3120673,3120144,3120673,3120144,3120673,3120144,3120673,3120144,3120673,3120144,3120673,3120144,3120673,3120144,3120673,3120144,3120673,3120144,3120144,3120144,3120144,3120144,3120144,3120144,3120144</t>
+          <t>5000100,5000100,5000101,5000102,5000103,5000105,5000100,5000100,5000101,5000102,5000103,5000105,5000100,5000100,5000101,5000102,5000103,5000105,5000100,5000100,5000101,5000102,5000103,5000105,5000100,5000100,5000101,5000102,5000103,5000105,5000100,5000100,5000101,5000102,5000103,5000105,5000100,5000100,5000101,5000102,5000103,5000105,5000100,5000100,5000101,5000102,5000103,5000105,5000100,5000100,5000101,5000102,5000103,5000100,5000100,5000101,5000102,5000100,5000100,5000101,5000102,5000100,5000100,5000101,5000102,5000100,5000100,5000101,5000102,5000100,5000100,5000101,5000100,5000100,5000101,5000100,5000100,5000101,5000100,5000100,5000101,5000100,5000100,5000101,5000100,5000100,5000101,5000100,5000101,5000101,5000101,5000100,5000100,5000101,5000102,5000103,5000105,5000100,5000100,5000101,5000102,5000103,5000105,5000100,5000100,5000101,5000102,5000103,5000105,5000100,5000100,5000101,5000102,5000103,5000105,5000100,5000100,5000101,5000102,5000103,5000105,5000100,5000100,5000101,5000102,5000103,5000105,5000100,5000100,5000101,5000102,5000103,5000105,5000100,5000100,5000101,5000102,5000103,5000105,5000100,5000100,5000101,5000102,5000103,5000100,5000100,5000101,5000102,5000100,5000100,5000101,5000102,5000100,5000100,5000101,5000102,5000100,5000100,5000101,5000102,5000100,5000100,5000101,5000100,5000100,5000101,5000100,5000100,5000101,5000100,5000100,5000101,5000100,5000100,5000101,5000100,5000100,5000101,5000100,5000101,5000101,5000101</t>
         </is>
       </c>
       <c r="D14" s="3" t="n">
@@ -1379,7 +1379,7 @@
       </c>
       <c r="F14" s="0" t="inlineStr">
         <is>
-          <t>L1 W11/25; N=91; EHP=3946.158169; air:11x3,air:12x3,air:13x3,air:14x2,normal:17x16,normal:18x17,medium:83x13,swarm:84x25,heavy:88x9 | manual: hp x1.5 (air x2.0), air x2 from W5</t>
+          <t>L1 W11/25; N=182; EHP=12141.295522; variants:5 (counts doubled, hp x1.5/x2.0) | wavebuff-20261029</t>
         </is>
       </c>
     </row>
@@ -1389,7 +1389,7 @@
       </c>
       <c r="C15" s="0" t="inlineStr">
         <is>
-          <t>3122136,3122091,3122091,3122668,3122709,3122136,3122091,3122091,3122668,3122709,3122136,3122091,3122091,3122668,3122709,3122136,3122099,3122099,3122668,3122709,3122136,3122099,3122099,3122668,3122709,3122136,3122099,3122099,3122668,3122709,3122136,3122107,3122107,3122668,3122709,3122136,3122107,3122107,3122668,3122709,3122136,3122107,3122107,3122668,3122709,3122136,3122115,3122115,3122668,3122136,3122115,3122115,3122668,3122136,3122115,3122115,3122668,3122136,3122673,3122668,3122136,3122673,3122668,3122136,3122673,3122136,3122673,3122136,3122673,3122136,3122673,3122144,3122673,3122144,3122673,3122144,3122673,3122144,3122673,3122144,3122673,3122144,3122673,3122144,3122673,3122144,3122673,3122144,3122673,3122144,3122144,3122144,3122144,3122144,3122144,3122144,3122144</t>
+          <t>5000110,5000110,5000111,5000112,5000113,5000115,5000110,5000110,5000111,5000112,5000113,5000115,5000110,5000110,5000111,5000112,5000113,5000115,5000110,5000110,5000111,5000112,5000113,5000115,5000110,5000110,5000111,5000112,5000113,5000115,5000110,5000110,5000111,5000112,5000113,5000115,5000110,5000110,5000111,5000112,5000113,5000115,5000110,5000110,5000111,5000112,5000113,5000115,5000110,5000110,5000111,5000112,5000113,5000115,5000110,5000110,5000111,5000112,5000113,5000110,5000110,5000111,5000112,5000110,5000110,5000111,5000112,5000110,5000110,5000111,5000112,5000110,5000110,5000111,5000112,5000110,5000110,5000111,5000110,5000110,5000111,5000110,5000110,5000111,5000110,5000110,5000111,5000110,5000110,5000111,5000110,5000110,5000111,5000110,5000111,5000111,5000111,5000110,5000110,5000111,5000112,5000113,5000115,5000110,5000110,5000111,5000112,5000113,5000115,5000110,5000110,5000111,5000112,5000113,5000115,5000110,5000110,5000111,5000112,5000113,5000115,5000110,5000110,5000111,5000112,5000113,5000115,5000110,5000110,5000111,5000112,5000113,5000115,5000110,5000110,5000111,5000112,5000113,5000115,5000110,5000110,5000111,5000112,5000113,5000115,5000110,5000110,5000111,5000112,5000113,5000115,5000110,5000110,5000111,5000112,5000113,5000110,5000110,5000111,5000112,5000110,5000110,5000111,5000112,5000110,5000110,5000111,5000112,5000110,5000110,5000111,5000112,5000110,5000110,5000111,5000110,5000110,5000111,5000110,5000110,5000111,5000110,5000110,5000111,5000110,5000110,5000111,5000110,5000110,5000111,5000110,5000111,5000111,5000111</t>
         </is>
       </c>
       <c r="D15" s="3" t="n">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="F15" s="0" t="inlineStr">
         <is>
-          <t>L1 W12/25; N=97; EHP=4088.288713; air:11x3,air:12x3,air:13x3,air:14x3,normal:17x18,normal:18x17,medium:83x14,swarm:84x27,heavy:88x9 | manual: hp x1.5 (air x2.0), air x2 from W5</t>
+          <t>L1 W12/25; N=194; EHP=12591.646760; variants:5 (counts doubled, hp x1.5/x2.0) | wavebuff-20261029</t>
         </is>
       </c>
     </row>
@@ -1410,7 +1410,7 @@
       </c>
       <c r="C16" s="0" t="inlineStr">
         <is>
-          <t>3124136,3124019,3124019,3124668,3124709,3124136,3124019,3124019,3124668,3124709,3124136,3124019,3124019,3124668,3124709,3124136,3124091,3124091,3124668,3124709,3124136,3124091,3124091,3124668,3124709,3124136,3124099,3124099,3124668,3124709,3124136,3124099,3124099,3124668,3124709,3124136,3124099,3124099,3124668,3124709,3124136,3124107,3124107,3124668,3124709,3124136,3124107,3124107,3124668,3124709,3124136,3124115,3124115,3124668,3124136,3124115,3124115,3124668,3124136,3124673,3124668,3124136,3124673,3124668,3124136,3124673,3124668,3124136,3124673,3124136,3124673,3124136,3124673,3124136,3124673,3124144,3124673,3124144,3124673,3124144,3124673,3124144,3124673,3124144,3124673,3124144,3124673,3124144,3124673,3124144,3124673,3124144,3124673,3124144,3124144,3124144,3124144,3124144,3124144,3124144,3124144,3124144,3124144</t>
+          <t>5000120,5000120,5000121,5000122,5000123,5000125,5000120,5000120,5000121,5000122,5000123,5000125,5000120,5000120,5000121,5000122,5000123,5000125,5000120,5000120,5000121,5000122,5000123,5000125,5000120,5000120,5000121,5000122,5000123,5000125,5000120,5000120,5000121,5000122,5000123,5000125,5000120,5000120,5000121,5000122,5000123,5000125,5000120,5000120,5000121,5000122,5000123,5000125,5000120,5000120,5000121,5000122,5000123,5000125,5000120,5000120,5000121,5000122,5000123,5000125,5000120,5000120,5000121,5000122,5000123,5000120,5000120,5000121,5000122,5000120,5000120,5000121,5000122,5000120,5000120,5000121,5000122,5000120,5000120,5000121,5000120,5000120,5000121,5000120,5000120,5000121,5000120,5000120,5000121,5000120,5000120,5000121,5000120,5000120,5000121,5000120,5000120,5000121,5000120,5000121,5000121,5000121,5000121,5000120,5000120,5000121,5000122,5000123,5000125,5000120,5000120,5000121,5000122,5000123,5000125,5000120,5000120,5000121,5000122,5000123,5000125,5000120,5000120,5000121,5000122,5000123,5000125,5000120,5000120,5000121,5000122,5000123,5000125,5000120,5000120,5000121,5000122,5000123,5000125,5000120,5000120,5000121,5000122,5000123,5000125,5000120,5000120,5000121,5000122,5000123,5000125,5000120,5000120,5000121,5000122,5000123,5000125,5000120,5000120,5000121,5000122,5000123,5000125,5000120,5000120,5000121,5000122,5000123,5000120,5000120,5000121,5000122,5000120,5000120,5000121,5000122,5000120,5000120,5000121,5000122,5000120,5000120,5000121,5000120,5000120,5000121,5000120,5000120,5000121,5000120,5000120,5000121,5000120,5000120,5000121,5000120,5000120,5000121,5000120,5000120,5000121,5000120,5000121,5000121,5000121,5000121</t>
         </is>
       </c>
       <c r="D16" s="3" t="n">
@@ -1421,7 +1421,7 @@
       </c>
       <c r="F16" s="0" t="inlineStr">
         <is>
-          <t>L1 W13/25; N=103; EHP=4984.821364; air:2x3,air:11x2,air:12x3,air:13x2,air:14x2,normal:17x19,normal:18x19,medium:83x15,swarm:84x28,heavy:88x10 | manual: hp x1.5 (air x2.0), air x2 from W5</t>
+          <t>L1 W13/25; N=206; EHP=15372.591629; variants:5 (counts doubled, hp x1.5/x2.0) | wavebuff-20261029</t>
         </is>
       </c>
     </row>
@@ -1431,7 +1431,7 @@
       </c>
       <c r="C17" s="0" t="inlineStr">
         <is>
-          <t>3126136,3126019,3126019,3126668,3126709,3126136,3126019,3126019,3126668,3126709,3126136,3126019,3126019,3126668,3126709,3126136,3126091,3126091,3126668,3126709,3126136,3126091,3126091,3126668,3126709,3126136,3126091,3126091,3126668,3126709,3126136,3126099,3126099,3126668,3126709,3126136,3126099,3126099,3126668,3126709,3126136,3126107,3126107,3126668,3126709,3126136,3126107,3126107,3126668,3126709,3126136,3126107,3126107,3126668,3126136,3126115,3126115,3126668,3126136,3126115,3126115,3126668,3126136,3126673,3126668,3126136,3126673,3126668,3126136,3126673,3126668,3126136,3126673,3126136,3126673,3126136,3126673,3126136,3126673,3126144,3126673,3126144,3126673,3126144,3126673,3126144,3126673,3126144,3126673,3126144,3126673,3126144,3126673,3126144,3126673,3126144,3126673,3126144,3126673,3126144,3126144,3126144,3126144,3126144,3126144,3126144,3126144,3126144,3126144</t>
+          <t>5000130,5000130,5000131,5000132,5000133,5000135,5000130,5000130,5000131,5000132,5000133,5000135,5000130,5000130,5000131,5000132,5000133,5000135,5000130,5000130,5000131,5000132,5000133,5000135,5000130,5000130,5000131,5000132,5000133,5000135,5000130,5000130,5000131,5000132,5000133,5000135,5000130,5000130,5000131,5000132,5000133,5000135,5000130,5000130,5000131,5000132,5000133,5000135,5000130,5000130,5000131,5000132,5000133,5000135,5000130,5000130,5000131,5000132,5000133,5000135,5000130,5000130,5000131,5000132,5000133,5000135,5000130,5000130,5000131,5000132,5000130,5000130,5000131,5000132,5000130,5000130,5000131,5000132,5000130,5000130,5000131,5000132,5000130,5000130,5000131,5000130,5000130,5000131,5000130,5000130,5000131,5000130,5000130,5000131,5000130,5000130,5000131,5000130,5000130,5000131,5000130,5000130,5000131,5000130,5000130,5000131,5000131,5000131,5000131,5000130,5000130,5000131,5000132,5000133,5000135,5000130,5000130,5000131,5000132,5000133,5000135,5000130,5000130,5000131,5000132,5000133,5000135,5000130,5000130,5000131,5000132,5000133,5000135,5000130,5000130,5000131,5000132,5000133,5000135,5000130,5000130,5000131,5000132,5000133,5000135,5000130,5000130,5000131,5000132,5000133,5000135,5000130,5000130,5000131,5000132,5000133,5000135,5000130,5000130,5000131,5000132,5000133,5000135,5000130,5000130,5000131,5000132,5000133,5000135,5000130,5000130,5000131,5000132,5000133,5000135,5000130,5000130,5000131,5000132,5000130,5000130,5000131,5000132,5000130,5000130,5000131,5000132,5000130,5000130,5000131,5000132,5000130,5000130,5000131,5000130,5000130,5000131,5000130,5000130,5000131,5000130,5000130,5000131,5000130,5000130,5000131,5000130,5000130,5000131,5000130,5000130,5000131,5000130,5000130,5000131,5000131,5000131,5000131</t>
         </is>
       </c>
       <c r="D17" s="3" t="n">
@@ -1442,7 +1442,7 @@
       </c>
       <c r="F17" s="0" t="inlineStr">
         <is>
-          <t>L1 W14/25; N=109; EHP=6020.503596; air:2x3,air:11x3,air:12x2,air:13x3,air:14x2,normal:17x20,normal:18x20,medium:83x16,swarm:84x30,heavy:88x10 | manual: hp x1.5 (air x2.0), air x2 from W5</t>
+          <t>L1 W14/25; N=218; EHP=18592.495024; variants:5 (counts doubled, hp x1.5/x2.0) | wavebuff-20261029</t>
         </is>
       </c>
     </row>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="C18" s="0" t="inlineStr">
         <is>
-          <t>3128136,3128019,3128019,3128668,3128709,3128136,3128019,3128019,3128668,3128709,3128136,3128091,3128091,3128668,3128709,3128136,3128091,3128091,3128668,3128709,3128136,3128091,3128091,3128668,3128709,3128136,3128099,3128099,3128668,3128709,3128136,3128099,3128099,3128668,3128709,3128136,3128099,3128099,3128668,3128709,3128136,3128107,3128107,3128668,3128709,3128136,3128107,3128107,3128988,3128709,3128136,3128107,3128107,3128988,3128709,3128136,3128115,3128115,3128988,3128136,3128115,3128115,3128988,3128136,3128115,3128115,3128988,3128136,3128673,3128988,3128136,3128673,3128988,3128136,3128673,3128988,3128136,3128673,3128136,3128673,3128136,3128673,3128144,3128673,3128144,3128673,3128144,3128673,3128144,3128673,3128144,3128673,3128144,3128673,3128144,3128673,3128144,3128673,3128144,3128673,3128144,3128673,3128144,3128673,3128144,3128673,3128144,3128144,3128144,3128144,3128144,3128144,3128144,3128144,3128144</t>
+          <t>5000140,5000140,5000141,5000142,5000143,5000145,5000140,5000140,5000141,5000142,5000143,5000145,5000140,5000140,5000141,5000142,5000143,5000145,5000140,5000140,5000141,5000142,5000143,5000145,5000140,5000140,5000141,5000142,5000143,5000145,5000140,5000140,5000141,5000142,5000143,5000145,5000140,5000140,5000141,5000142,5000143,5000145,5000140,5000140,5000141,5000142,5000143,5000145,5000140,5000140,5000141,5000142,5000143,5000145,5000140,5000140,5000141,5000142,5000143,5000145,5000140,5000140,5000141,5000142,5000143,5000145,5000140,5000140,5000141,5000142,5000143,5000145,5000140,5000140,5000141,5000142,5000140,5000140,5000141,5000142,5000140,5000140,5000141,5000142,5000140,5000140,5000141,5000142,5000140,5000140,5000141,5000140,5000140,5000141,5000140,5000140,5000141,5000140,5000140,5000141,5000140,5000140,5000141,5000140,5000140,5000141,5000140,5000140,5000141,5000140,5000140,5000141,5000141,5000141,5000141,5000140,5000140,5000141,5000142,5000143,5000145,5000140,5000140,5000141,5000142,5000143,5000145,5000140,5000140,5000141,5000142,5000143,5000145,5000140,5000140,5000141,5000142,5000143,5000145,5000140,5000140,5000141,5000142,5000143,5000145,5000140,5000140,5000141,5000142,5000143,5000145,5000140,5000140,5000141,5000142,5000143,5000145,5000140,5000140,5000141,5000142,5000143,5000145,5000140,5000140,5000141,5000142,5000143,5000145,5000140,5000140,5000141,5000142,5000143,5000145,5000140,5000140,5000141,5000142,5000143,5000145,5000140,5000140,5000141,5000142,5000143,5000145,5000140,5000140,5000141,5000142,5000140,5000140,5000141,5000142,5000140,5000140,5000141,5000142,5000140,5000140,5000141,5000142,5000140,5000140,5000141,5000140,5000140,5000141,5000140,5000140,5000141,5000140,5000140,5000141,5000140,5000140,5000141,5000140,5000140,5000141,5000140,5000140,5000141,5000140,5000140,5000141,5000141,5000141,5000141</t>
         </is>
       </c>
       <c r="D18" s="3" t="n">
@@ -1463,217 +1463,217 @@
       </c>
       <c r="F18" s="0" t="inlineStr">
         <is>
-          <t>L1 W15/25; N=115; EHP=10511.057165; air:2x2,air:11x3,air:12x3,air:13x3,air:14x3,normal:17x20,normal:18x21,medium:83x9,swarm:84x32,heavy:88x11,medium:123x8 | manual: hp x1.5 (air x2.0), air x2 from W5</t>
+          <t>L1 W15/25; N=230; EHP=32479.285768; variants:5 (counts doubled, hp x1.5/x2.0) | wavebuff-20261029</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="0" t="n">
-        <v>401</v>
+        <v>16</v>
       </c>
       <c r="C19" s="0" t="inlineStr">
         <is>
-          <t>10016742,10048470,10048470,10016744,10016746,10016742,10048470,10048470,10016744,10016746,10016742,10048470,10048470,10016744,10016746,10016742,10016740,10016740,10016744,10016746,10016742,10016740,10016740,10016744,10016746,10016742,10016740,10016740,10016744,10016746,10016742,10016740,10016740,10016744,10016746,10016742,10048471,10048471,10016744,10016746,10016742,10048471,10048471,10016744,10016746,10016742,10048471,10048471,10016744,10016746,10016742,10048471,10048471,10016744,10016746,10016742,10016741,10016741,10016747,10016746,10016742,10016741,10016741,10016747,10016746,10016742,10016741,10016741,10016747,10016746,10016742,10046035,10046035,10016747,10016746,10016742,10046035,10046035,10016747,10016742,10046035,10046035,10016747,10016742,10046035,10046035,10016747,10016742,10016745,10016747,10016742,10016745,10016747,10016742,10016745,10016747,10016742,10016745,10016747,10016742,10016745,10016742,10016745,10016742,10016745,10016742,10016745,10016742,10016745,10016743,10016745,10016743,10016745,10016743,10016745,10016743,10016745,10016743,10016745,10016743,10016745,10016743,10016745,10016743,10016745,10016743,10016745,10016743,10016745,10016743,10016745,10016743,10016745,10016743,10016745,10016743,10016745,10016743,10016745,10016743,10016743,10016743,10016743,10016743,10016743,10016743,10016743,10016743,10016743,10016743,10016743</t>
+          <t>5000150,5000150,5000151,5000152,5000153,5000155,5000150,5000150,5000151,5000152,5000153,5000155,5000150,5000150,5000151,5000152,5000153,5000155,5000150,5000150,5000151,5000152,5000153,5000155,5000150,5000150,5000151,5000152,5000153,5000155,5000150,5000150,5000151,5000152,5000153,5000155,5000150,5000150,5000151,5000152,5000153,5000155,5000150,5000150,5000151,5000152,5000153,5000155,5000150,5000150,5000151,5000152,5000153,5000155,5000150,5000150,5000151,5000152,5000153,5000155,5000150,5000150,5000151,5000152,5000153,5000155,5000150,5000150,5000151,5000152,5000153,5000155,5000150,5000150,5000151,5000152,5000155,5000150,5000150,5000151,5000152,5000150,5000150,5000151,5000152,5000150,5000150,5000151,5000152,5000150,5000150,5000151,5000152,5000150,5000150,5000151,5000150,5000150,5000151,5000150,5000150,5000151,5000150,5000150,5000151,5000150,5000150,5000151,5000150,5000150,5000151,5000150,5000150,5000151,5000150,5000150,5000151,5000151,5000151,5000151,5000151,5000150,5000150,5000151,5000152,5000153,5000155,5000150,5000150,5000151,5000152,5000153,5000155,5000150,5000150,5000151,5000152,5000153,5000155,5000150,5000150,5000151,5000152,5000153,5000155,5000150,5000150,5000151,5000152,5000153,5000155,5000150,5000150,5000151,5000152,5000153,5000155,5000150,5000150,5000151,5000152,5000153,5000155,5000150,5000150,5000151,5000152,5000153,5000155,5000150,5000150,5000151,5000152,5000153,5000155,5000150,5000150,5000151,5000152,5000153,5000155,5000150,5000150,5000151,5000152,5000153,5000155,5000150,5000150,5000151,5000152,5000153,5000155,5000150,5000150,5000151,5000152,5000155,5000150,5000150,5000151,5000152,5000150,5000150,5000151,5000152,5000150,5000150,5000151,5000152,5000150,5000150,5000151,5000152,5000150,5000150,5000151,5000150,5000150,5000151,5000150,5000150,5000151,5000150,5000150,5000151,5000150,5000150,5000151,5000150,5000150,5000151,5000150,5000150,5000151,5000150,5000150,5000151,5000151,5000151,5000151,5000151</t>
         </is>
       </c>
       <c r="D19" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E19" s="0" t="n">
-        <v>140</v>
+        <v>175</v>
       </c>
       <c r="F19" s="0" t="inlineStr">
         <is>
-          <t>L1 W21/25; N=151; EHP=23191.824781; air:2x3,air:11x4,air:12x4,air:13x3,air:14x4,normal:17x27,normal:18x27,medium:83x11,swarm:84x42,heavy:88x15,medium:123x11 | manual: hp x1.5 (air x2.0), air x2 from W5</t>
+          <t>L1 W16/25; N=242; EHP=33173.979189; variants:5 (counts doubled, hp x1.5/x2.0) | wavebuff-20261029</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="B20" s="0" t="n">
-        <v>402</v>
+        <v>17</v>
       </c>
       <c r="C20" s="0" t="inlineStr">
         <is>
-          <t>10016751,10048472,10048472,10016753,10016755,10016751,10048472,10048472,10016753,10016755,10016751,10048472,10048472,10016753,10016755,10016751,10048472,10048472,10016753,10016755,10016751,10016748,10016748,10016753,10016755,10016751,10016748,10016748,10016753,10016755,10016751,10016748,10016748,10016753,10016755,10016751,10048473,10048473,10016753,10016755,10016751,10048473,10048473,10016753,10016755,10016751,10048473,10048473,10016753,10016755,10016751,10048473,10048473,10016753,10016755,10016751,10016749,10016749,10016756,10016755,10016751,10016749,10016749,10016756,10016755,10016751,10016749,10016749,10016756,10016755,10016751,10016749,10016749,10016756,10016755,10016751,10016750,10016750,10016756,10016751,10016750,10016750,10016756,10016751,10016750,10016750,10016756,10016751,10016750,10016750,10016756,10016751,10016754,10016756,10016751,10016754,10016756,10016751,10016754,10016756,10016751,10016754,10016756,10016751,10016754,10016751,10016754,10016751,10016754,10016751,10016754,10016751,10016754,10016751,10016754,10016752,10016754,10016752,10016754,10016752,10016754,10016752,10016754,10016752,10016754,10016752,10016754,10016752,10016754,10016752,10016754,10016752,10016754,10016752,10016754,10016752,10016754,10016752,10016754,10016752,10016754,10016752,10016754,10016752,10016752,10016752,10016752,10016752,10016752,10016752,10016752,10016752,10016752,10016752,10016752,10016752,10016752</t>
+          <t>5000160,5000160,5000161,5000162,5000163,5000165,5000160,5000160,5000161,5000162,5000163,5000165,5000160,5000160,5000161,5000162,5000163,5000165,5000160,5000160,5000161,5000162,5000163,5000165,5000160,5000160,5000161,5000162,5000163,5000165,5000160,5000160,5000161,5000162,5000163,5000165,5000160,5000160,5000161,5000162,5000163,5000165,5000160,5000160,5000161,5000162,5000163,5000165,5000160,5000160,5000161,5000162,5000163,5000165,5000160,5000160,5000161,5000162,5000163,5000165,5000160,5000160,5000161,5000162,5000163,5000165,5000160,5000160,5000161,5000162,5000163,5000165,5000160,5000160,5000161,5000162,5000163,5000165,5000160,5000160,5000161,5000162,5000165,5000160,5000160,5000161,5000162,5000160,5000160,5000161,5000162,5000160,5000160,5000161,5000162,5000160,5000160,5000161,5000162,5000160,5000160,5000161,5000160,5000160,5000161,5000160,5000160,5000161,5000160,5000160,5000161,5000160,5000160,5000161,5000160,5000160,5000161,5000160,5000160,5000161,5000160,5000160,5000161,5000161,5000161,5000161,5000161,5000160,5000160,5000161,5000162,5000163,5000165,5000160,5000160,5000161,5000162,5000163,5000165,5000160,5000160,5000161,5000162,5000163,5000165,5000160,5000160,5000161,5000162,5000163,5000165,5000160,5000160,5000161,5000162,5000163,5000165,5000160,5000160,5000161,5000162,5000163,5000165,5000160,5000160,5000161,5000162,5000163,5000165,5000160,5000160,5000161,5000162,5000163,5000165,5000160,5000160,5000161,5000162,5000163,5000165,5000160,5000160,5000161,5000162,5000163,5000165,5000160,5000160,5000161,5000162,5000163,5000165,5000160,5000160,5000161,5000162,5000163,5000165,5000160,5000160,5000161,5000162,5000163,5000165,5000160,5000160,5000161,5000162,5000165,5000160,5000160,5000161,5000162,5000160,5000160,5000161,5000162,5000160,5000160,5000161,5000162,5000160,5000160,5000161,5000162,5000160,5000160,5000161,5000160,5000160,5000161,5000160,5000160,5000161,5000160,5000160,5000161,5000160,5000160,5000161,5000160,5000160,5000161,5000160,5000160,5000161,5000160,5000160,5000161,5000161,5000161,5000161,5000161</t>
         </is>
       </c>
       <c r="D20" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E20" s="0" t="n">
-        <v>133</v>
+        <v>168</v>
       </c>
       <c r="F20" s="0" t="inlineStr">
         <is>
-          <t>L1 W22/25; N=157; EHP=23660.892210; air:2x4,air:11x3,air:12x4,air:13x4,air:14x4,normal:17x29,normal:18x28,medium:83x11,swarm:84x43,heavy:88x15,medium:123x12 | manual: hp x1.5 (air x2.0), air x2 from W5</t>
+          <t>L1 W17/25; N=254; EHP=33840.828765; variants:5 (counts doubled, hp x1.5/x2.0) | wavebuff-20261029</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="B21" s="0" t="n">
-        <v>403</v>
+        <v>18</v>
       </c>
       <c r="C21" s="0" t="inlineStr">
         <is>
-          <t>10016760,10048474,10048474,10016762,10016764,10016760,10048474,10048474,10016762,10016764,10016760,10048474,10048474,10016762,10016764,10016760,10048474,10048474,10016762,10016764,10016760,10016757,10016757,10016762,10016764,10016760,10016757,10016757,10016762,10016764,10016760,10016757,10016757,10016762,10016764,10016760,10016757,10016757,10016762,10016764,10016760,10048475,10048475,10016762,10016764,10016760,10048475,10048475,10016762,10016764,10016760,10048475,10048475,10016762,10016764,10016760,10048475,10048475,10016762,10016764,10016760,10016758,10016758,10016765,10016764,10016760,10016758,10016758,10016765,10016764,10016760,10016758,10016758,10016765,10016764,10016760,10016758,10016758,10016765,10016764,10016760,10016759,10016759,10016765,10016760,10016759,10016759,10016765,10016760,10016759,10016759,10016765,10016760,10016759,10016759,10016765,10016760,10016763,10016765,10016760,10016763,10016765,10016760,10016763,10016765,10016760,10016763,10016765,10016760,10016763,10016760,10016763,10016760,10016763,10016760,10016763,10016760,10016763,10016761,10016763,10016761,10016763,10016761,10016763,10016761,10016763,10016761,10016763,10016761,10016763,10016761,10016763,10016761,10016763,10016761,10016763,10016761,10016763,10016761,10016763,10016761,10016763,10016761,10016763,10016761,10016763,10016761,10016763,10016761,10016763,10016761,10016761,10016761,10016761,10016761,10016761,10016761,10016761,10016761,10016761,10016761,10016761,10016761</t>
+          <t>5000170,5000170,5000171,5000172,5000173,5000175,5000170,5000170,5000171,5000172,5000173,5000175,5000170,5000170,5000171,5000172,5000173,5000175,5000170,5000170,5000171,5000172,5000173,5000175,5000170,5000170,5000171,5000172,5000173,5000175,5000170,5000170,5000171,5000172,5000173,5000175,5000170,5000170,5000171,5000172,5000173,5000175,5000170,5000170,5000171,5000172,5000173,5000175,5000170,5000170,5000171,5000172,5000173,5000175,5000170,5000170,5000171,5000172,5000173,5000175,5000170,5000170,5000171,5000172,5000173,5000175,5000170,5000170,5000171,5000172,5000173,5000175,5000170,5000170,5000171,5000172,5000173,5000175,5000170,5000170,5000171,5000172,5000173,5000175,5000170,5000170,5000171,5000172,5000175,5000170,5000170,5000171,5000172,5000170,5000170,5000171,5000172,5000170,5000170,5000171,5000172,5000170,5000170,5000171,5000170,5000170,5000171,5000170,5000170,5000171,5000170,5000170,5000171,5000170,5000170,5000171,5000170,5000170,5000171,5000170,5000170,5000171,5000170,5000170,5000171,5000170,5000170,5000171,5000170,5000171,5000171,5000171,5000171,5000170,5000170,5000171,5000172,5000173,5000175,5000170,5000170,5000171,5000172,5000173,5000175,5000170,5000170,5000171,5000172,5000173,5000175,5000170,5000170,5000171,5000172,5000173,5000175,5000170,5000170,5000171,5000172,5000173,5000175,5000170,5000170,5000171,5000172,5000173,5000175,5000170,5000170,5000171,5000172,5000173,5000175,5000170,5000170,5000171,5000172,5000173,5000175,5000170,5000170,5000171,5000172,5000173,5000175,5000170,5000170,5000171,5000172,5000173,5000175,5000170,5000170,5000171,5000172,5000173,5000175,5000170,5000170,5000171,5000172,5000173,5000175,5000170,5000170,5000171,5000172,5000173,5000175,5000170,5000170,5000171,5000172,5000173,5000175,5000170,5000170,5000171,5000172,5000175,5000170,5000170,5000171,5000172,5000170,5000170,5000171,5000172,5000170,5000170,5000171,5000172,5000170,5000170,5000171,5000170,5000170,5000171,5000170,5000170,5000171,5000170,5000170,5000171,5000170,5000170,5000171,5000170,5000170,5000171,5000170,5000170,5000171,5000170,5000170,5000171,5000170,5000170,5000171,5000170,5000171,5000171,5000171,5000171</t>
         </is>
       </c>
       <c r="D21" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E21" s="0" t="n">
-        <v>128</v>
+        <v>161</v>
       </c>
       <c r="F21" s="0" t="inlineStr">
         <is>
-          <t>L1 W23/25; N=163; EHP=24137.544993; air:2x4,air:11x4,air:12x4,air:13x4,air:14x4,normal:17x29,normal:18x29,medium:83x12,swarm:84x45,heavy:88x16,medium:123x12 | manual: hp x1.5 (air x2.0), air x2 from W5</t>
+          <t>L1 W18/25; N=266; EHP=36200.289405; variants:5 (counts doubled, hp x1.5/x2.0) | wavebuff-20261029</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="B22" s="0" t="n">
-        <v>404</v>
+        <v>19</v>
       </c>
       <c r="C22" s="0" t="inlineStr">
         <is>
-          <t>10016769,10048476,10048476,10016771,10016773,10016769,10048476,10048476,10016771,10016773,10016769,10048476,10048476,10016771,10016773,10016769,10048476,10048476,10016771,10016773,10016769,10016766,10016766,10016771,10016773,10016769,10016766,10016766,10016771,10016773,10016769,10016766,10016766,10016771,10016773,10016769,10016766,10016766,10016771,10016773,10016769,10048477,10048477,10016771,10016773,10016769,10048477,10048477,10016771,10016773,10016769,10048477,10048477,10016771,10016773,10016769,10048477,10048477,10016771,10016773,10016769,10016767,10016767,10016774,10016773,10016769,10016767,10016767,10016774,10016773,10016769,10016767,10016767,10016774,10016773,10016769,10016767,10016767,10016774,10016773,10016769,10016768,10016768,10016774,10016769,10016768,10016768,10016774,10016769,10016768,10016768,10016774,10016769,10016768,10016768,10016774,10016769,10016772,10016774,10016769,10016772,10016774,10016769,10016772,10016774,10016769,10016772,10016774,10016769,10016772,10016774,10016769,10016772,10016769,10016772,10016769,10016772,10016769,10016772,10016769,10016772,10016769,10016772,10016770,10016772,10016770,10016772,10016770,10016772,10016770,10016772,10016770,10016772,10016770,10016772,10016770,10016772,10016770,10016772,10016770,10016772,10016770,10016772,10016770,10016772,10016770,10016772,10016770,10016772,10016770,10016772,10016770,10016772,10016770,10016772,10016770,10016770,10016770,10016770,10016770,10016770,10016770,10016770,10016770,10016770,10016770,10016770,10016770,10016770</t>
+          <t>5000180,5000180,5000181,5000182,5000183,5000185,5000180,5000180,5000181,5000182,5000183,5000185,5000180,5000180,5000181,5000182,5000183,5000185,5000180,5000180,5000181,5000182,5000183,5000185,5000180,5000180,5000181,5000182,5000183,5000185,5000180,5000180,5000181,5000182,5000183,5000185,5000180,5000180,5000181,5000182,5000183,5000185,5000180,5000180,5000181,5000182,5000183,5000185,5000180,5000180,5000181,5000182,5000183,5000185,5000180,5000180,5000181,5000182,5000183,5000185,5000180,5000180,5000181,5000182,5000183,5000185,5000180,5000180,5000181,5000182,5000183,5000185,5000180,5000180,5000181,5000182,5000183,5000185,5000180,5000180,5000181,5000182,5000183,5000185,5000180,5000180,5000181,5000182,5000185,5000180,5000180,5000181,5000182,5000185,5000180,5000180,5000181,5000182,5000180,5000180,5000181,5000182,5000180,5000180,5000181,5000182,5000180,5000180,5000181,5000180,5000180,5000181,5000180,5000180,5000181,5000180,5000180,5000181,5000180,5000180,5000181,5000180,5000180,5000181,5000180,5000180,5000181,5000180,5000180,5000181,5000180,5000180,5000181,5000180,5000181,5000181,5000181,5000181,5000181,5000180,5000180,5000181,5000182,5000183,5000185,5000180,5000180,5000181,5000182,5000183,5000185,5000180,5000180,5000181,5000182,5000183,5000185,5000180,5000180,5000181,5000182,5000183,5000185,5000180,5000180,5000181,5000182,5000183,5000185,5000180,5000180,5000181,5000182,5000183,5000185,5000180,5000180,5000181,5000182,5000183,5000185,5000180,5000180,5000181,5000182,5000183,5000185,5000180,5000180,5000181,5000182,5000183,5000185,5000180,5000180,5000181,5000182,5000183,5000185,5000180,5000180,5000181,5000182,5000183,5000185,5000180,5000180,5000181,5000182,5000183,5000185,5000180,5000180,5000181,5000182,5000183,5000185,5000180,5000180,5000181,5000182,5000183,5000185,5000180,5000180,5000181,5000182,5000185,5000180,5000180,5000181,5000182,5000185,5000180,5000180,5000181,5000182,5000180,5000180,5000181,5000182,5000180,5000180,5000181,5000182,5000180,5000180,5000181,5000180,5000180,5000181,5000180,5000180,5000181,5000180,5000180,5000181,5000180,5000180,5000181,5000180,5000180,5000181,5000180,5000180,5000181,5000180,5000180,5000181,5000180,5000180,5000181,5000180,5000181,5000181,5000181,5000181,5000181</t>
         </is>
       </c>
       <c r="D22" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E22" s="0" t="n">
-        <v>128</v>
+        <v>154</v>
       </c>
       <c r="F22" s="0" t="inlineStr">
         <is>
-          <t>L1 W24/25; N=169; EHP=25837.572034; air:2x4,air:11x4,air:12x4,air:13x4,air:14x4,normal:17x31,normal:18x30,medium:83x12,swarm:84x47,heavy:88x16,medium:123x13 | manual: hp x1.5 (air x2.0), air x2 from W5</t>
+          <t>L1 W19/25; N=278; EHP=41973.372707; variants:5 (counts doubled, hp x1.5/x2.0) | wavebuff-20261029</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="B23" s="0" t="n">
-        <v>405</v>
+        <v>20</v>
       </c>
       <c r="C23" s="0" t="inlineStr">
         <is>
-          <t>10016778,10048478,10048478,10016780,10016782,10016783,10016778,10048478,10048478,10016780,10016782,10016778,10048478,10048478,10016780,10016782,10016778,10048478,10048478,10016780,10016782,10016778,10016775,10016775,10016780,10016782,10016778,10016775,10016775,10016780,10016782,10016778,10016775,10016775,10016780,10016782,10016778,10016775,10016775,10016780,10016782,10016778,10048479,10048479,10016780,10016782,10016778,10048479,10048479,10016780,10016782,10016778,10048479,10048479,10016780,10016782,10016778,10048479,10048479,10016780,10016782,10016778,10016776,10016776,10016780,10016782,10016778,10016776,10016776,10016784,10016782,10016778,10016776,10016776,10016784,10016782,10016778,10016776,10016776,10016784,10016782,10016778,10016776,10016776,10016784,10016782,10016778,10016777,10016777,10016784,10016778,10016777,10016777,10016784,10016778,10016777,10016777,10016784,10016778,10016777,10016777,10016784,10016778,10016781,10016784,10016778,10016781,10016784,10016778,10016781,10016784,10016778,10016781,10016784,10016778,10016781,10016784,10016778,10016781,10016778,10016781,10016778,10016781,10016778,10016781,10016779,10016781,10016779,10016781,10016779,10016781,10016779,10016781,10016779,10016781,10016779,10016781,10016779,10016781,10016779,10016781,10016779,10016781,10016779,10016781,10016779,10016781,10016779,10016781,10016779,10016781,10016779,10016781,10016779,10016781,10016779,10016781,10016779,10016781,10016779,10016781,10016779,10016781,10016779,10016779,10016779,10016779,10016779,10016779,10016779,10016779,10016779,10016779,10016779,10016779</t>
+          <t>5000190,5000190,5000191,5000192,5000193,5000195,5000190,5000190,5000191,5000192,5000193,5000195,5000190,5000190,5000191,5000192,5000193,5000195,5000190,5000190,5000191,5000192,5000193,5000195,5000190,5000190,5000191,5000192,5000193,5000195,5000190,5000190,5000191,5000192,5000193,5000195,5000190,5000190,5000191,5000192,5000193,5000195,5000190,5000190,5000191,5000192,5000193,5000195,5000190,5000190,5000191,5000192,5000193,5000195,5000190,5000190,5000191,5000192,5000193,5000195,5000190,5000190,5000191,5000192,5000193,5000195,5000190,5000190,5000191,5000192,5000193,5000195,5000190,5000190,5000191,5000192,5000193,5000195,5000190,5000190,5000191,5000192,5000193,5000195,5000190,5000190,5000191,5000192,5000193,5000195,5000190,5000190,5000191,5000192,5000195,5000190,5000190,5000191,5000192,5000195,5000190,5000190,5000191,5000192,5000190,5000190,5000191,5000192,5000190,5000190,5000191,5000192,5000190,5000190,5000191,5000190,5000190,5000191,5000190,5000190,5000191,5000190,5000190,5000191,5000190,5000190,5000191,5000190,5000190,5000191,5000190,5000190,5000191,5000190,5000190,5000191,5000190,5000190,5000191,5000190,5000191,5000191,5000191,5000191,5000191,5000190,5000190,5000191,5000192,5000193,5000195,5000190,5000190,5000191,5000192,5000193,5000195,5000190,5000190,5000191,5000192,5000193,5000195,5000190,5000190,5000191,5000192,5000193,5000195,5000190,5000190,5000191,5000192,5000193,5000195,5000190,5000190,5000191,5000192,5000193,5000195,5000190,5000190,5000191,5000192,5000193,5000195,5000190,5000190,5000191,5000192,5000193,5000195,5000190,5000190,5000191,5000192,5000193,5000195,5000190,5000190,5000191,5000192,5000193,5000195,5000190,5000190,5000191,5000192,5000193,5000195,5000190,5000190,5000191,5000192,5000193,5000195,5000190,5000190,5000191,5000192,5000193,5000195,5000190,5000190,5000191,5000192,5000193,5000195,5000190,5000190,5000191,5000192,5000193,5000195,5000190,5000190,5000191,5000192,5000195,5000190,5000190,5000191,5000192,5000195,5000190,5000190,5000191,5000192,5000190,5000190,5000191,5000192,5000190,5000190,5000191,5000192,5000190,5000190,5000191,5000190,5000190,5000191,5000190,5000190,5000191,5000190,5000190,5000191,5000190,5000190,5000191,5000190,5000190,5000191,5000190,5000190,5000191,5000190,5000190,5000191,5000190,5000190,5000191,5000190,5000191,5000191,5000191,5000191,5000191</t>
         </is>
       </c>
       <c r="D23" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E23" s="0" t="n">
-        <v>128</v>
+        <v>147</v>
       </c>
       <c r="F23" s="0" t="inlineStr">
         <is>
-          <t>L1 W25/25; N=175; EHP=51578.680682; air:2x4,air:11x4,air:12x4,air:13x5,air:14x4,normal:17x30,normal:18x31,medium:83x13,swarm:84x49,heavy:88x17,elite:123x1,medium:123x13 | manual: hp x1.5 (air x2.0), air x2 from W5</t>
+          <t>L1 W20/25; N=290; EHP=70500.504819; variants:5 (counts doubled, hp x1.5/x2.0) | wavebuff-20261029</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="B24" s="0" t="n">
-        <v>16</v>
+        <v>401</v>
       </c>
       <c r="C24" s="0" t="inlineStr">
         <is>
-          <t>3130136,3130019,3130019,3130668,3130709,3130136,3130019,3130019,3130668,3130709,3130136,3130019,3130019,3130668,3130709,3130136,3130091,3130091,3130668,3130709,3130136,3130091,3130091,3130668,3130709,3130136,3130091,3130091,3130668,3130709,3130136,3130099,3130099,3130668,3130709,3130136,3130099,3130099,3130668,3130709,3130136,3130099,3130099,3130668,3130709,3130136,3130107,3130107,3130988,3130709,3130136,3130107,3130107,3130988,3130709,3130136,3130107,3130107,3130988,3130709,3130136,3130115,3130115,3130988,3130136,3130115,3130115,3130988,3130136,3130115,3130115,3130988,3130136,3130673,3130988,3130136,3130673,3130988,3130136,3130673,3130988,3130136,3130673,3130136,3130673,3130136,3130673,3130136,3130673,3130144,3130673,3130144,3130673,3130144,3130673,3130144,3130673,3130144,3130673,3130144,3130673,3130144,3130673,3130144,3130673,3130144,3130673,3130144,3130673,3130144,3130673,3130144,3130144,3130144,3130144,3130144,3130144,3130144,3130144,3130144,3130144</t>
+          <t>5000200,5000200,5000201,5000202,5000203,5000205,5000200,5000200,5000201,5000202,5000203,5000205,5000200,5000200,5000201,5000202,5000203,5000205,5000200,5000200,5000201,5000202,5000203,5000205,5000200,5000200,5000201,5000202,5000203,5000205,5000200,5000200,5000201,5000202,5000203,5000205,5000200,5000200,5000201,5000202,5000203,5000205,5000200,5000200,5000201,5000202,5000203,5000205,5000200,5000200,5000201,5000202,5000203,5000205,5000200,5000200,5000201,5000202,5000203,5000205,5000200,5000200,5000201,5000202,5000203,5000205,5000200,5000200,5000201,5000202,5000203,5000205,5000200,5000200,5000201,5000202,5000203,5000205,5000200,5000200,5000201,5000202,5000203,5000205,5000200,5000200,5000201,5000202,5000203,5000205,5000200,5000200,5000201,5000202,5000205,5000200,5000200,5000201,5000202,5000205,5000200,5000200,5000201,5000202,5000205,5000200,5000200,5000201,5000202,5000200,5000200,5000201,5000202,5000200,5000200,5000201,5000202,5000200,5000200,5000201,5000200,5000200,5000201,5000200,5000200,5000201,5000200,5000200,5000201,5000200,5000200,5000201,5000200,5000200,5000201,5000200,5000200,5000201,5000200,5000200,5000201,5000200,5000200,5000201,5000200,5000200,5000201,5000201,5000201,5000201,5000201,5000200,5000200,5000201,5000202,5000203,5000205,5000200,5000200,5000201,5000202,5000203,5000205,5000200,5000200,5000201,5000202,5000203,5000205,5000200,5000200,5000201,5000202,5000203,5000205,5000200,5000200,5000201,5000202,5000203,5000205,5000200,5000200,5000201,5000202,5000203,5000205,5000200,5000200,5000201,5000202,5000203,5000205,5000200,5000200,5000201,5000202,5000203,5000205,5000200,5000200,5000201,5000202,5000203,5000205,5000200,5000200,5000201,5000202,5000203,5000205,5000200,5000200,5000201,5000202,5000203,5000205,5000200,5000200,5000201,5000202,5000203,5000205,5000200,5000200,5000201,5000202,5000203,5000205,5000200,5000200,5000201,5000202,5000203,5000205,5000200,5000200,5000201,5000202,5000203,5000205,5000200,5000200,5000201,5000202,5000205,5000200,5000200,5000201,5000202,5000205,5000200,5000200,5000201,5000202,5000205,5000200,5000200,5000201,5000202,5000200,5000200,5000201,5000202,5000200,5000200,5000201,5000202,5000200,5000200,5000201,5000200,5000200,5000201,5000200,5000200,5000201,5000200,5000200,5000201,5000200,5000200,5000201,5000200,5000200,5000201,5000200,5000200,5000201,5000200,5000200,5000201,5000200,5000200,5000201,5000200,5000200,5000201,5000201,5000201,5000201,5000201</t>
         </is>
       </c>
       <c r="D24" s="0" t="n">
         <v>0</v>
       </c>
       <c r="E24" s="0" t="n">
-        <v>175</v>
+        <v>140</v>
       </c>
       <c r="F24" s="0" t="inlineStr">
         <is>
-          <t>L1 W16/25; N=121; EHP=10723.013261; air:2x3,air:11x3,air:12x3,air:13x3,air:14x3,normal:17x22,normal:18x21,medium:83x9,swarm:84x33,heavy:88x12,medium:123x9 | manual: hp x1.5 (air x2.0), air x2 from W5</t>
+          <t>L1 W21/25; N=302; EHP=71980.354364; variants:5 (counts doubled, hp x1.5/x2.0) | wavebuff-20261029</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="B25" s="0" t="n">
-        <v>17</v>
+        <v>402</v>
       </c>
       <c r="C25" s="0" t="inlineStr">
         <is>
-          <t>3132136,3132019,3132019,3132668,3132709,3132136,3132019,3132019,3132668,3132709,3132136,3132019,3132019,3132668,3132709,3132136,3132091,3132091,3132668,3132709,3132136,3132091,3132091,3132668,3132709,3132136,3132091,3132091,3132668,3132709,3132136,3132099,3132099,3132668,3132709,3132136,3132099,3132099,3132668,3132709,3132136,3132099,3132099,3132668,3132709,3132136,3132107,3132107,3132668,3132709,3132136,3132107,3132107,3132988,3132709,3132136,3132107,3132107,3132988,3132709,3132136,3132115,3132115,3132988,3132136,3132115,3132115,3132988,3132136,3132115,3132115,3132988,3132136,3132673,3132988,3132136,3132673,3132988,3132136,3132673,3132988,3132136,3132673,3132988,3132136,3132673,3132136,3132673,3132136,3132673,3132136,3132673,3132144,3132673,3132144,3132673,3132144,3132673,3132144,3132673,3132144,3132673,3132144,3132673,3132144,3132673,3132144,3132673,3132144,3132673,3132144,3132673,3132144,3132673,3132144,3132673,3132144,3132144,3132144,3132144,3132144,3132144,3132144,3132144,3132144,3132144,3132144</t>
+          <t>5000210,5000210,5000211,5000212,5000213,5000215,5000210,5000210,5000211,5000212,5000213,5000215,5000210,5000210,5000211,5000212,5000213,5000215,5000210,5000210,5000211,5000212,5000213,5000215,5000210,5000210,5000211,5000212,5000213,5000215,5000210,5000210,5000211,5000212,5000213,5000215,5000210,5000210,5000211,5000212,5000213,5000215,5000210,5000210,5000211,5000212,5000213,5000215,5000210,5000210,5000211,5000212,5000213,5000215,5000210,5000210,5000211,5000212,5000213,5000215,5000210,5000210,5000211,5000212,5000213,5000215,5000210,5000210,5000211,5000212,5000213,5000215,5000210,5000210,5000211,5000212,5000213,5000215,5000210,5000210,5000211,5000212,5000213,5000215,5000210,5000210,5000211,5000212,5000213,5000215,5000210,5000210,5000211,5000212,5000213,5000215,5000210,5000210,5000211,5000212,5000215,5000210,5000210,5000211,5000212,5000215,5000210,5000210,5000211,5000212,5000215,5000210,5000210,5000211,5000212,5000210,5000210,5000211,5000212,5000210,5000210,5000211,5000212,5000210,5000210,5000211,5000210,5000210,5000211,5000210,5000210,5000211,5000210,5000210,5000211,5000210,5000210,5000211,5000210,5000210,5000211,5000210,5000210,5000211,5000210,5000210,5000211,5000210,5000210,5000211,5000210,5000211,5000211,5000211,5000211,5000211,5000211,5000210,5000210,5000211,5000212,5000213,5000215,5000210,5000210,5000211,5000212,5000213,5000215,5000210,5000210,5000211,5000212,5000213,5000215,5000210,5000210,5000211,5000212,5000213,5000215,5000210,5000210,5000211,5000212,5000213,5000215,5000210,5000210,5000211,5000212,5000213,5000215,5000210,5000210,5000211,5000212,5000213,5000215,5000210,5000210,5000211,5000212,5000213,5000215,5000210,5000210,5000211,5000212,5000213,5000215,5000210,5000210,5000211,5000212,5000213,5000215,5000210,5000210,5000211,5000212,5000213,5000215,5000210,5000210,5000211,5000212,5000213,5000215,5000210,5000210,5000211,5000212,5000213,5000215,5000210,5000210,5000211,5000212,5000213,5000215,5000210,5000210,5000211,5000212,5000213,5000215,5000210,5000210,5000211,5000212,5000213,5000215,5000210,5000210,5000211,5000212,5000215,5000210,5000210,5000211,5000212,5000215,5000210,5000210,5000211,5000212,5000215,5000210,5000210,5000211,5000212,5000210,5000210,5000211,5000212,5000210,5000210,5000211,5000212,5000210,5000210,5000211,5000210,5000210,5000211,5000210,5000210,5000211,5000210,5000210,5000211,5000210,5000210,5000211,5000210,5000210,5000211,5000210,5000210,5000211,5000210,5000210,5000211,5000210,5000210,5000211,5000210,5000211,5000211,5000211,5000211,5000211,5000211</t>
         </is>
       </c>
       <c r="D25" s="0" t="n">
         <v>0</v>
       </c>
       <c r="E25" s="0" t="n">
-        <v>168</v>
+        <v>133</v>
       </c>
       <c r="F25" s="0" t="inlineStr">
         <is>
-          <t>L1 W17/25; N=127; EHP=10932.849478; air:2x3,air:11x3,air:12x3,air:13x3,air:14x3,normal:17x23,normal:18x23,medium:83x10,swarm:84x35,heavy:88x12,medium:123x9 | manual: hp x1.5 (air x2.0), air x2 from W5</t>
+          <t>L1 W22/25; N=314; EHP=73459.340624; variants:5 (counts doubled, hp x1.5/x2.0) | wavebuff-20261029</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="B26" s="0" t="n">
-        <v>18</v>
+        <v>403</v>
       </c>
       <c r="C26" s="0" t="inlineStr">
         <is>
-          <t>3134136,3134019,3134019,3134668,3134709,3134136,3134019,3134019,3134668,3134709,3134136,3134019,3134019,3134668,3134709,3134136,3134091,3134091,3134668,3134709,3134136,3134091,3134091,3134668,3134709,3134136,3134091,3134091,3134668,3134709,3134136,3134099,3134099,3134668,3134709,3134136,3134099,3134099,3134668,3134709,3134136,3134099,3134099,3134668,3134709,3134136,3134099,3134099,3134988,3134709,3134136,3134107,3134107,3134988,3134709,3134136,3134107,3134107,3134988,3134709,3134136,3134107,3134107,3134988,3134709,3134136,3134115,3134115,3134988,3134136,3134115,3134115,3134988,3134136,3134115,3134115,3134988,3134136,3134673,3134988,3134136,3134673,3134988,3134136,3134673,3134988,3134136,3134673,3134136,3134673,3134136,3134673,3134136,3134673,3134136,3134673,3134144,3134673,3134144,3134673,3134144,3134673,3134144,3134673,3134144,3134673,3134144,3134673,3134144,3134673,3134144,3134673,3134144,3134673,3134144,3134673,3134144,3134673,3134144,3134673,3134144,3134673,3134144,3134144,3134144,3134144,3134144,3134144,3134144,3134144,3134144,3134144,3134144</t>
+          <t>5000220,5000220,5000221,5000222,5000223,5000225,5000220,5000220,5000221,5000222,5000223,5000225,5000220,5000220,5000221,5000222,5000223,5000225,5000220,5000220,5000221,5000222,5000223,5000225,5000220,5000220,5000221,5000222,5000223,5000225,5000220,5000220,5000221,5000222,5000223,5000225,5000220,5000220,5000221,5000222,5000223,5000225,5000220,5000220,5000221,5000222,5000223,5000225,5000220,5000220,5000221,5000222,5000223,5000225,5000220,5000220,5000221,5000222,5000223,5000225,5000220,5000220,5000221,5000222,5000223,5000225,5000220,5000220,5000221,5000222,5000223,5000225,5000220,5000220,5000221,5000222,5000223,5000225,5000220,5000220,5000221,5000222,5000223,5000225,5000220,5000220,5000221,5000222,5000223,5000225,5000220,5000220,5000221,5000222,5000223,5000225,5000220,5000220,5000221,5000222,5000223,5000225,5000220,5000220,5000221,5000222,5000225,5000220,5000220,5000221,5000222,5000225,5000220,5000220,5000221,5000222,5000225,5000220,5000220,5000221,5000222,5000220,5000220,5000221,5000222,5000220,5000220,5000221,5000220,5000220,5000221,5000220,5000220,5000221,5000220,5000220,5000221,5000220,5000220,5000221,5000220,5000220,5000221,5000220,5000220,5000221,5000220,5000220,5000221,5000220,5000220,5000221,5000220,5000220,5000221,5000220,5000220,5000221,5000221,5000221,5000221,5000221,5000221,5000220,5000220,5000221,5000222,5000223,5000225,5000220,5000220,5000221,5000222,5000223,5000225,5000220,5000220,5000221,5000222,5000223,5000225,5000220,5000220,5000221,5000222,5000223,5000225,5000220,5000220,5000221,5000222,5000223,5000225,5000220,5000220,5000221,5000222,5000223,5000225,5000220,5000220,5000221,5000222,5000223,5000225,5000220,5000220,5000221,5000222,5000223,5000225,5000220,5000220,5000221,5000222,5000223,5000225,5000220,5000220,5000221,5000222,5000223,5000225,5000220,5000220,5000221,5000222,5000223,5000225,5000220,5000220,5000221,5000222,5000223,5000225,5000220,5000220,5000221,5000222,5000223,5000225,5000220,5000220,5000221,5000222,5000223,5000225,5000220,5000220,5000221,5000222,5000223,5000225,5000220,5000220,5000221,5000222,5000223,5000225,5000220,5000220,5000221,5000222,5000223,5000225,5000220,5000220,5000221,5000222,5000225,5000220,5000220,5000221,5000222,5000225,5000220,5000220,5000221,5000222,5000225,5000220,5000220,5000221,5000222,5000220,5000220,5000221,5000222,5000220,5000220,5000221,5000220,5000220,5000221,5000220,5000220,5000221,5000220,5000220,5000221,5000220,5000220,5000221,5000220,5000220,5000221,5000220,5000220,5000221,5000220,5000220,5000221,5000220,5000220,5000221,5000220,5000220,5000221,5000220,5000220,5000221,5000221,5000221,5000221,5000221,5000221</t>
         </is>
       </c>
       <c r="D26" s="0" t="n">
         <v>0</v>
       </c>
       <c r="E26" s="0" t="n">
-        <v>161</v>
+        <v>126</v>
       </c>
       <c r="F26" s="0" t="inlineStr">
         <is>
-          <t>L1 W18/25; N=133; EHP=11688.055949; air:2x3,air:11x3,air:12x4,air:13x3,air:14x3,normal:17x24,normal:18x24,medium:83x9,swarm:84x37,heavy:88x13,medium:123x10 | manual: hp x1.5 (air x2.0), air x2 from W5</t>
+          <t>L1 W23/25; N=326; EHP=74969.412363; variants:5 (counts doubled, hp x1.5/x2.0) | wavebuff-20261029</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="B27" s="0" t="n">
-        <v>19</v>
+        <v>404</v>
       </c>
       <c r="C27" s="0" t="inlineStr">
         <is>
-          <t>3136136,3136019,3136019,3136668,3136709,3136136,3136019,3136019,3136668,3136709,3136136,3136019,3136019,3136668,3136709,3136136,3136019,3136019,3136668,3136709,3136136,3136091,3136091,3136668,3136709,3136136,3136091,3136091,3136668,3136709,3136136,3136091,3136091,3136668,3136709,3136136,3136099,3136099,3136668,3136709,3136136,3136099,3136099,3136668,3136709,3136136,3136099,3136099,3136668,3136709,3136136,3136107,3136107,3136988,3136709,3136136,3136107,3136107,3136988,3136709,3136136,3136107,3136107,3136988,3136709,3136136,3136107,3136107,3136988,3136136,3136115,3136115,3136988,3136136,3136115,3136115,3136988,3136136,3136115,3136115,3136988,3136136,3136673,3136988,3136136,3136673,3136988,3136136,3136673,3136988,3136136,3136673,3136136,3136673,3136136,3136673,3136136,3136673,3136136,3136673,3136144,3136673,3136144,3136673,3136144,3136673,3136144,3136673,3136144,3136673,3136144,3136673,3136144,3136673,3136144,3136673,3136144,3136673,3136144,3136673,3136144,3136673,3136144,3136673,3136144,3136673,3136144,3136144,3136144,3136144,3136144,3136144,3136144,3136144,3136144,3136144,3136144,3136144,3136144</t>
+          <t>5000230,5000230,5000231,5000232,5000233,5000235,5000230,5000230,5000231,5000232,5000233,5000235,5000230,5000230,5000231,5000232,5000233,5000235,5000230,5000230,5000231,5000232,5000233,5000235,5000230,5000230,5000231,5000232,5000233,5000235,5000230,5000230,5000231,5000232,5000233,5000235,5000230,5000230,5000231,5000232,5000233,5000235,5000230,5000230,5000231,5000232,5000233,5000235,5000230,5000230,5000231,5000232,5000233,5000235,5000230,5000230,5000231,5000232,5000233,5000235,5000230,5000230,5000231,5000232,5000233,5000235,5000230,5000230,5000231,5000232,5000233,5000235,5000230,5000230,5000231,5000232,5000233,5000235,5000230,5000230,5000231,5000232,5000233,5000235,5000230,5000230,5000231,5000232,5000233,5000235,5000230,5000230,5000231,5000232,5000233,5000235,5000230,5000230,5000231,5000232,5000233,5000235,5000230,5000230,5000231,5000232,5000235,5000230,5000230,5000231,5000232,5000235,5000230,5000230,5000231,5000232,5000235,5000230,5000230,5000231,5000232,5000235,5000230,5000230,5000231,5000232,5000230,5000230,5000231,5000232,5000230,5000230,5000231,5000230,5000230,5000231,5000230,5000230,5000231,5000230,5000230,5000231,5000230,5000230,5000231,5000230,5000230,5000231,5000230,5000230,5000231,5000230,5000230,5000231,5000230,5000230,5000231,5000230,5000230,5000231,5000230,5000230,5000231,5000230,5000231,5000231,5000231,5000231,5000231,5000230,5000230,5000231,5000232,5000233,5000235,5000230,5000230,5000231,5000232,5000233,5000235,5000230,5000230,5000231,5000232,5000233,5000235,5000230,5000230,5000231,5000232,5000233,5000235,5000230,5000230,5000231,5000232,5000233,5000235,5000230,5000230,5000231,5000232,5000233,5000235,5000230,5000230,5000231,5000232,5000233,5000235,5000230,5000230,5000231,5000232,5000233,5000235,5000230,5000230,5000231,5000232,5000233,5000235,5000230,5000230,5000231,5000232,5000233,5000235,5000230,5000230,5000231,5000232,5000233,5000235,5000230,5000230,5000231,5000232,5000233,5000235,5000230,5000230,5000231,5000232,5000233,5000235,5000230,5000230,5000231,5000232,5000233,5000235,5000230,5000230,5000231,5000232,5000233,5000235,5000230,5000230,5000231,5000232,5000233,5000235,5000230,5000230,5000231,5000232,5000233,5000235,5000230,5000230,5000231,5000232,5000235,5000230,5000230,5000231,5000232,5000235,5000230,5000230,5000231,5000232,5000235,5000230,5000230,5000231,5000232,5000235,5000230,5000230,5000231,5000232,5000230,5000230,5000231,5000232,5000230,5000230,5000231,5000230,5000230,5000231,5000230,5000230,5000231,5000230,5000230,5000231,5000230,5000230,5000231,5000230,5000230,5000231,5000230,5000230,5000231,5000230,5000230,5000231,5000230,5000230,5000231,5000230,5000230,5000231,5000230,5000230,5000231,5000230,5000231,5000231,5000231,5000231,5000231</t>
         </is>
       </c>
       <c r="D27" s="0" t="n">
         <v>0</v>
       </c>
       <c r="E27" s="0" t="n">
-        <v>154</v>
+        <v>128</v>
       </c>
       <c r="F27" s="0" t="inlineStr">
         <is>
-          <t>L1 W19/25; N=139; EHP=13538.914400; air:2x4,air:11x3,air:12x3,air:13x4,air:14x3,normal:17x25,normal:18x26,medium:83x10,swarm:84x38,heavy:88x13,medium:123x10 | manual: hp x1.5 (air x2.0), air x2 from W5</t>
+          <t>L1 W24/25; N=338; EHP=80301.915228; variants:5 (counts doubled, hp x1.5/x2.0) | wavebuff-20261029</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="B28" s="0" t="n">
-        <v>20</v>
+        <v>405</v>
       </c>
       <c r="C28" s="0" t="inlineStr">
         <is>
-          <t>3138136,3138019,3138019,3138668,3138709,3138136,3138019,3138019,3138668,3138709,3138136,3138019,3138019,3138668,3138709,3138136,3138091,3138091,3138668,3138709,3138136,3138091,3138091,3138668,3138709,3138136,3138091,3138091,3138668,3138709,3138136,3138091,3138091,3138668,3138709,3138136,3138099,3138099,3138668,3138709,3138136,3138099,3138099,3138668,3138709,3138136,3138099,3138099,3138668,3138709,3138136,3138107,3138107,3138988,3138709,3138136,3138107,3138107,3138988,3138709,3138136,3138107,3138107,3138988,3138709,3138136,3138107,3138107,3138988,3138709,3138136,3138115,3138115,3138988,3138136,3138115,3138115,3138988,3138136,3138115,3138115,3138988,3138136,3138673,3138988,3138136,3138673,3138988,3138136,3138673,3138988,3138136,3138673,3138988,3138136,3138673,3138136,3138673,3138136,3138673,3138136,3138673,3138136,3138673,3138136,3138673,3138144,3138673,3138144,3138673,3138144,3138673,3138144,3138673,3138144,3138673,3138144,3138673,3138144,3138673,3138144,3138673,3138144,3138673,3138144,3138673,3138144,3138673,3138144,3138673,3138144,3138673,3138144,3138144,3138144,3138144,3138144,3138144,3138144,3138144,3138144,3138144,3138144,3138144,3138144</t>
+          <t>5000240,5000240,5000241,5000242,5000243,5000244,5000245,5000240,5000240,5000241,5000242,5000243,5000244,5000245,5000240,5000240,5000241,5000242,5000243,5000244,5000245,5000240,5000240,5000241,5000242,5000243,5000245,5000240,5000240,5000241,5000242,5000243,5000245,5000240,5000240,5000241,5000242,5000243,5000245,5000240,5000240,5000241,5000242,5000243,5000245,5000240,5000240,5000241,5000242,5000243,5000245,5000240,5000240,5000241,5000242,5000243,5000245,5000240,5000240,5000241,5000242,5000243,5000245,5000240,5000240,5000241,5000242,5000243,5000245,5000240,5000240,5000241,5000242,5000243,5000245,5000240,5000240,5000241,5000242,5000243,5000245,5000240,5000240,5000241,5000242,5000243,5000245,5000240,5000240,5000241,5000242,5000243,5000245,5000240,5000240,5000241,5000242,5000243,5000245,5000240,5000240,5000241,5000242,5000243,5000245,5000240,5000240,5000241,5000242,5000243,5000245,5000240,5000240,5000241,5000242,5000243,5000245,5000240,5000240,5000241,5000242,5000243,5000245,5000240,5000240,5000241,5000242,5000243,5000245,5000240,5000240,5000241,5000242,5000245,5000240,5000240,5000241,5000242,5000240,5000240,5000241,5000242,5000240,5000240,5000241,5000240,5000240,5000241,5000240,5000240,5000241,5000240,5000240,5000241,5000240,5000240,5000241,5000240,5000240,5000241,5000240,5000240,5000241,5000240,5000240,5000241,5000240,5000240,5000241,5000241,5000241,5000241,5000241,5000241,5000241,5000240,5000240,5000241,5000242,5000243,5000244,5000245,5000240,5000240,5000241,5000242,5000243,5000244,5000245,5000240,5000240,5000241,5000242,5000243,5000244,5000245,5000240,5000240,5000241,5000242,5000243,5000245,5000240,5000240,5000241,5000242,5000243,5000245,5000240,5000240,5000241,5000242,5000243,5000245,5000240,5000240,5000241,5000242,5000243,5000245,5000240,5000240,5000241,5000242,5000243,5000245,5000240,5000240,5000241,5000242,5000243,5000245,5000240,5000240,5000241,5000242,5000243,5000245,5000240,5000240,5000241,5000242,5000243,5000245,5000240,5000240,5000241,5000242,5000243,5000245,5000240,5000240,5000241,5000242,5000243,5000245,5000240,5000240,5000241,5000242,5000243,5000245,5000240,5000240,5000241,5000242,5000243,5000245,5000240,5000240,5000241,5000242,5000243,5000245,5000240,5000240,5000241,5000242,5000243,5000245,5000240,5000240,5000241,5000242,5000243,5000245,5000240,5000240,5000241,5000242,5000243,5000245,5000240,5000240,5000241,5000242,5000243,5000245,5000240,5000240,5000241,5000242,5000243,5000245,5000240,5000240,5000241,5000242,5000245,5000240,5000240,5000241,5000242,5000240,5000240,5000241,5000242,5000240,5000240,5000241,5000240,5000240,5000241,5000240,5000240,5000241,5000240,5000240,5000241,5000240,5000240,5000241,5000240,5000240,5000241,5000240,5000240,5000241,5000240,5000240,5000241,5000240,5000240,5000241,5000241,5000241,5000241,5000241,5000241,5000241</t>
         </is>
       </c>
       <c r="D28" s="0" t="n">
         <v>0</v>
       </c>
       <c r="E28" s="0" t="n">
-        <v>147</v>
+        <v>215</v>
       </c>
       <c r="F28" s="0" t="inlineStr">
         <is>
-          <t>L1 W20/25; N=145; EHP=22732.759536; air:2x3,air:11x4,air:12x3,air:13x4,air:14x3,normal:17x27,normal:18x26,medium:83x10,swarm:84x40,heavy:88x14,medium:123x11 | manual: hp x1.5 (air x2.0), air x2 from W5</t>
+          <t>L1 W25/25; N=350; EHP=159766.309670; variants:6 (counts doubled, hp x1.5/x2.0) | wavebuff-20261029</t>
         </is>
       </c>
     </row>

--- a/Luban/Config/Datas/Levels/L01/EnemyList.xlsx
+++ b/Luban/Config/Datas/Levels/L01/EnemyList.xlsx
@@ -1242,7 +1242,7 @@
       </c>
       <c r="C8" s="0" t="inlineStr">
         <is>
-          <t>5000040,5000040,5000041,5000042,5000045,5000040,5000040,5000041,5000042,5000045,5000040,5000040,5000041,5000042,5000040,5000040,5000041,5000042,5000040,5000040,5000041,5000042,5000040,5000040,5000041,5000042,5000040,5000040,5000041,5000042,5000040,5000040,5000041,5000042,5000040,5000040,5000041,5000042,5000040,5000040,5000041,5000042,5000040,5000040,5000041,5000040,5000040,5000041,5000040,5000040,5000041,5000040,5000040,5000041,5000041,5000040,5000040,5000041,5000042,5000045,5000040,5000040,5000041,5000042,5000045,5000040,5000040,5000041,5000042,5000040,5000040,5000041,5000042,5000040,5000040,5000041,5000042,5000040,5000040,5000041,5000042,5000040,5000040,5000041,5000042,5000040,5000040,5000041,5000042,5000040,5000040,5000041,5000042,5000040,5000040,5000041,5000042,5000040,5000040,5000041,5000040,5000040,5000041,5000040,5000040,5000041,5000040,5000040,5000041,5000041</t>
+          <t>5000040,5000040,5000041,5000042,5000045,5000040,5000040,5000041,5000042,5000045,5000040,5000040,5000041,5000042,5000040,5000040,5000041,5000042,5000040,5000040,5000040,5000041,5000042,5000040,5000040,5000041,5000042,5000040,5000040,5000041,5000042,5000040,5000040,5000041,5000042,5000040,5000040,5000041,5000040,5000042,5000040,5000040,5000041,5000042,5000040,5000040,5000041,5000040,5000040,5000041,5000040,5000040,5000041,5000040,5000040,5000041,5000041,5000040,5000040,5000040,5000041,5000042,5000045,5000040,5000040,5000041,5000042,5000045,5000040,5000040,5000041,5000042,5000040,5000040,5000041,5000042,5000040,5000040,5000040,5000041,5000042,5000040,5000040,5000041,5000042,5000040,5000040,5000041,5000042,5000040,5000040,5000041,5000042,5000040,5000040,5000041,5000040,5000042,5000040,5000040,5000041,5000042,5000040,5000040,5000041,5000040,5000040,5000041,5000040,5000040,5000041,5000040,5000040,5000041,5000041,5000040,5000040,5000040,5000041,5000042,5000045,5000040,5000040,5000041,5000042,5000045,5000040,5000040,5000041,5000042,5000040,5000040,5000041,5000042,5000040,5000041,5000040,5000041,5000042,5000040,5000040,5000041,5000042,5000040,5000040,5000041,5000042,5000040,5000040,5000041,5000042,5000040,5000040,5000041,5000041,5000042,5000040,5000040,5000041,5000042,5000040,5000040,5000041,5000040,5000040,5000041,5000040,5000040,5000041,5000040,5000040,5000041,5000041,5000041,5000040,5000040,5000041,5000042,5000045,5000040,5000040,5000041,5000042,5000045,5000040,5000040,5000041,5000042,5000040,5000040,5000041,5000042,5000040,5000042,5000040,5000041,5000042,5000040,5000040,5000041,5000042,5000040,5000040,5000041,5000042,5000040,5000040,5000041,5000042,5000040,5000040,5000041,5000042,5000042,5000040,5000040,5000041,5000042,5000040,5000040,5000041,5000040,5000040,5000041,5000040,5000040,5000041,5000040,5000040,5000041,5000041</t>
         </is>
       </c>
       <c r="D8" s="3" t="n">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="F8" s="0" t="inlineStr">
         <is>
-          <t>L1 W5/25; N=110; EHP=3213.174621; variants:4 (counts doubled, hp x1.5/x2.0) | wavebuff-20261029</t>
+          <t>L1 W5/25; N=231; EHP=10280.709008 | wavebuff2-20261029 (counts x2 again, hp stacked) | gold20-20261029: killGold=60 | ground5-20261030: ground +11 (5%)</t>
         </is>
       </c>
     </row>
@@ -1263,7 +1263,7 @@
       </c>
       <c r="C9" s="0" t="inlineStr">
         <is>
-          <t>5000050,5000050,5000051,5000052,5000055,5000050,5000050,5000051,5000052,5000055,5000050,5000050,5000051,5000052,5000055,5000050,5000050,5000051,5000052,5000050,5000050,5000051,5000052,5000050,5000050,5000051,5000052,5000050,5000050,5000051,5000052,5000050,5000050,5000051,5000052,5000050,5000050,5000051,5000052,5000050,5000050,5000051,5000052,5000050,5000050,5000051,5000052,5000050,5000050,5000051,5000050,5000050,5000051,5000050,5000050,5000051,5000050,5000050,5000051,5000051,5000051,5000050,5000050,5000051,5000052,5000055,5000050,5000050,5000051,5000052,5000055,5000050,5000050,5000051,5000052,5000055,5000050,5000050,5000051,5000052,5000050,5000050,5000051,5000052,5000050,5000050,5000051,5000052,5000050,5000050,5000051,5000052,5000050,5000050,5000051,5000052,5000050,5000050,5000051,5000052,5000050,5000050,5000051,5000052,5000050,5000050,5000051,5000052,5000050,5000050,5000051,5000050,5000050,5000051,5000050,5000050,5000051,5000050,5000050,5000051,5000051,5000051</t>
+          <t>5000050,5000050,5000051,5000052,5000055,5000050,5000050,5000051,5000052,5000055,5000050,5000050,5000051,5000052,5000055,5000050,5000050,5000051,5000052,5000050,5000050,5000050,5000051,5000052,5000050,5000050,5000051,5000052,5000050,5000050,5000051,5000052,5000050,5000050,5000051,5000052,5000050,5000050,5000051,5000050,5000052,5000050,5000050,5000051,5000052,5000050,5000050,5000051,5000052,5000050,5000050,5000051,5000050,5000050,5000051,5000050,5000050,5000051,5000050,5000050,5000050,5000051,5000051,5000051,5000050,5000050,5000051,5000052,5000055,5000050,5000050,5000051,5000052,5000055,5000050,5000050,5000051,5000052,5000055,5000050,5000050,5000050,5000051,5000052,5000050,5000050,5000051,5000052,5000050,5000050,5000051,5000052,5000050,5000050,5000051,5000052,5000050,5000050,5000050,5000051,5000052,5000050,5000050,5000051,5000052,5000050,5000050,5000051,5000052,5000050,5000050,5000051,5000052,5000050,5000050,5000051,5000050,5000050,5000050,5000051,5000050,5000050,5000051,5000050,5000050,5000051,5000051,5000051,5000050,5000050,5000051,5000052,5000055,5000050,5000050,5000051,5000052,5000055,5000051,5000050,5000050,5000051,5000052,5000055,5000050,5000050,5000051,5000052,5000050,5000050,5000051,5000052,5000050,5000050,5000051,5000052,5000050,5000050,5000051,5000051,5000052,5000050,5000050,5000051,5000052,5000050,5000050,5000051,5000052,5000050,5000050,5000051,5000052,5000050,5000050,5000051,5000052,5000051,5000050,5000050,5000051,5000050,5000050,5000051,5000050,5000050,5000051,5000050,5000050,5000051,5000051,5000051,5000050,5000050,5000051,5000052,5000055,5000051,5000050,5000050,5000051,5000052,5000055,5000050,5000050,5000051,5000052,5000055,5000050,5000050,5000051,5000052,5000050,5000050,5000051,5000052,5000050,5000052,5000050,5000051,5000052,5000050,5000050,5000051,5000052,5000050,5000050,5000051,5000052,5000050,5000050,5000051,5000052,5000050,5000050,5000051,5000052,5000052,5000050,5000050,5000051,5000052,5000050,5000050,5000051,5000050,5000050,5000051,5000050,5000050,5000051,5000050,5000050,5000051,5000051,5000051</t>
         </is>
       </c>
       <c r="D9" s="3" t="n">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="F9" s="0" t="inlineStr">
         <is>
-          <t>L1 W6/25; N=122; EHP=3286.118479; variants:4 (counts doubled, hp x1.5/x2.0) | wavebuff-20261029</t>
+          <t>L1 W6/25; N=256; EHP=10548.512992 | wavebuff2-20261029 (counts x2 again, hp stacked) | gold20-20261029: killGold=80 | ground5-20261030: ground +12 (5%)</t>
         </is>
       </c>
     </row>
@@ -1284,7 +1284,7 @@
       </c>
       <c r="C10" s="0" t="inlineStr">
         <is>
-          <t>5000060,5000060,5000061,5000062,5000065,5000060,5000060,5000061,5000062,5000065,5000060,5000060,5000061,5000062,5000065,5000060,5000060,5000061,5000062,5000065,5000060,5000060,5000061,5000062,5000060,5000060,5000061,5000062,5000060,5000060,5000061,5000062,5000060,5000060,5000061,5000062,5000060,5000060,5000061,5000062,5000060,5000060,5000061,5000062,5000060,5000060,5000061,5000062,5000060,5000060,5000061,5000062,5000060,5000060,5000061,5000060,5000060,5000061,5000060,5000060,5000061,5000060,5000060,5000061,5000060,5000061,5000061,5000060,5000060,5000061,5000062,5000065,5000060,5000060,5000061,5000062,5000065,5000060,5000060,5000061,5000062,5000065,5000060,5000060,5000061,5000062,5000065,5000060,5000060,5000061,5000062,5000060,5000060,5000061,5000062,5000060,5000060,5000061,5000062,5000060,5000060,5000061,5000062,5000060,5000060,5000061,5000062,5000060,5000060,5000061,5000062,5000060,5000060,5000061,5000062,5000060,5000060,5000061,5000062,5000060,5000060,5000061,5000060,5000060,5000061,5000060,5000060,5000061,5000060,5000060,5000061,5000060,5000061,5000061</t>
+          <t>5000060,5000060,5000061,5000062,5000065,5000060,5000060,5000061,5000062,5000065,5000060,5000060,5000061,5000062,5000065,5000060,5000060,5000061,5000062,5000065,5000060,5000060,5000060,5000061,5000062,5000060,5000060,5000061,5000062,5000060,5000060,5000061,5000062,5000060,5000060,5000061,5000062,5000060,5000060,5000061,5000060,5000062,5000060,5000060,5000061,5000062,5000060,5000060,5000061,5000062,5000060,5000060,5000061,5000062,5000060,5000060,5000061,5000060,5000060,5000061,5000060,5000060,5000060,5000061,5000060,5000060,5000061,5000060,5000061,5000061,5000060,5000060,5000061,5000062,5000065,5000060,5000060,5000061,5000062,5000065,5000060,5000060,5000060,5000061,5000062,5000065,5000060,5000060,5000061,5000062,5000065,5000060,5000060,5000061,5000062,5000060,5000060,5000061,5000062,5000060,5000060,5000060,5000061,5000062,5000060,5000060,5000061,5000062,5000060,5000060,5000061,5000062,5000060,5000060,5000061,5000062,5000060,5000060,5000061,5000062,5000060,5000060,5000060,5000061,5000062,5000060,5000060,5000061,5000060,5000060,5000061,5000060,5000060,5000061,5000060,5000060,5000061,5000060,5000061,5000061,5000060,5000060,5000060,5000061,5000062,5000065,5000060,5000060,5000061,5000062,5000065,5000060,5000060,5000061,5000062,5000065,5000060,5000060,5000061,5000062,5000065,5000061,5000060,5000060,5000061,5000062,5000060,5000060,5000061,5000062,5000060,5000060,5000061,5000062,5000060,5000060,5000061,5000062,5000060,5000060,5000061,5000061,5000062,5000060,5000060,5000061,5000062,5000060,5000060,5000061,5000062,5000060,5000060,5000061,5000062,5000060,5000060,5000061,5000060,5000060,5000061,5000061,5000060,5000060,5000061,5000060,5000060,5000061,5000060,5000061,5000061,5000060,5000060,5000061,5000062,5000065,5000060,5000060,5000061,5000062,5000065,5000061,5000060,5000060,5000061,5000062,5000065,5000060,5000060,5000061,5000062,5000065,5000060,5000060,5000061,5000062,5000060,5000060,5000061,5000062,5000060,5000062,5000060,5000061,5000062,5000060,5000060,5000061,5000062,5000060,5000060,5000061,5000062,5000060,5000060,5000061,5000062,5000060,5000060,5000061,5000062,5000062,5000060,5000060,5000061,5000062,5000060,5000060,5000061,5000060,5000060,5000061,5000060,5000060,5000061,5000060,5000060,5000061,5000060,5000061,5000061</t>
         </is>
       </c>
       <c r="D10" s="3" t="n">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="F10" s="0" t="inlineStr">
         <is>
-          <t>L1 W7/25; N=134; EHP=3853.089834; variants:4 (counts doubled, hp x1.5/x2.0) | wavebuff-20261029</t>
+          <t>L1 W7/25; N=281; EHP=12410.951006 | wavebuff2-20261029 (counts x2 again, hp stacked) | gold20-20261029: killGold=132 | ground5-20261030: ground +13 (5%)</t>
         </is>
       </c>
     </row>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="C11" s="0" t="inlineStr">
         <is>
-          <t>5000070,5000070,5000071,5000072,5000075,5000070,5000070,5000071,5000072,5000075,5000070,5000070,5000071,5000072,5000075,5000070,5000070,5000071,5000072,5000075,5000070,5000070,5000071,5000072,5000075,5000070,5000070,5000071,5000072,5000070,5000070,5000071,5000072,5000070,5000070,5000071,5000072,5000070,5000070,5000071,5000072,5000070,5000070,5000071,5000072,5000070,5000070,5000071,5000072,5000070,5000070,5000071,5000072,5000070,5000070,5000071,5000072,5000070,5000070,5000071,5000070,5000070,5000071,5000070,5000070,5000071,5000070,5000070,5000071,5000070,5000071,5000071,5000071,5000070,5000070,5000071,5000072,5000075,5000070,5000070,5000071,5000072,5000075,5000070,5000070,5000071,5000072,5000075,5000070,5000070,5000071,5000072,5000075,5000070,5000070,5000071,5000072,5000075,5000070,5000070,5000071,5000072,5000070,5000070,5000071,5000072,5000070,5000070,5000071,5000072,5000070,5000070,5000071,5000072,5000070,5000070,5000071,5000072,5000070,5000070,5000071,5000072,5000070,5000070,5000071,5000072,5000070,5000070,5000071,5000072,5000070,5000070,5000071,5000070,5000070,5000071,5000070,5000070,5000071,5000070,5000070,5000071,5000070,5000071,5000071,5000071</t>
+          <t>5000070,5000070,5000071,5000072,5000075,5000070,5000070,5000071,5000072,5000075,5000070,5000070,5000071,5000072,5000075,5000070,5000070,5000071,5000072,5000075,5000070,5000070,5000070,5000071,5000072,5000075,5000070,5000070,5000071,5000072,5000070,5000070,5000071,5000072,5000070,5000070,5000071,5000072,5000070,5000070,5000070,5000071,5000072,5000070,5000070,5000071,5000072,5000070,5000070,5000071,5000072,5000070,5000070,5000071,5000072,5000070,5000070,5000071,5000072,5000070,5000070,5000070,5000071,5000070,5000070,5000071,5000070,5000070,5000071,5000070,5000070,5000071,5000070,5000071,5000071,5000071,5000070,5000070,5000071,5000072,5000075,5000070,5000070,5000070,5000071,5000072,5000075,5000070,5000070,5000071,5000072,5000075,5000070,5000070,5000071,5000072,5000075,5000070,5000070,5000071,5000072,5000075,5000070,5000070,5000070,5000071,5000072,5000070,5000070,5000071,5000072,5000070,5000070,5000071,5000072,5000070,5000070,5000071,5000072,5000070,5000070,5000071,5000070,5000072,5000070,5000070,5000071,5000072,5000070,5000070,5000071,5000072,5000070,5000070,5000071,5000072,5000070,5000070,5000071,5000070,5000070,5000071,5000070,5000070,5000070,5000071,5000070,5000070,5000071,5000070,5000071,5000071,5000071,5000070,5000070,5000071,5000072,5000075,5000070,5000070,5000071,5000072,5000075,5000071,5000070,5000070,5000071,5000072,5000075,5000070,5000070,5000071,5000072,5000075,5000070,5000070,5000071,5000072,5000075,5000070,5000070,5000071,5000072,5000070,5000071,5000070,5000071,5000072,5000070,5000070,5000071,5000072,5000070,5000070,5000071,5000072,5000070,5000070,5000071,5000072,5000070,5000070,5000071,5000072,5000071,5000070,5000070,5000071,5000072,5000070,5000070,5000071,5000072,5000070,5000070,5000071,5000070,5000070,5000071,5000070,5000070,5000071,5000070,5000070,5000071,5000071,5000070,5000071,5000071,5000071,5000070,5000070,5000071,5000072,5000075,5000070,5000070,5000071,5000072,5000075,5000070,5000070,5000071,5000072,5000075,5000072,5000070,5000070,5000071,5000072,5000075,5000070,5000070,5000071,5000072,5000075,5000070,5000070,5000071,5000072,5000070,5000070,5000071,5000072,5000070,5000070,5000072,5000071,5000072,5000070,5000070,5000071,5000072,5000070,5000070,5000071,5000072,5000070,5000070,5000071,5000072,5000070,5000070,5000071,5000072,5000070,5000072,5000070,5000071,5000072,5000070,5000070,5000071,5000070,5000070,5000071,5000070,5000070,5000071,5000070,5000070,5000071,5000070,5000071,5000071,5000071</t>
         </is>
       </c>
       <c r="D11" s="3" t="n">
@@ -1316,7 +1316,7 @@
       </c>
       <c r="F11" s="0" t="inlineStr">
         <is>
-          <t>L1 W8/25; N=146; EHP=5024.550000; variants:4 (counts doubled, hp x1.5/x2.0) | wavebuff-20261029</t>
+          <t>L1 W8/25; N=306; EHP=16280.767458 | wavebuff2-20261029 (counts x2 again, hp stacked) | gold20-20261029: killGold=20 | ground5-20261030: ground +14 (5%)</t>
         </is>
       </c>
     </row>
@@ -1326,7 +1326,7 @@
       </c>
       <c r="C12" s="0" t="inlineStr">
         <is>
-          <t>5000080,5000080,5000081,5000082,5000085,5000080,5000080,5000081,5000082,5000085,5000080,5000080,5000081,5000082,5000085,5000080,5000080,5000081,5000082,5000085,5000080,5000080,5000081,5000082,5000085,5000080,5000080,5000081,5000082,5000085,5000080,5000080,5000081,5000082,5000080,5000080,5000081,5000082,5000080,5000080,5000081,5000082,5000080,5000080,5000081,5000082,5000080,5000080,5000081,5000082,5000080,5000080,5000081,5000082,5000080,5000080,5000081,5000082,5000080,5000080,5000081,5000082,5000080,5000080,5000081,5000080,5000080,5000081,5000080,5000080,5000081,5000080,5000080,5000081,5000080,5000080,5000081,5000081,5000081,5000080,5000080,5000081,5000082,5000085,5000080,5000080,5000081,5000082,5000085,5000080,5000080,5000081,5000082,5000085,5000080,5000080,5000081,5000082,5000085,5000080,5000080,5000081,5000082,5000085,5000080,5000080,5000081,5000082,5000085,5000080,5000080,5000081,5000082,5000080,5000080,5000081,5000082,5000080,5000080,5000081,5000082,5000080,5000080,5000081,5000082,5000080,5000080,5000081,5000082,5000080,5000080,5000081,5000082,5000080,5000080,5000081,5000082,5000080,5000080,5000081,5000082,5000080,5000080,5000081,5000080,5000080,5000081,5000080,5000080,5000081,5000080,5000080,5000081,5000080,5000080,5000081,5000081,5000081</t>
+          <t>5000080,5000080,5000081,5000082,5000085,5000080,5000080,5000081,5000082,5000085,5000080,5000080,5000081,5000082,5000085,5000080,5000080,5000081,5000082,5000085,5000080,5000080,5000080,5000081,5000082,5000085,5000080,5000080,5000081,5000082,5000085,5000080,5000080,5000081,5000082,5000080,5000080,5000081,5000082,5000080,5000080,5000080,5000081,5000082,5000080,5000080,5000081,5000082,5000080,5000080,5000081,5000082,5000080,5000080,5000081,5000082,5000080,5000080,5000081,5000082,5000080,5000080,5000080,5000081,5000082,5000080,5000080,5000081,5000080,5000080,5000081,5000080,5000080,5000081,5000080,5000080,5000081,5000080,5000080,5000081,5000081,5000081,5000080,5000080,5000080,5000081,5000082,5000085,5000080,5000080,5000081,5000082,5000085,5000080,5000080,5000081,5000082,5000085,5000080,5000080,5000081,5000082,5000085,5000080,5000080,5000080,5000081,5000082,5000085,5000080,5000080,5000081,5000082,5000085,5000080,5000080,5000081,5000082,5000080,5000080,5000081,5000082,5000080,5000080,5000080,5000081,5000082,5000080,5000080,5000081,5000082,5000080,5000080,5000081,5000082,5000080,5000080,5000081,5000082,5000080,5000080,5000081,5000082,5000080,5000080,5000080,5000081,5000082,5000080,5000080,5000081,5000080,5000080,5000081,5000080,5000080,5000081,5000080,5000080,5000081,5000080,5000080,5000081,5000081,5000081,5000080,5000080,5000080,5000081,5000082,5000085,5000080,5000080,5000081,5000082,5000085,5000080,5000080,5000081,5000082,5000085,5000080,5000080,5000081,5000082,5000085,5000081,5000080,5000080,5000081,5000082,5000085,5000080,5000080,5000081,5000082,5000085,5000080,5000080,5000081,5000082,5000080,5000080,5000081,5000082,5000080,5000080,5000081,5000081,5000082,5000080,5000080,5000081,5000082,5000080,5000080,5000081,5000082,5000080,5000080,5000081,5000082,5000080,5000080,5000081,5000082,5000080,5000080,5000081,5000081,5000082,5000080,5000080,5000081,5000080,5000080,5000081,5000080,5000080,5000081,5000080,5000080,5000081,5000080,5000080,5000081,5000081,5000081,5000081,5000080,5000080,5000081,5000082,5000085,5000080,5000080,5000081,5000082,5000085,5000080,5000080,5000081,5000082,5000085,5000080,5000080,5000081,5000082,5000085,5000082,5000080,5000080,5000081,5000082,5000085,5000080,5000080,5000081,5000082,5000085,5000080,5000080,5000081,5000082,5000080,5000080,5000081,5000082,5000080,5000080,5000082,5000081,5000082,5000080,5000080,5000081,5000082,5000080,5000080,5000081,5000082,5000080,5000080,5000081,5000082,5000080,5000080,5000081,5000082,5000080,5000080,5000082,5000081,5000082,5000080,5000080,5000081,5000080,5000080,5000081,5000080,5000080,5000081,5000080,5000080,5000081,5000080,5000080,5000081,5000081,5000081</t>
         </is>
       </c>
       <c r="D12" s="3" t="n">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="F12" s="0" t="inlineStr">
         <is>
-          <t>L1 W9/25; N=158; EHP=6455.595767; variants:4 (counts doubled, hp x1.5/x2.0) | wavebuff-20261029</t>
+          <t>L1 W9/25; N=331; EHP=20961.699193 | wavebuff2-20261029 (counts x2 again, hp stacked) | gold20-20261029: killGold=24 | ground5-20261030: ground +15 (5%)</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="C13" s="0" t="inlineStr">
         <is>
-          <t>5000090,5000090,5000091,5000092,5000095,5000090,5000090,5000091,5000092,5000095,5000090,5000090,5000091,5000092,5000095,5000090,5000090,5000091,5000092,5000095,5000090,5000090,5000091,5000092,5000095,5000090,5000090,5000091,5000092,5000095,5000090,5000090,5000091,5000092,5000095,5000090,5000090,5000091,5000092,5000090,5000090,5000091,5000092,5000090,5000090,5000091,5000092,5000090,5000090,5000091,5000092,5000090,5000090,5000091,5000092,5000090,5000090,5000091,5000092,5000090,5000090,5000091,5000092,5000090,5000090,5000091,5000092,5000090,5000090,5000091,5000090,5000090,5000091,5000090,5000090,5000091,5000090,5000090,5000091,5000090,5000090,5000091,5000091,5000091,5000091,5000090,5000090,5000091,5000092,5000095,5000090,5000090,5000091,5000092,5000095,5000090,5000090,5000091,5000092,5000095,5000090,5000090,5000091,5000092,5000095,5000090,5000090,5000091,5000092,5000095,5000090,5000090,5000091,5000092,5000095,5000090,5000090,5000091,5000092,5000095,5000090,5000090,5000091,5000092,5000090,5000090,5000091,5000092,5000090,5000090,5000091,5000092,5000090,5000090,5000091,5000092,5000090,5000090,5000091,5000092,5000090,5000090,5000091,5000092,5000090,5000090,5000091,5000092,5000090,5000090,5000091,5000092,5000090,5000090,5000091,5000090,5000090,5000091,5000090,5000090,5000091,5000090,5000090,5000091,5000090,5000090,5000091,5000091,5000091,5000091</t>
+          <t>5000090,5000090,5000091,5000092,5000095,5000090,5000090,5000091,5000092,5000095,5000090,5000090,5000091,5000092,5000095,5000090,5000090,5000091,5000092,5000095,5000090,5000090,5000090,5000091,5000092,5000095,5000090,5000090,5000091,5000092,5000095,5000090,5000090,5000091,5000092,5000095,5000090,5000090,5000091,5000092,5000090,5000090,5000090,5000091,5000092,5000090,5000090,5000091,5000092,5000090,5000090,5000091,5000092,5000090,5000090,5000091,5000092,5000090,5000090,5000091,5000092,5000090,5000090,5000090,5000091,5000092,5000090,5000090,5000091,5000092,5000090,5000090,5000091,5000090,5000090,5000091,5000090,5000090,5000091,5000090,5000090,5000091,5000090,5000090,5000090,5000091,5000091,5000091,5000091,5000090,5000090,5000091,5000092,5000095,5000090,5000090,5000091,5000092,5000095,5000090,5000090,5000091,5000092,5000095,5000090,5000090,5000090,5000091,5000092,5000095,5000090,5000090,5000091,5000092,5000095,5000090,5000090,5000091,5000092,5000095,5000090,5000090,5000091,5000092,5000095,5000090,5000090,5000090,5000091,5000092,5000090,5000090,5000091,5000092,5000090,5000090,5000091,5000092,5000090,5000090,5000091,5000092,5000090,5000090,5000091,5000092,5000090,5000090,5000090,5000091,5000092,5000090,5000090,5000091,5000092,5000090,5000090,5000091,5000092,5000090,5000090,5000091,5000090,5000090,5000091,5000090,5000090,5000090,5000091,5000090,5000090,5000091,5000090,5000090,5000091,5000091,5000091,5000091,5000090,5000090,5000091,5000092,5000095,5000090,5000090,5000091,5000092,5000095,5000091,5000090,5000090,5000091,5000092,5000095,5000090,5000090,5000091,5000092,5000095,5000090,5000090,5000091,5000092,5000095,5000090,5000090,5000091,5000092,5000095,5000091,5000090,5000090,5000091,5000092,5000095,5000090,5000090,5000091,5000092,5000090,5000090,5000091,5000092,5000090,5000090,5000091,5000092,5000090,5000090,5000091,5000091,5000092,5000090,5000090,5000091,5000092,5000090,5000090,5000091,5000092,5000090,5000090,5000091,5000092,5000090,5000090,5000091,5000092,5000090,5000090,5000091,5000091,5000090,5000090,5000091,5000090,5000090,5000091,5000090,5000090,5000091,5000090,5000090,5000091,5000091,5000091,5000091,5000090,5000090,5000091,5000092,5000095,5000091,5000090,5000090,5000091,5000092,5000095,5000090,5000090,5000091,5000092,5000095,5000090,5000090,5000091,5000092,5000095,5000090,5000090,5000091,5000092,5000095,5000092,5000090,5000090,5000091,5000092,5000095,5000090,5000090,5000091,5000092,5000095,5000090,5000090,5000091,5000092,5000090,5000090,5000091,5000092,5000090,5000090,5000092,5000091,5000092,5000090,5000090,5000091,5000092,5000090,5000090,5000091,5000092,5000090,5000090,5000091,5000092,5000090,5000090,5000091,5000092,5000090,5000090,5000092,5000091,5000092,5000090,5000090,5000091,5000090,5000090,5000091,5000090,5000090,5000091,5000090,5000090,5000091,5000090,5000090,5000091,5000091,5000091,5000091</t>
         </is>
       </c>
       <c r="D13" s="3" t="n">
@@ -1358,7 +1358,7 @@
       </c>
       <c r="F13" s="0" t="inlineStr">
         <is>
-          <t>L1 W10/25; N=170; EHP=11964.417797; variants:4 (counts doubled, hp x1.5/x2.0) | wavebuff-20261029</t>
+          <t>L1 W10/25; N=356; EHP=38896.801214 | wavebuff2-20261029 (counts x2 again, hp stacked) | gold20-20261029: killGold=0 | ground5-20261030: ground +16 (5%)</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       </c>
       <c r="C14" s="0" t="inlineStr">
         <is>
-          <t>5000100,5000100,5000101,5000102,5000103,5000105,5000100,5000100,5000101,5000102,5000103,5000105,5000100,5000100,5000101,5000102,5000103,5000105,5000100,5000100,5000101,5000102,5000103,5000105,5000100,5000100,5000101,5000102,5000103,5000105,5000100,5000100,5000101,5000102,5000103,5000105,5000100,5000100,5000101,5000102,5000103,5000105,5000100,5000100,5000101,5000102,5000103,5000105,5000100,5000100,5000101,5000102,5000103,5000100,5000100,5000101,5000102,5000100,5000100,5000101,5000102,5000100,5000100,5000101,5000102,5000100,5000100,5000101,5000102,5000100,5000100,5000101,5000100,5000100,5000101,5000100,5000100,5000101,5000100,5000100,5000101,5000100,5000100,5000101,5000100,5000100,5000101,5000100,5000101,5000101,5000101,5000100,5000100,5000101,5000102,5000103,5000105,5000100,5000100,5000101,5000102,5000103,5000105,5000100,5000100,5000101,5000102,5000103,5000105,5000100,5000100,5000101,5000102,5000103,5000105,5000100,5000100,5000101,5000102,5000103,5000105,5000100,5000100,5000101,5000102,5000103,5000105,5000100,5000100,5000101,5000102,5000103,5000105,5000100,5000100,5000101,5000102,5000103,5000105,5000100,5000100,5000101,5000102,5000103,5000100,5000100,5000101,5000102,5000100,5000100,5000101,5000102,5000100,5000100,5000101,5000102,5000100,5000100,5000101,5000102,5000100,5000100,5000101,5000100,5000100,5000101,5000100,5000100,5000101,5000100,5000100,5000101,5000100,5000100,5000101,5000100,5000100,5000101,5000100,5000101,5000101,5000101</t>
+          <t>5000100,5000100,5000101,5000102,5000103,5000105,5000100,5000100,5000101,5000102,5000103,5000105,5000100,5000100,5000101,5000102,5000103,5000105,5000100,5000100,5000101,5000100,5000102,5000103,5000105,5000100,5000100,5000101,5000102,5000103,5000105,5000100,5000100,5000101,5000102,5000103,5000105,5000100,5000100,5000101,5000102,5000103,5000100,5000105,5000100,5000100,5000101,5000102,5000103,5000105,5000100,5000100,5000101,5000102,5000103,5000100,5000100,5000101,5000102,5000100,5000100,5000101,5000102,5000100,5000100,5000100,5000101,5000102,5000100,5000100,5000101,5000102,5000100,5000100,5000101,5000100,5000100,5000101,5000100,5000100,5000101,5000100,5000100,5000101,5000100,5000100,5000100,5000101,5000100,5000100,5000101,5000100,5000101,5000101,5000101,5000100,5000100,5000101,5000102,5000103,5000105,5000100,5000100,5000101,5000102,5000103,5000100,5000105,5000100,5000100,5000101,5000102,5000103,5000105,5000100,5000100,5000101,5000102,5000103,5000105,5000100,5000100,5000101,5000102,5000103,5000105,5000100,5000100,5000100,5000101,5000102,5000103,5000105,5000100,5000100,5000101,5000102,5000103,5000105,5000100,5000100,5000101,5000102,5000103,5000105,5000100,5000100,5000101,5000100,5000102,5000103,5000100,5000100,5000101,5000102,5000100,5000100,5000101,5000102,5000100,5000100,5000101,5000102,5000100,5000100,5000101,5000102,5000100,5000100,5000100,5000101,5000100,5000100,5000101,5000100,5000100,5000101,5000100,5000100,5000101,5000100,5000100,5000101,5000100,5000100,5000101,5000100,5000101,5000101,5000101,5000101,5000100,5000100,5000101,5000102,5000103,5000105,5000100,5000100,5000101,5000102,5000103,5000105,5000100,5000100,5000101,5000102,5000103,5000105,5000100,5000100,5000101,5000101,5000102,5000103,5000105,5000100,5000100,5000101,5000102,5000103,5000105,5000100,5000100,5000101,5000102,5000103,5000105,5000100,5000100,5000101,5000102,5000103,5000101,5000105,5000100,5000100,5000101,5000102,5000103,5000105,5000100,5000100,5000101,5000102,5000103,5000100,5000100,5000101,5000102,5000100,5000100,5000101,5000102,5000101,5000100,5000100,5000101,5000102,5000100,5000100,5000101,5000102,5000100,5000100,5000101,5000100,5000100,5000101,5000100,5000100,5000101,5000100,5000100,5000101,5000102,5000100,5000100,5000101,5000100,5000100,5000101,5000100,5000101,5000101,5000101,5000100,5000100,5000101,5000102,5000103,5000105,5000100,5000100,5000101,5000102,5000103,5000102,5000105,5000100,5000100,5000101,5000102,5000103,5000105,5000100,5000100,5000101,5000102,5000103,5000105,5000100,5000100,5000101,5000102,5000103,5000105,5000100,5000102,5000100,5000101,5000102,5000103,5000105,5000100,5000100,5000101,5000102,5000103,5000105,5000100,5000100,5000101,5000102,5000103,5000105,5000100,5000100,5000101,5000103,5000102,5000103,5000100,5000100,5000101,5000102,5000100,5000100,5000101,5000102,5000100,5000100,5000101,5000102,5000100,5000100,5000101,5000102,5000100,5000100,5000103,5000101,5000100,5000100,5000101,5000100,5000100,5000101,5000100,5000100,5000101,5000100,5000100,5000101,5000100,5000100,5000101,5000100,5000101,5000101,5000101</t>
         </is>
       </c>
       <c r="D14" s="3" t="n">
@@ -1379,7 +1379,7 @@
       </c>
       <c r="F14" s="0" t="inlineStr">
         <is>
-          <t>L1 W11/25; N=182; EHP=12141.295522; variants:5 (counts doubled, hp x1.5/x2.0) | wavebuff-20261029</t>
+          <t>L1 W11/25; N=381; EHP=39385.756064 | wavebuff2-20261029 (counts x2 again, hp stacked) | gold20-20261029: killGold=0 | ground5-20261030: ground +17 (5%)</t>
         </is>
       </c>
     </row>
@@ -1389,7 +1389,7 @@
       </c>
       <c r="C15" s="0" t="inlineStr">
         <is>
-          <t>5000110,5000110,5000111,5000112,5000113,5000115,5000110,5000110,5000111,5000112,5000113,5000115,5000110,5000110,5000111,5000112,5000113,5000115,5000110,5000110,5000111,5000112,5000113,5000115,5000110,5000110,5000111,5000112,5000113,5000115,5000110,5000110,5000111,5000112,5000113,5000115,5000110,5000110,5000111,5000112,5000113,5000115,5000110,5000110,5000111,5000112,5000113,5000115,5000110,5000110,5000111,5000112,5000113,5000115,5000110,5000110,5000111,5000112,5000113,5000110,5000110,5000111,5000112,5000110,5000110,5000111,5000112,5000110,5000110,5000111,5000112,5000110,5000110,5000111,5000112,5000110,5000110,5000111,5000110,5000110,5000111,5000110,5000110,5000111,5000110,5000110,5000111,5000110,5000110,5000111,5000110,5000110,5000111,5000110,5000111,5000111,5000111,5000110,5000110,5000111,5000112,5000113,5000115,5000110,5000110,5000111,5000112,5000113,5000115,5000110,5000110,5000111,5000112,5000113,5000115,5000110,5000110,5000111,5000112,5000113,5000115,5000110,5000110,5000111,5000112,5000113,5000115,5000110,5000110,5000111,5000112,5000113,5000115,5000110,5000110,5000111,5000112,5000113,5000115,5000110,5000110,5000111,5000112,5000113,5000115,5000110,5000110,5000111,5000112,5000113,5000115,5000110,5000110,5000111,5000112,5000113,5000110,5000110,5000111,5000112,5000110,5000110,5000111,5000112,5000110,5000110,5000111,5000112,5000110,5000110,5000111,5000112,5000110,5000110,5000111,5000110,5000110,5000111,5000110,5000110,5000111,5000110,5000110,5000111,5000110,5000110,5000111,5000110,5000110,5000111,5000110,5000111,5000111,5000111</t>
+          <t>5000110,5000110,5000111,5000112,5000113,5000115,5000110,5000110,5000111,5000112,5000113,5000115,5000110,5000110,5000111,5000112,5000113,5000115,5000110,5000110,5000111,5000110,5000112,5000113,5000115,5000110,5000110,5000111,5000112,5000113,5000115,5000110,5000110,5000111,5000112,5000113,5000115,5000110,5000110,5000111,5000112,5000113,5000110,5000115,5000110,5000110,5000111,5000112,5000113,5000115,5000110,5000110,5000111,5000112,5000113,5000115,5000110,5000110,5000111,5000112,5000113,5000110,5000110,5000111,5000110,5000112,5000110,5000110,5000111,5000112,5000110,5000110,5000111,5000112,5000110,5000110,5000111,5000112,5000110,5000110,5000111,5000110,5000110,5000111,5000110,5000110,5000110,5000111,5000110,5000110,5000111,5000110,5000110,5000111,5000110,5000110,5000111,5000110,5000111,5000111,5000111,5000110,5000110,5000111,5000112,5000113,5000115,5000110,5000110,5000110,5000111,5000112,5000113,5000115,5000110,5000110,5000111,5000112,5000113,5000115,5000110,5000110,5000111,5000112,5000113,5000115,5000110,5000110,5000110,5000111,5000112,5000113,5000115,5000110,5000110,5000111,5000112,5000113,5000115,5000110,5000110,5000111,5000112,5000113,5000115,5000110,5000110,5000111,5000112,5000110,5000113,5000115,5000110,5000110,5000111,5000112,5000113,5000115,5000110,5000110,5000111,5000112,5000113,5000110,5000110,5000111,5000112,5000110,5000110,5000111,5000112,5000110,5000110,5000110,5000111,5000112,5000110,5000110,5000111,5000112,5000110,5000110,5000111,5000110,5000110,5000111,5000110,5000110,5000111,5000110,5000110,5000111,5000111,5000110,5000110,5000111,5000110,5000110,5000111,5000110,5000111,5000111,5000111,5000110,5000110,5000111,5000112,5000113,5000115,5000110,5000110,5000111,5000112,5000113,5000111,5000115,5000110,5000110,5000111,5000112,5000113,5000115,5000110,5000110,5000111,5000112,5000113,5000115,5000110,5000110,5000111,5000112,5000113,5000115,5000110,5000111,5000110,5000111,5000112,5000113,5000115,5000110,5000110,5000111,5000112,5000113,5000115,5000110,5000110,5000111,5000112,5000113,5000115,5000110,5000110,5000111,5000112,5000111,5000113,5000115,5000110,5000110,5000111,5000112,5000113,5000110,5000110,5000111,5000112,5000110,5000110,5000111,5000112,5000110,5000110,5000111,5000112,5000110,5000111,5000110,5000111,5000112,5000110,5000110,5000111,5000110,5000110,5000111,5000110,5000110,5000111,5000110,5000110,5000111,5000110,5000110,5000111,5000110,5000110,5000112,5000111,5000110,5000111,5000111,5000111,5000110,5000110,5000111,5000112,5000113,5000115,5000110,5000110,5000111,5000112,5000113,5000115,5000110,5000110,5000111,5000112,5000112,5000113,5000115,5000110,5000110,5000111,5000112,5000113,5000115,5000110,5000110,5000111,5000112,5000113,5000115,5000110,5000110,5000111,5000112,5000113,5000115,5000112,5000110,5000110,5000111,5000112,5000113,5000115,5000110,5000110,5000111,5000112,5000113,5000115,5000110,5000110,5000111,5000112,5000113,5000115,5000110,5000110,5000111,5000113,5000112,5000113,5000110,5000110,5000111,5000112,5000110,5000110,5000111,5000112,5000110,5000110,5000111,5000112,5000110,5000110,5000111,5000112,5000110,5000110,5000113,5000111,5000110,5000110,5000111,5000110,5000110,5000111,5000110,5000110,5000111,5000110,5000110,5000111,5000110,5000110,5000111,5000110,5000111,5000111,5000111</t>
         </is>
       </c>
       <c r="D15" s="3" t="n">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="F15" s="0" t="inlineStr">
         <is>
-          <t>L1 W12/25; N=194; EHP=12591.646760; variants:5 (counts doubled, hp x1.5/x2.0) | wavebuff-20261029</t>
+          <t>L1 W12/25; N=406; EHP=40809.085638 | wavebuff2-20261029 (counts x2 again, hp stacked) | gold20-20261029: killGold=0 | ground5-20261030: ground +18 (5%)</t>
         </is>
       </c>
     </row>
@@ -1410,7 +1410,7 @@
       </c>
       <c r="C16" s="0" t="inlineStr">
         <is>
-          <t>5000120,5000120,5000121,5000122,5000123,5000125,5000120,5000120,5000121,5000122,5000123,5000125,5000120,5000120,5000121,5000122,5000123,5000125,5000120,5000120,5000121,5000122,5000123,5000125,5000120,5000120,5000121,5000122,5000123,5000125,5000120,5000120,5000121,5000122,5000123,5000125,5000120,5000120,5000121,5000122,5000123,5000125,5000120,5000120,5000121,5000122,5000123,5000125,5000120,5000120,5000121,5000122,5000123,5000125,5000120,5000120,5000121,5000122,5000123,5000125,5000120,5000120,5000121,5000122,5000123,5000120,5000120,5000121,5000122,5000120,5000120,5000121,5000122,5000120,5000120,5000121,5000122,5000120,5000120,5000121,5000120,5000120,5000121,5000120,5000120,5000121,5000120,5000120,5000121,5000120,5000120,5000121,5000120,5000120,5000121,5000120,5000120,5000121,5000120,5000121,5000121,5000121,5000121,5000120,5000120,5000121,5000122,5000123,5000125,5000120,5000120,5000121,5000122,5000123,5000125,5000120,5000120,5000121,5000122,5000123,5000125,5000120,5000120,5000121,5000122,5000123,5000125,5000120,5000120,5000121,5000122,5000123,5000125,5000120,5000120,5000121,5000122,5000123,5000125,5000120,5000120,5000121,5000122,5000123,5000125,5000120,5000120,5000121,5000122,5000123,5000125,5000120,5000120,5000121,5000122,5000123,5000125,5000120,5000120,5000121,5000122,5000123,5000125,5000120,5000120,5000121,5000122,5000123,5000120,5000120,5000121,5000122,5000120,5000120,5000121,5000122,5000120,5000120,5000121,5000122,5000120,5000120,5000121,5000120,5000120,5000121,5000120,5000120,5000121,5000120,5000120,5000121,5000120,5000120,5000121,5000120,5000120,5000121,5000120,5000120,5000121,5000120,5000121,5000121,5000121,5000121</t>
+          <t>5000120,5000120,5000121,5000122,5000123,5000125,5000120,5000120,5000121,5000122,5000123,5000125,5000120,5000120,5000121,5000122,5000123,5000125,5000120,5000120,5000121,5000120,5000122,5000123,5000125,5000120,5000120,5000121,5000122,5000123,5000125,5000120,5000120,5000121,5000122,5000123,5000125,5000120,5000120,5000121,5000122,5000123,5000125,5000120,5000120,5000120,5000121,5000122,5000123,5000125,5000120,5000120,5000121,5000122,5000123,5000125,5000120,5000120,5000121,5000122,5000123,5000125,5000120,5000120,5000120,5000121,5000122,5000123,5000120,5000120,5000121,5000122,5000120,5000120,5000121,5000122,5000120,5000120,5000121,5000122,5000120,5000120,5000121,5000120,5000120,5000121,5000120,5000120,5000120,5000121,5000120,5000120,5000121,5000120,5000120,5000121,5000120,5000120,5000121,5000120,5000120,5000121,5000120,5000121,5000121,5000121,5000121,5000120,5000120,5000120,5000121,5000122,5000123,5000125,5000120,5000120,5000121,5000122,5000123,5000125,5000120,5000120,5000121,5000122,5000123,5000125,5000120,5000120,5000121,5000120,5000122,5000123,5000125,5000120,5000120,5000121,5000122,5000123,5000125,5000120,5000120,5000121,5000122,5000123,5000125,5000120,5000120,5000121,5000122,5000123,5000125,5000120,5000120,5000120,5000121,5000122,5000123,5000125,5000120,5000120,5000121,5000122,5000123,5000125,5000120,5000120,5000121,5000122,5000123,5000125,5000120,5000120,5000120,5000121,5000122,5000123,5000120,5000120,5000121,5000122,5000120,5000120,5000121,5000122,5000120,5000120,5000121,5000122,5000120,5000120,5000121,5000120,5000120,5000121,5000120,5000120,5000120,5000121,5000120,5000120,5000121,5000120,5000120,5000121,5000120,5000120,5000121,5000120,5000120,5000121,5000120,5000121,5000121,5000121,5000121,5000121,5000120,5000120,5000121,5000122,5000123,5000125,5000120,5000120,5000121,5000122,5000123,5000125,5000120,5000120,5000121,5000122,5000123,5000125,5000120,5000120,5000121,5000121,5000122,5000123,5000125,5000120,5000120,5000121,5000122,5000123,5000125,5000120,5000120,5000121,5000122,5000123,5000125,5000120,5000120,5000121,5000122,5000123,5000125,5000121,5000120,5000120,5000121,5000122,5000123,5000125,5000120,5000120,5000121,5000122,5000123,5000125,5000120,5000120,5000121,5000122,5000123,5000125,5000120,5000120,5000121,5000121,5000122,5000123,5000120,5000120,5000121,5000122,5000120,5000120,5000121,5000122,5000120,5000120,5000121,5000122,5000120,5000120,5000121,5000120,5000120,5000121,5000121,5000120,5000120,5000121,5000120,5000120,5000121,5000120,5000120,5000121,5000120,5000120,5000121,5000120,5000120,5000121,5000120,5000121,5000121,5000121,5000121,5000122,5000120,5000120,5000121,5000122,5000123,5000125,5000120,5000120,5000121,5000122,5000123,5000125,5000120,5000120,5000121,5000122,5000123,5000125,5000120,5000120,5000121,5000122,5000122,5000123,5000125,5000120,5000120,5000121,5000122,5000123,5000125,5000120,5000120,5000121,5000122,5000123,5000125,5000120,5000120,5000121,5000122,5000123,5000125,5000122,5000120,5000120,5000121,5000122,5000123,5000125,5000120,5000120,5000121,5000122,5000123,5000125,5000120,5000120,5000121,5000122,5000123,5000125,5000120,5000120,5000123,5000121,5000122,5000123,5000120,5000120,5000121,5000122,5000120,5000120,5000121,5000122,5000120,5000120,5000121,5000122,5000120,5000120,5000121,5000120,5000120,5000121,5000123,5000120,5000120,5000121,5000120,5000120,5000121,5000120,5000120,5000121,5000120,5000120,5000121,5000120,5000120,5000121,5000120,5000121,5000121,5000121,5000121</t>
         </is>
       </c>
       <c r="D16" s="3" t="n">
@@ -1421,7 +1421,7 @@
       </c>
       <c r="F16" s="0" t="inlineStr">
         <is>
-          <t>L1 W13/25; N=206; EHP=15372.591629; variants:5 (counts doubled, hp x1.5/x2.0) | wavebuff-20261029</t>
+          <t>L1 W13/25; N=431; EHP=49843.475103 | wavebuff2-20261029 (counts x2 again, hp stacked) | gold20-20261029: killGold=0 | ground5-20261030: ground +19 (5%)</t>
         </is>
       </c>
     </row>
@@ -1431,7 +1431,7 @@
       </c>
       <c r="C17" s="0" t="inlineStr">
         <is>
-          <t>5000130,5000130,5000131,5000132,5000133,5000135,5000130,5000130,5000131,5000132,5000133,5000135,5000130,5000130,5000131,5000132,5000133,5000135,5000130,5000130,5000131,5000132,5000133,5000135,5000130,5000130,5000131,5000132,5000133,5000135,5000130,5000130,5000131,5000132,5000133,5000135,5000130,5000130,5000131,5000132,5000133,5000135,5000130,5000130,5000131,5000132,5000133,5000135,5000130,5000130,5000131,5000132,5000133,5000135,5000130,5000130,5000131,5000132,5000133,5000135,5000130,5000130,5000131,5000132,5000133,5000135,5000130,5000130,5000131,5000132,5000130,5000130,5000131,5000132,5000130,5000130,5000131,5000132,5000130,5000130,5000131,5000132,5000130,5000130,5000131,5000130,5000130,5000131,5000130,5000130,5000131,5000130,5000130,5000131,5000130,5000130,5000131,5000130,5000130,5000131,5000130,5000130,5000131,5000130,5000130,5000131,5000131,5000131,5000131,5000130,5000130,5000131,5000132,5000133,5000135,5000130,5000130,5000131,5000132,5000133,5000135,5000130,5000130,5000131,5000132,5000133,5000135,5000130,5000130,5000131,5000132,5000133,5000135,5000130,5000130,5000131,5000132,5000133,5000135,5000130,5000130,5000131,5000132,5000133,5000135,5000130,5000130,5000131,5000132,5000133,5000135,5000130,5000130,5000131,5000132,5000133,5000135,5000130,5000130,5000131,5000132,5000133,5000135,5000130,5000130,5000131,5000132,5000133,5000135,5000130,5000130,5000131,5000132,5000133,5000135,5000130,5000130,5000131,5000132,5000130,5000130,5000131,5000132,5000130,5000130,5000131,5000132,5000130,5000130,5000131,5000132,5000130,5000130,5000131,5000130,5000130,5000131,5000130,5000130,5000131,5000130,5000130,5000131,5000130,5000130,5000131,5000130,5000130,5000131,5000130,5000130,5000131,5000130,5000130,5000131,5000131,5000131,5000131</t>
+          <t>5000130,5000130,5000131,5000132,5000133,5000135,5000130,5000130,5000131,5000132,5000133,5000135,5000130,5000130,5000131,5000132,5000133,5000135,5000130,5000130,5000131,5000130,5000132,5000133,5000135,5000130,5000130,5000131,5000132,5000133,5000135,5000130,5000130,5000131,5000132,5000133,5000135,5000130,5000130,5000131,5000132,5000133,5000135,5000130,5000130,5000130,5000131,5000132,5000133,5000135,5000130,5000130,5000131,5000132,5000133,5000135,5000130,5000130,5000131,5000132,5000133,5000135,5000130,5000130,5000131,5000130,5000132,5000133,5000135,5000130,5000130,5000131,5000132,5000130,5000130,5000131,5000132,5000130,5000130,5000131,5000132,5000130,5000130,5000131,5000132,5000130,5000130,5000130,5000131,5000130,5000130,5000131,5000130,5000130,5000131,5000130,5000130,5000131,5000130,5000130,5000131,5000130,5000130,5000131,5000130,5000130,5000131,5000130,5000130,5000130,5000131,5000131,5000131,5000131,5000130,5000130,5000131,5000132,5000133,5000135,5000130,5000130,5000131,5000132,5000133,5000135,5000130,5000130,5000131,5000132,5000130,5000133,5000135,5000130,5000130,5000131,5000132,5000133,5000135,5000130,5000130,5000131,5000132,5000133,5000135,5000130,5000130,5000131,5000132,5000133,5000135,5000130,5000130,5000130,5000131,5000132,5000133,5000135,5000130,5000130,5000131,5000132,5000133,5000135,5000130,5000130,5000131,5000132,5000133,5000135,5000130,5000130,5000131,5000132,5000130,5000133,5000135,5000130,5000130,5000131,5000132,5000133,5000135,5000130,5000130,5000131,5000132,5000130,5000130,5000131,5000132,5000130,5000130,5000131,5000132,5000130,5000130,5000130,5000131,5000132,5000130,5000130,5000131,5000130,5000130,5000131,5000130,5000130,5000131,5000130,5000130,5000131,5000130,5000130,5000131,5000130,5000130,5000130,5000131,5000130,5000130,5000131,5000130,5000130,5000131,5000131,5000131,5000131,5000130,5000130,5000131,5000132,5000133,5000135,5000130,5000130,5000131,5000132,5000133,5000131,5000135,5000130,5000130,5000131,5000132,5000133,5000135,5000130,5000130,5000131,5000132,5000133,5000135,5000130,5000130,5000131,5000132,5000133,5000135,5000130,5000130,5000131,5000131,5000132,5000133,5000135,5000130,5000130,5000131,5000132,5000133,5000135,5000130,5000130,5000131,5000132,5000133,5000135,5000130,5000130,5000131,5000132,5000131,5000133,5000135,5000130,5000130,5000131,5000132,5000133,5000135,5000130,5000130,5000131,5000132,5000133,5000135,5000130,5000130,5000131,5000132,5000130,5000130,5000131,5000131,5000132,5000130,5000130,5000131,5000132,5000130,5000130,5000131,5000132,5000130,5000130,5000131,5000130,5000130,5000131,5000130,5000130,5000131,5000130,5000130,5000131,5000131,5000130,5000130,5000131,5000130,5000130,5000131,5000130,5000130,5000131,5000130,5000130,5000131,5000131,5000131,5000131,5000130,5000130,5000131,5000132,5000133,5000135,5000132,5000130,5000130,5000131,5000132,5000133,5000135,5000130,5000130,5000131,5000132,5000133,5000135,5000130,5000130,5000131,5000132,5000133,5000135,5000130,5000130,5000132,5000131,5000132,5000133,5000135,5000130,5000130,5000131,5000132,5000133,5000135,5000130,5000130,5000131,5000132,5000133,5000135,5000130,5000130,5000131,5000132,5000133,5000132,5000135,5000130,5000130,5000131,5000132,5000133,5000135,5000130,5000130,5000131,5000132,5000133,5000135,5000130,5000130,5000131,5000132,5000133,5000135,5000130,5000130,5000133,5000131,5000132,5000130,5000130,5000131,5000132,5000130,5000130,5000131,5000132,5000130,5000130,5000131,5000132,5000130,5000130,5000131,5000130,5000130,5000131,5000130,5000133,5000130,5000131,5000130,5000130,5000131,5000130,5000130,5000131,5000130,5000130,5000131,5000130,5000130,5000131,5000130,5000130,5000131,5000131,5000131,5000131</t>
         </is>
       </c>
       <c r="D17" s="3" t="n">
@@ -1442,7 +1442,7 @@
       </c>
       <c r="F17" s="0" t="inlineStr">
         <is>
-          <t>L1 W14/25; N=218; EHP=18592.495024; variants:5 (counts doubled, hp x1.5/x2.0) | wavebuff-20261029</t>
+          <t>L1 W14/25; N=456; EHP=60354.909159 | wavebuff2-20261029 (counts x2 again, hp stacked) | gold20-20261029: killGold=0 | ground5-20261030: ground +20 (5%)</t>
         </is>
       </c>
     </row>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="C18" s="0" t="inlineStr">
         <is>
-          <t>5000140,5000140,5000141,5000142,5000143,5000145,5000140,5000140,5000141,5000142,5000143,5000145,5000140,5000140,5000141,5000142,5000143,5000145,5000140,5000140,5000141,5000142,5000143,5000145,5000140,5000140,5000141,5000142,5000143,5000145,5000140,5000140,5000141,5000142,5000143,5000145,5000140,5000140,5000141,5000142,5000143,5000145,5000140,5000140,5000141,5000142,5000143,5000145,5000140,5000140,5000141,5000142,5000143,5000145,5000140,5000140,5000141,5000142,5000143,5000145,5000140,5000140,5000141,5000142,5000143,5000145,5000140,5000140,5000141,5000142,5000143,5000145,5000140,5000140,5000141,5000142,5000140,5000140,5000141,5000142,5000140,5000140,5000141,5000142,5000140,5000140,5000141,5000142,5000140,5000140,5000141,5000140,5000140,5000141,5000140,5000140,5000141,5000140,5000140,5000141,5000140,5000140,5000141,5000140,5000140,5000141,5000140,5000140,5000141,5000140,5000140,5000141,5000141,5000141,5000141,5000140,5000140,5000141,5000142,5000143,5000145,5000140,5000140,5000141,5000142,5000143,5000145,5000140,5000140,5000141,5000142,5000143,5000145,5000140,5000140,5000141,5000142,5000143,5000145,5000140,5000140,5000141,5000142,5000143,5000145,5000140,5000140,5000141,5000142,5000143,5000145,5000140,5000140,5000141,5000142,5000143,5000145,5000140,5000140,5000141,5000142,5000143,5000145,5000140,5000140,5000141,5000142,5000143,5000145,5000140,5000140,5000141,5000142,5000143,5000145,5000140,5000140,5000141,5000142,5000143,5000145,5000140,5000140,5000141,5000142,5000143,5000145,5000140,5000140,5000141,5000142,5000140,5000140,5000141,5000142,5000140,5000140,5000141,5000142,5000140,5000140,5000141,5000142,5000140,5000140,5000141,5000140,5000140,5000141,5000140,5000140,5000141,5000140,5000140,5000141,5000140,5000140,5000141,5000140,5000140,5000141,5000140,5000140,5000141,5000140,5000140,5000141,5000141,5000141,5000141</t>
+          <t>5000140,5000140,5000141,5000142,5000143,5000145,5000140,5000140,5000141,5000142,5000143,5000145,5000140,5000140,5000141,5000142,5000143,5000145,5000140,5000140,5000141,5000140,5000142,5000143,5000145,5000140,5000140,5000141,5000142,5000143,5000145,5000140,5000140,5000141,5000142,5000143,5000145,5000140,5000140,5000141,5000142,5000143,5000145,5000140,5000140,5000140,5000141,5000142,5000143,5000145,5000140,5000140,5000141,5000142,5000143,5000145,5000140,5000140,5000141,5000142,5000143,5000145,5000140,5000140,5000141,5000140,5000142,5000143,5000145,5000140,5000140,5000141,5000142,5000143,5000145,5000140,5000140,5000141,5000142,5000140,5000140,5000141,5000142,5000140,5000140,5000141,5000142,5000140,5000140,5000140,5000141,5000142,5000140,5000140,5000141,5000140,5000140,5000141,5000140,5000140,5000141,5000140,5000140,5000141,5000140,5000140,5000141,5000140,5000140,5000140,5000141,5000140,5000140,5000141,5000140,5000140,5000141,5000141,5000141,5000141,5000140,5000140,5000141,5000142,5000143,5000145,5000140,5000140,5000141,5000142,5000143,5000140,5000145,5000140,5000140,5000141,5000142,5000143,5000145,5000140,5000140,5000141,5000142,5000143,5000145,5000140,5000140,5000141,5000142,5000143,5000145,5000140,5000140,5000140,5000141,5000142,5000143,5000145,5000140,5000140,5000141,5000142,5000143,5000145,5000140,5000140,5000141,5000142,5000143,5000145,5000140,5000140,5000141,5000142,5000143,5000140,5000145,5000140,5000140,5000141,5000142,5000143,5000145,5000140,5000140,5000141,5000142,5000143,5000145,5000140,5000140,5000141,5000142,5000143,5000145,5000140,5000140,5000140,5000141,5000142,5000140,5000140,5000141,5000142,5000140,5000140,5000141,5000142,5000140,5000140,5000141,5000142,5000140,5000140,5000141,5000140,5000140,5000141,5000140,5000140,5000140,5000141,5000140,5000140,5000141,5000140,5000140,5000141,5000140,5000140,5000141,5000140,5000140,5000141,5000140,5000140,5000141,5000141,5000141,5000141,5000141,5000140,5000140,5000141,5000142,5000143,5000145,5000140,5000140,5000141,5000142,5000143,5000145,5000140,5000140,5000141,5000142,5000143,5000145,5000140,5000140,5000141,5000141,5000142,5000143,5000145,5000140,5000140,5000141,5000142,5000143,5000145,5000140,5000140,5000141,5000142,5000143,5000145,5000140,5000140,5000141,5000142,5000143,5000145,5000141,5000140,5000140,5000141,5000142,5000143,5000145,5000140,5000140,5000141,5000142,5000143,5000145,5000140,5000140,5000141,5000142,5000143,5000145,5000140,5000140,5000141,5000141,5000142,5000143,5000145,5000140,5000140,5000141,5000142,5000143,5000145,5000140,5000140,5000141,5000142,5000140,5000140,5000141,5000142,5000140,5000140,5000141,5000142,5000141,5000140,5000140,5000141,5000142,5000140,5000140,5000141,5000140,5000140,5000141,5000140,5000140,5000141,5000140,5000140,5000141,5000140,5000140,5000141,5000140,5000140,5000141,5000141,5000140,5000140,5000141,5000140,5000140,5000141,5000141,5000141,5000141,5000140,5000140,5000141,5000142,5000143,5000145,5000140,5000140,5000141,5000142,5000143,5000142,5000145,5000140,5000140,5000141,5000142,5000143,5000145,5000140,5000140,5000141,5000142,5000143,5000145,5000140,5000140,5000141,5000142,5000143,5000145,5000140,5000140,5000142,5000141,5000142,5000143,5000145,5000140,5000140,5000141,5000142,5000143,5000145,5000140,5000140,5000141,5000142,5000143,5000145,5000140,5000140,5000141,5000142,5000143,5000142,5000145,5000140,5000140,5000141,5000142,5000143,5000145,5000140,5000140,5000141,5000142,5000143,5000145,5000140,5000140,5000141,5000142,5000143,5000145,5000140,5000140,5000143,5000141,5000142,5000140,5000140,5000141,5000142,5000140,5000140,5000141,5000142,5000140,5000140,5000141,5000142,5000140,5000140,5000141,5000140,5000140,5000141,5000140,5000143,5000140,5000141,5000140,5000140,5000141,5000140,5000140,5000141,5000140,5000140,5000141,5000140,5000140,5000141,5000140,5000140,5000141,5000141,5000141,5000141</t>
         </is>
       </c>
       <c r="D18" s="3" t="n">
@@ -1463,7 +1463,7 @@
       </c>
       <c r="F18" s="0" t="inlineStr">
         <is>
-          <t>L1 W15/25; N=230; EHP=32479.285768; variants:5 (counts doubled, hp x1.5/x2.0) | wavebuff-20261029</t>
+          <t>L1 W15/25; N=481; EHP=105348.214470 | wavebuff2-20261029 (counts x2 again, hp stacked) | gold20-20261029: killGold=0 | ground5-20261030: ground +21 (5%)</t>
         </is>
       </c>
     </row>
@@ -1473,7 +1473,7 @@
       </c>
       <c r="C19" s="0" t="inlineStr">
         <is>
-          <t>5000150,5000150,5000151,5000152,5000153,5000155,5000150,5000150,5000151,5000152,5000153,5000155,5000150,5000150,5000151,5000152,5000153,5000155,5000150,5000150,5000151,5000152,5000153,5000155,5000150,5000150,5000151,5000152,5000153,5000155,5000150,5000150,5000151,5000152,5000153,5000155,5000150,5000150,5000151,5000152,5000153,5000155,5000150,5000150,5000151,5000152,5000153,5000155,5000150,5000150,5000151,5000152,5000153,5000155,5000150,5000150,5000151,5000152,5000153,5000155,5000150,5000150,5000151,5000152,5000153,5000155,5000150,5000150,5000151,5000152,5000153,5000155,5000150,5000150,5000151,5000152,5000155,5000150,5000150,5000151,5000152,5000150,5000150,5000151,5000152,5000150,5000150,5000151,5000152,5000150,5000150,5000151,5000152,5000150,5000150,5000151,5000150,5000150,5000151,5000150,5000150,5000151,5000150,5000150,5000151,5000150,5000150,5000151,5000150,5000150,5000151,5000150,5000150,5000151,5000150,5000150,5000151,5000151,5000151,5000151,5000151,5000150,5000150,5000151,5000152,5000153,5000155,5000150,5000150,5000151,5000152,5000153,5000155,5000150,5000150,5000151,5000152,5000153,5000155,5000150,5000150,5000151,5000152,5000153,5000155,5000150,5000150,5000151,5000152,5000153,5000155,5000150,5000150,5000151,5000152,5000153,5000155,5000150,5000150,5000151,5000152,5000153,5000155,5000150,5000150,5000151,5000152,5000153,5000155,5000150,5000150,5000151,5000152,5000153,5000155,5000150,5000150,5000151,5000152,5000153,5000155,5000150,5000150,5000151,5000152,5000153,5000155,5000150,5000150,5000151,5000152,5000153,5000155,5000150,5000150,5000151,5000152,5000155,5000150,5000150,5000151,5000152,5000150,5000150,5000151,5000152,5000150,5000150,5000151,5000152,5000150,5000150,5000151,5000152,5000150,5000150,5000151,5000150,5000150,5000151,5000150,5000150,5000151,5000150,5000150,5000151,5000150,5000150,5000151,5000150,5000150,5000151,5000150,5000150,5000151,5000150,5000150,5000151,5000151,5000151,5000151,5000151</t>
+          <t>5000150,5000150,5000151,5000152,5000153,5000155,5000150,5000150,5000151,5000152,5000153,5000155,5000150,5000150,5000151,5000152,5000153,5000155,5000150,5000150,5000151,5000152,5000150,5000153,5000155,5000150,5000150,5000151,5000152,5000153,5000155,5000150,5000150,5000151,5000152,5000153,5000155,5000150,5000150,5000151,5000152,5000153,5000155,5000150,5000150,5000150,5000151,5000152,5000153,5000155,5000150,5000150,5000151,5000152,5000153,5000155,5000150,5000150,5000151,5000152,5000153,5000155,5000150,5000150,5000151,5000152,5000150,5000153,5000155,5000150,5000150,5000151,5000152,5000153,5000155,5000150,5000150,5000151,5000152,5000155,5000150,5000150,5000151,5000152,5000150,5000150,5000151,5000152,5000150,5000150,5000150,5000151,5000152,5000150,5000150,5000151,5000152,5000150,5000150,5000151,5000150,5000150,5000151,5000150,5000150,5000151,5000150,5000150,5000151,5000150,5000150,5000150,5000151,5000150,5000150,5000151,5000150,5000150,5000151,5000150,5000150,5000151,5000151,5000151,5000151,5000151,5000150,5000150,5000151,5000152,5000153,5000155,5000150,5000150,5000150,5000151,5000152,5000153,5000155,5000150,5000150,5000151,5000152,5000153,5000155,5000150,5000150,5000151,5000152,5000153,5000155,5000150,5000150,5000151,5000150,5000152,5000153,5000155,5000150,5000150,5000151,5000152,5000153,5000155,5000150,5000150,5000151,5000152,5000153,5000155,5000150,5000150,5000151,5000152,5000153,5000155,5000150,5000150,5000150,5000151,5000152,5000153,5000155,5000150,5000150,5000151,5000152,5000153,5000155,5000150,5000150,5000151,5000152,5000153,5000155,5000150,5000150,5000151,5000150,5000152,5000153,5000155,5000150,5000150,5000151,5000152,5000155,5000150,5000150,5000151,5000152,5000150,5000150,5000151,5000152,5000150,5000150,5000151,5000152,5000150,5000150,5000150,5000151,5000152,5000150,5000150,5000151,5000150,5000150,5000151,5000150,5000150,5000151,5000150,5000150,5000151,5000150,5000150,5000151,5000150,5000150,5000151,5000151,5000150,5000150,5000151,5000150,5000150,5000151,5000151,5000151,5000151,5000151,5000150,5000150,5000151,5000152,5000153,5000155,5000150,5000150,5000151,5000152,5000153,5000151,5000155,5000150,5000150,5000151,5000152,5000153,5000155,5000150,5000150,5000151,5000152,5000153,5000155,5000150,5000150,5000151,5000152,5000153,5000155,5000150,5000150,5000151,5000151,5000152,5000153,5000155,5000150,5000150,5000151,5000152,5000153,5000155,5000150,5000150,5000151,5000152,5000153,5000155,5000150,5000150,5000151,5000152,5000153,5000151,5000155,5000150,5000150,5000151,5000152,5000153,5000155,5000150,5000150,5000151,5000152,5000153,5000155,5000150,5000150,5000151,5000152,5000153,5000155,5000150,5000150,5000151,5000151,5000152,5000155,5000150,5000150,5000151,5000152,5000150,5000150,5000151,5000152,5000150,5000150,5000151,5000152,5000150,5000150,5000151,5000152,5000150,5000150,5000151,5000151,5000150,5000150,5000151,5000150,5000150,5000151,5000150,5000150,5000151,5000150,5000150,5000151,5000150,5000150,5000151,5000150,5000150,5000151,5000150,5000150,5000152,5000151,5000151,5000151,5000151,5000151,5000150,5000150,5000151,5000152,5000153,5000155,5000150,5000150,5000151,5000152,5000153,5000155,5000150,5000150,5000151,5000152,5000152,5000153,5000155,5000150,5000150,5000151,5000152,5000153,5000155,5000150,5000150,5000151,5000152,5000153,5000155,5000150,5000150,5000151,5000152,5000153,5000155,5000150,5000152,5000150,5000151,5000152,5000153,5000155,5000150,5000150,5000151,5000152,5000153,5000155,5000150,5000150,5000151,5000152,5000153,5000155,5000150,5000150,5000151,5000152,5000152,5000153,5000155,5000150,5000150,5000151,5000152,5000153,5000155,5000150,5000150,5000151,5000152,5000153,5000155,5000150,5000150,5000151,5000152,5000155,5000150,5000150,5000153,5000151,5000152,5000150,5000150,5000151,5000152,5000150,5000150,5000151,5000152,5000150,5000150,5000151,5000152,5000150,5000150,5000151,5000150,5000150,5000151,5000150,5000153,5000150,5000151,5000150,5000150,5000151,5000150,5000150,5000151,5000150,5000150,5000151,5000150,5000150,5000151,5000150,5000150,5000151,5000151,5000151,5000151,5000151</t>
         </is>
       </c>
       <c r="D19" s="3" t="n">
@@ -1484,7 +1484,7 @@
       </c>
       <c r="F19" s="0" t="inlineStr">
         <is>
-          <t>L1 W16/25; N=242; EHP=33173.979189; variants:5 (counts doubled, hp x1.5/x2.0) | wavebuff-20261029</t>
+          <t>L1 W16/25; N=506; EHP=107875.827726 | wavebuff2-20261029 (counts x2 again, hp stacked) | gold20-20261029: killGold=200 | ground5-20261030: ground +22 (5%)</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="C20" s="0" t="inlineStr">
         <is>
-          <t>5000160,5000160,5000161,5000162,5000163,5000165,5000160,5000160,5000161,5000162,5000163,5000165,5000160,5000160,5000161,5000162,5000163,5000165,5000160,5000160,5000161,5000162,5000163,5000165,5000160,5000160,5000161,5000162,5000163,5000165,5000160,5000160,5000161,5000162,5000163,5000165,5000160,5000160,5000161,5000162,5000163,5000165,5000160,5000160,5000161,5000162,5000163,5000165,5000160,5000160,5000161,5000162,5000163,5000165,5000160,5000160,5000161,5000162,5000163,5000165,5000160,5000160,5000161,5000162,5000163,5000165,5000160,5000160,5000161,5000162,5000163,5000165,5000160,5000160,5000161,5000162,5000163,5000165,5000160,5000160,5000161,5000162,5000165,5000160,5000160,5000161,5000162,5000160,5000160,5000161,5000162,5000160,5000160,5000161,5000162,5000160,5000160,5000161,5000162,5000160,5000160,5000161,5000160,5000160,5000161,5000160,5000160,5000161,5000160,5000160,5000161,5000160,5000160,5000161,5000160,5000160,5000161,5000160,5000160,5000161,5000160,5000160,5000161,5000161,5000161,5000161,5000161,5000160,5000160,5000161,5000162,5000163,5000165,5000160,5000160,5000161,5000162,5000163,5000165,5000160,5000160,5000161,5000162,5000163,5000165,5000160,5000160,5000161,5000162,5000163,5000165,5000160,5000160,5000161,5000162,5000163,5000165,5000160,5000160,5000161,5000162,5000163,5000165,5000160,5000160,5000161,5000162,5000163,5000165,5000160,5000160,5000161,5000162,5000163,5000165,5000160,5000160,5000161,5000162,5000163,5000165,5000160,5000160,5000161,5000162,5000163,5000165,5000160,5000160,5000161,5000162,5000163,5000165,5000160,5000160,5000161,5000162,5000163,5000165,5000160,5000160,5000161,5000162,5000163,5000165,5000160,5000160,5000161,5000162,5000165,5000160,5000160,5000161,5000162,5000160,5000160,5000161,5000162,5000160,5000160,5000161,5000162,5000160,5000160,5000161,5000162,5000160,5000160,5000161,5000160,5000160,5000161,5000160,5000160,5000161,5000160,5000160,5000161,5000160,5000160,5000161,5000160,5000160,5000161,5000160,5000160,5000161,5000160,5000160,5000161,5000161,5000161,5000161,5000161</t>
+          <t>5000160,5000160,5000161,5000162,5000163,5000165,5000160,5000160,5000161,5000162,5000163,5000165,5000160,5000160,5000161,5000162,5000163,5000165,5000160,5000160,5000161,5000162,5000160,5000163,5000165,5000160,5000160,5000161,5000162,5000163,5000165,5000160,5000160,5000161,5000162,5000163,5000165,5000160,5000160,5000161,5000162,5000163,5000165,5000160,5000160,5000160,5000161,5000162,5000163,5000165,5000160,5000160,5000161,5000162,5000163,5000165,5000160,5000160,5000161,5000162,5000163,5000165,5000160,5000160,5000161,5000162,5000160,5000163,5000165,5000160,5000160,5000161,5000162,5000163,5000165,5000160,5000160,5000161,5000162,5000163,5000165,5000160,5000160,5000161,5000162,5000165,5000160,5000160,5000160,5000161,5000162,5000160,5000160,5000161,5000162,5000160,5000160,5000161,5000162,5000160,5000160,5000161,5000162,5000160,5000160,5000161,5000160,5000160,5000161,5000160,5000160,5000160,5000161,5000160,5000160,5000161,5000160,5000160,5000161,5000160,5000160,5000161,5000160,5000160,5000161,5000160,5000160,5000161,5000161,5000161,5000161,5000161,5000160,5000160,5000160,5000161,5000162,5000163,5000165,5000160,5000160,5000161,5000162,5000163,5000165,5000160,5000160,5000161,5000162,5000163,5000165,5000160,5000160,5000161,5000162,5000160,5000163,5000165,5000160,5000160,5000161,5000162,5000163,5000165,5000160,5000160,5000161,5000162,5000163,5000165,5000160,5000160,5000161,5000162,5000163,5000165,5000160,5000160,5000160,5000161,5000162,5000163,5000165,5000160,5000160,5000161,5000162,5000163,5000165,5000160,5000160,5000161,5000162,5000163,5000165,5000160,5000160,5000161,5000162,5000160,5000163,5000165,5000160,5000160,5000161,5000162,5000163,5000165,5000160,5000160,5000161,5000162,5000163,5000165,5000160,5000160,5000161,5000162,5000165,5000160,5000160,5000160,5000161,5000162,5000160,5000160,5000161,5000162,5000160,5000160,5000161,5000162,5000160,5000160,5000161,5000162,5000160,5000160,5000161,5000160,5000160,5000161,5000160,5000161,5000160,5000161,5000160,5000160,5000161,5000160,5000160,5000161,5000160,5000160,5000161,5000160,5000160,5000161,5000160,5000160,5000161,5000161,5000161,5000161,5000161,5000161,5000160,5000160,5000161,5000162,5000163,5000165,5000160,5000160,5000161,5000162,5000163,5000165,5000160,5000160,5000161,5000162,5000163,5000165,5000160,5000160,5000161,5000162,5000161,5000163,5000165,5000160,5000160,5000161,5000162,5000163,5000165,5000160,5000160,5000161,5000162,5000163,5000165,5000160,5000160,5000161,5000162,5000163,5000165,5000160,5000161,5000160,5000161,5000162,5000163,5000165,5000160,5000160,5000161,5000162,5000163,5000165,5000160,5000160,5000161,5000162,5000163,5000165,5000160,5000160,5000161,5000162,5000161,5000163,5000165,5000160,5000160,5000161,5000162,5000163,5000165,5000160,5000160,5000161,5000162,5000163,5000165,5000160,5000160,5000161,5000162,5000165,5000160,5000160,5000161,5000161,5000162,5000160,5000160,5000161,5000162,5000160,5000160,5000161,5000162,5000160,5000160,5000161,5000162,5000160,5000160,5000161,5000160,5000160,5000161,5000160,5000162,5000160,5000161,5000160,5000160,5000161,5000160,5000160,5000161,5000160,5000160,5000161,5000160,5000160,5000161,5000160,5000160,5000161,5000161,5000161,5000161,5000161,5000162,5000160,5000160,5000161,5000162,5000163,5000165,5000160,5000160,5000161,5000162,5000163,5000165,5000160,5000160,5000161,5000162,5000163,5000165,5000160,5000160,5000161,5000162,5000162,5000163,5000165,5000160,5000160,5000161,5000162,5000163,5000165,5000160,5000160,5000161,5000162,5000163,5000165,5000160,5000160,5000161,5000162,5000163,5000165,5000160,5000162,5000160,5000161,5000162,5000163,5000165,5000160,5000160,5000161,5000162,5000163,5000165,5000160,5000160,5000161,5000162,5000163,5000165,5000160,5000160,5000161,5000162,5000163,5000163,5000165,5000160,5000160,5000161,5000162,5000163,5000165,5000160,5000160,5000161,5000162,5000163,5000165,5000160,5000160,5000161,5000162,5000165,5000160,5000160,5000163,5000161,5000162,5000160,5000160,5000161,5000162,5000160,5000160,5000161,5000162,5000160,5000160,5000161,5000162,5000160,5000160,5000161,5000160,5000160,5000161,5000160,5000163,5000160,5000161,5000160,5000160,5000161,5000160,5000160,5000161,5000160,5000160,5000161,5000160,5000160,5000161,5000160,5000160,5000161,5000161,5000161,5000161,5000161</t>
         </is>
       </c>
       <c r="D20" s="3" t="n">
@@ -1505,7 +1505,7 @@
       </c>
       <c r="F20" s="0" t="inlineStr">
         <is>
-          <t>L1 W17/25; N=254; EHP=33840.828765; variants:5 (counts doubled, hp x1.5/x2.0) | wavebuff-20261029</t>
+          <t>L1 W17/25; N=531; EHP=110419.889399 | wavebuff2-20261029 (counts x2 again, hp stacked) | gold20-20261029: killGold=0 | ground5-20261030: ground +23 (5%)</t>
         </is>
       </c>
     </row>
@@ -1515,7 +1515,7 @@
       </c>
       <c r="C21" s="0" t="inlineStr">
         <is>
-          <t>5000170,5000170,5000171,5000172,5000173,5000175,5000170,5000170,5000171,5000172,5000173,5000175,5000170,5000170,5000171,5000172,5000173,5000175,5000170,5000170,5000171,5000172,5000173,5000175,5000170,5000170,5000171,5000172,5000173,5000175,5000170,5000170,5000171,5000172,5000173,5000175,5000170,5000170,5000171,5000172,5000173,5000175,5000170,5000170,5000171,5000172,5000173,5000175,5000170,5000170,5000171,5000172,5000173,5000175,5000170,5000170,5000171,5000172,5000173,5000175,5000170,5000170,5000171,5000172,5000173,5000175,5000170,5000170,5000171,5000172,5000173,5000175,5000170,5000170,5000171,5000172,5000173,5000175,5000170,5000170,5000171,5000172,5000173,5000175,5000170,5000170,5000171,5000172,5000175,5000170,5000170,5000171,5000172,5000170,5000170,5000171,5000172,5000170,5000170,5000171,5000172,5000170,5000170,5000171,5000170,5000170,5000171,5000170,5000170,5000171,5000170,5000170,5000171,5000170,5000170,5000171,5000170,5000170,5000171,5000170,5000170,5000171,5000170,5000170,5000171,5000170,5000170,5000171,5000170,5000171,5000171,5000171,5000171,5000170,5000170,5000171,5000172,5000173,5000175,5000170,5000170,5000171,5000172,5000173,5000175,5000170,5000170,5000171,5000172,5000173,5000175,5000170,5000170,5000171,5000172,5000173,5000175,5000170,5000170,5000171,5000172,5000173,5000175,5000170,5000170,5000171,5000172,5000173,5000175,5000170,5000170,5000171,5000172,5000173,5000175,5000170,5000170,5000171,5000172,5000173,5000175,5000170,5000170,5000171,5000172,5000173,5000175,5000170,5000170,5000171,5000172,5000173,5000175,5000170,5000170,5000171,5000172,5000173,5000175,5000170,5000170,5000171,5000172,5000173,5000175,5000170,5000170,5000171,5000172,5000173,5000175,5000170,5000170,5000171,5000172,5000173,5000175,5000170,5000170,5000171,5000172,5000175,5000170,5000170,5000171,5000172,5000170,5000170,5000171,5000172,5000170,5000170,5000171,5000172,5000170,5000170,5000171,5000170,5000170,5000171,5000170,5000170,5000171,5000170,5000170,5000171,5000170,5000170,5000171,5000170,5000170,5000171,5000170,5000170,5000171,5000170,5000170,5000171,5000170,5000170,5000171,5000170,5000171,5000171,5000171,5000171</t>
+          <t>5000170,5000170,5000171,5000172,5000173,5000175,5000170,5000170,5000171,5000172,5000173,5000175,5000170,5000170,5000171,5000172,5000173,5000175,5000170,5000170,5000171,5000172,5000170,5000173,5000175,5000170,5000170,5000171,5000172,5000173,5000175,5000170,5000170,5000171,5000172,5000173,5000175,5000170,5000170,5000171,5000172,5000173,5000175,5000170,5000170,5000170,5000171,5000172,5000173,5000175,5000170,5000170,5000171,5000172,5000173,5000175,5000170,5000170,5000171,5000172,5000173,5000175,5000170,5000170,5000171,5000172,5000170,5000173,5000175,5000170,5000170,5000171,5000172,5000173,5000175,5000170,5000170,5000171,5000172,5000173,5000175,5000170,5000170,5000171,5000172,5000173,5000175,5000170,5000170,5000170,5000171,5000172,5000175,5000170,5000170,5000171,5000172,5000170,5000170,5000171,5000172,5000170,5000170,5000171,5000172,5000170,5000170,5000171,5000170,5000170,5000171,5000170,5000170,5000170,5000171,5000170,5000170,5000171,5000170,5000170,5000171,5000170,5000170,5000171,5000170,5000170,5000171,5000170,5000170,5000171,5000170,5000170,5000171,5000170,5000170,5000171,5000171,5000171,5000171,5000170,5000170,5000171,5000172,5000173,5000175,5000170,5000170,5000171,5000172,5000173,5000175,5000170,5000170,5000171,5000172,5000170,5000173,5000175,5000170,5000170,5000171,5000172,5000173,5000175,5000170,5000170,5000171,5000172,5000173,5000175,5000170,5000170,5000171,5000172,5000173,5000175,5000170,5000170,5000170,5000171,5000172,5000173,5000175,5000170,5000170,5000171,5000172,5000173,5000175,5000170,5000170,5000171,5000172,5000173,5000175,5000170,5000170,5000171,5000172,5000173,5000170,5000175,5000170,5000170,5000171,5000172,5000173,5000175,5000170,5000170,5000171,5000172,5000173,5000175,5000170,5000170,5000171,5000172,5000173,5000175,5000170,5000170,5000170,5000171,5000172,5000173,5000175,5000170,5000170,5000171,5000172,5000175,5000170,5000170,5000171,5000172,5000170,5000170,5000171,5000172,5000170,5000170,5000171,5000172,5000170,5000170,5000170,5000171,5000170,5000170,5000171,5000170,5000170,5000171,5000170,5000170,5000171,5000170,5000170,5000171,5000170,5000170,5000171,5000170,5000170,5000171,5000170,5000171,5000170,5000171,5000170,5000170,5000171,5000170,5000171,5000171,5000171,5000171,5000170,5000170,5000171,5000172,5000173,5000175,5000170,5000170,5000171,5000172,5000173,5000171,5000175,5000170,5000170,5000171,5000172,5000173,5000175,5000170,5000170,5000171,5000172,5000173,5000175,5000170,5000170,5000171,5000172,5000173,5000175,5000170,5000170,5000171,5000171,5000172,5000173,5000175,5000170,5000170,5000171,5000172,5000173,5000175,5000170,5000170,5000171,5000172,5000173,5000175,5000170,5000170,5000171,5000172,5000173,5000175,5000171,5000170,5000170,5000171,5000172,5000173,5000175,5000170,5000170,5000171,5000172,5000173,5000175,5000170,5000170,5000171,5000172,5000173,5000175,5000170,5000170,5000171,5000171,5000172,5000173,5000175,5000170,5000170,5000171,5000172,5000173,5000175,5000170,5000170,5000171,5000172,5000175,5000170,5000170,5000171,5000172,5000170,5000170,5000171,5000171,5000172,5000170,5000170,5000171,5000172,5000170,5000170,5000171,5000170,5000170,5000171,5000170,5000170,5000171,5000170,5000170,5000171,5000170,5000170,5000171,5000170,5000170,5000172,5000171,5000170,5000170,5000171,5000170,5000170,5000171,5000170,5000170,5000171,5000170,5000171,5000171,5000171,5000171,5000170,5000170,5000171,5000172,5000173,5000175,5000172,5000170,5000170,5000171,5000172,5000173,5000175,5000170,5000170,5000171,5000172,5000173,5000175,5000170,5000170,5000171,5000172,5000173,5000175,5000170,5000170,5000171,5000172,5000172,5000173,5000175,5000170,5000170,5000171,5000172,5000173,5000175,5000170,5000170,5000171,5000172,5000173,5000175,5000170,5000170,5000171,5000172,5000173,5000175,5000172,5000170,5000170,5000171,5000172,5000173,5000175,5000170,5000170,5000171,5000172,5000173,5000175,5000170,5000170,5000171,5000172,5000173,5000175,5000170,5000170,5000171,5000172,5000173,5000173,5000175,5000170,5000170,5000171,5000172,5000173,5000175,5000170,5000170,5000171,5000172,5000173,5000175,5000170,5000170,5000171,5000172,5000175,5000170,5000170,5000173,5000171,5000172,5000170,5000170,5000171,5000172,5000170,5000170,5000171,5000172,5000170,5000170,5000171,5000170,5000170,5000171,5000170,5000170,5000171,5000170,5000170,5000173,5000171,5000170,5000170,5000171,5000170,5000170,5000171,5000170,5000170,5000171,5000170,5000170,5000171,5000170,5000170,5000171,5000170,5000171,5000171,5000171,5000171</t>
         </is>
       </c>
       <c r="D21" s="3" t="n">
@@ -1526,7 +1526,7 @@
       </c>
       <c r="F21" s="0" t="inlineStr">
         <is>
-          <t>L1 W18/25; N=266; EHP=36200.289405; variants:5 (counts doubled, hp x1.5/x2.0) | wavebuff-20261029</t>
+          <t>L1 W18/25; N=556; EHP=118103.089258 | wavebuff2-20261029 (counts x2 again, hp stacked) | gold20-20261029: killGold=0 | ground5-20261030: ground +24 (5%)</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C22" s="0" t="inlineStr">
         <is>
-          <t>5000180,5000180,5000181,5000182,5000183,5000185,5000180,5000180,5000181,5000182,5000183,5000185,5000180,5000180,5000181,5000182,5000183,5000185,5000180,5000180,5000181,5000182,5000183,5000185,5000180,5000180,5000181,5000182,5000183,5000185,5000180,5000180,5000181,5000182,5000183,5000185,5000180,5000180,5000181,5000182,5000183,5000185,5000180,5000180,5000181,5000182,5000183,5000185,5000180,5000180,5000181,5000182,5000183,5000185,5000180,5000180,5000181,5000182,5000183,5000185,5000180,5000180,5000181,5000182,5000183,5000185,5000180,5000180,5000181,5000182,5000183,5000185,5000180,5000180,5000181,5000182,5000183,5000185,5000180,5000180,5000181,5000182,5000183,5000185,5000180,5000180,5000181,5000182,5000185,5000180,5000180,5000181,5000182,5000185,5000180,5000180,5000181,5000182,5000180,5000180,5000181,5000182,5000180,5000180,5000181,5000182,5000180,5000180,5000181,5000180,5000180,5000181,5000180,5000180,5000181,5000180,5000180,5000181,5000180,5000180,5000181,5000180,5000180,5000181,5000180,5000180,5000181,5000180,5000180,5000181,5000180,5000180,5000181,5000180,5000181,5000181,5000181,5000181,5000181,5000180,5000180,5000181,5000182,5000183,5000185,5000180,5000180,5000181,5000182,5000183,5000185,5000180,5000180,5000181,5000182,5000183,5000185,5000180,5000180,5000181,5000182,5000183,5000185,5000180,5000180,5000181,5000182,5000183,5000185,5000180,5000180,5000181,5000182,5000183,5000185,5000180,5000180,5000181,5000182,5000183,5000185,5000180,5000180,5000181,5000182,5000183,5000185,5000180,5000180,5000181,5000182,5000183,5000185,5000180,5000180,5000181,5000182,5000183,5000185,5000180,5000180,5000181,5000182,5000183,5000185,5000180,5000180,5000181,5000182,5000183,5000185,5000180,5000180,5000181,5000182,5000183,5000185,5000180,5000180,5000181,5000182,5000183,5000185,5000180,5000180,5000181,5000182,5000185,5000180,5000180,5000181,5000182,5000185,5000180,5000180,5000181,5000182,5000180,5000180,5000181,5000182,5000180,5000180,5000181,5000182,5000180,5000180,5000181,5000180,5000180,5000181,5000180,5000180,5000181,5000180,5000180,5000181,5000180,5000180,5000181,5000180,5000180,5000181,5000180,5000180,5000181,5000180,5000180,5000181,5000180,5000180,5000181,5000180,5000181,5000181,5000181,5000181,5000181</t>
+          <t>5000180,5000180,5000181,5000182,5000183,5000185,5000180,5000180,5000181,5000182,5000183,5000185,5000180,5000180,5000181,5000182,5000183,5000185,5000180,5000180,5000181,5000182,5000180,5000183,5000185,5000180,5000180,5000181,5000182,5000183,5000185,5000180,5000180,5000181,5000182,5000183,5000185,5000180,5000180,5000181,5000182,5000183,5000185,5000180,5000180,5000180,5000181,5000182,5000183,5000185,5000180,5000180,5000181,5000182,5000183,5000185,5000180,5000180,5000181,5000182,5000183,5000185,5000180,5000180,5000181,5000182,5000183,5000180,5000185,5000180,5000180,5000181,5000182,5000183,5000185,5000180,5000180,5000181,5000182,5000183,5000185,5000180,5000180,5000181,5000182,5000183,5000185,5000180,5000180,5000180,5000181,5000182,5000185,5000180,5000180,5000181,5000182,5000185,5000180,5000180,5000181,5000182,5000180,5000180,5000181,5000182,5000180,5000180,5000181,5000182,5000180,5000180,5000180,5000181,5000180,5000180,5000181,5000180,5000180,5000181,5000180,5000180,5000181,5000180,5000180,5000181,5000180,5000180,5000181,5000180,5000180,5000181,5000180,5000180,5000180,5000181,5000180,5000180,5000181,5000180,5000181,5000181,5000181,5000181,5000181,5000180,5000180,5000181,5000182,5000183,5000185,5000180,5000180,5000181,5000182,5000183,5000180,5000185,5000180,5000180,5000181,5000182,5000183,5000185,5000180,5000180,5000181,5000182,5000183,5000185,5000180,5000180,5000181,5000182,5000183,5000185,5000180,5000180,5000181,5000180,5000182,5000183,5000185,5000180,5000180,5000181,5000182,5000183,5000185,5000180,5000180,5000181,5000182,5000183,5000185,5000180,5000180,5000181,5000182,5000183,5000185,5000180,5000180,5000180,5000181,5000182,5000183,5000185,5000180,5000180,5000181,5000182,5000183,5000185,5000180,5000180,5000181,5000182,5000183,5000185,5000180,5000180,5000181,5000180,5000182,5000183,5000185,5000180,5000180,5000181,5000182,5000183,5000185,5000180,5000180,5000181,5000182,5000185,5000180,5000180,5000181,5000182,5000185,5000180,5000180,5000181,5000180,5000182,5000180,5000180,5000181,5000182,5000180,5000180,5000181,5000182,5000180,5000180,5000181,5000180,5000180,5000181,5000180,5000180,5000181,5000180,5000180,5000181,5000181,5000180,5000180,5000181,5000180,5000180,5000181,5000180,5000180,5000181,5000180,5000180,5000181,5000180,5000180,5000181,5000180,5000181,5000181,5000181,5000181,5000181,5000181,5000180,5000180,5000181,5000182,5000183,5000185,5000180,5000180,5000181,5000182,5000183,5000185,5000180,5000180,5000181,5000182,5000183,5000185,5000180,5000180,5000181,5000182,5000181,5000183,5000185,5000180,5000180,5000181,5000182,5000183,5000185,5000180,5000180,5000181,5000182,5000183,5000185,5000180,5000180,5000181,5000182,5000183,5000185,5000180,5000181,5000180,5000181,5000182,5000183,5000185,5000180,5000180,5000181,5000182,5000183,5000185,5000180,5000180,5000181,5000182,5000183,5000185,5000180,5000180,5000181,5000182,5000183,5000181,5000185,5000180,5000180,5000181,5000182,5000183,5000185,5000180,5000180,5000181,5000182,5000183,5000185,5000180,5000180,5000181,5000182,5000183,5000185,5000180,5000180,5000181,5000181,5000182,5000185,5000180,5000180,5000181,5000182,5000185,5000180,5000180,5000181,5000182,5000180,5000180,5000181,5000182,5000180,5000180,5000181,5000182,5000180,5000181,5000180,5000181,5000180,5000180,5000181,5000180,5000180,5000181,5000180,5000180,5000181,5000180,5000180,5000181,5000180,5000180,5000181,5000180,5000180,5000181,5000180,5000180,5000182,5000181,5000180,5000180,5000181,5000180,5000181,5000181,5000181,5000181,5000181,5000180,5000180,5000181,5000182,5000183,5000185,5000180,5000180,5000181,5000182,5000183,5000182,5000185,5000180,5000180,5000181,5000182,5000183,5000185,5000180,5000180,5000181,5000182,5000183,5000185,5000180,5000180,5000181,5000182,5000183,5000185,5000180,5000180,5000181,5000182,5000182,5000183,5000185,5000180,5000180,5000181,5000182,5000183,5000185,5000180,5000180,5000181,5000182,5000183,5000185,5000180,5000180,5000181,5000182,5000183,5000185,5000182,5000180,5000180,5000181,5000182,5000183,5000185,5000180,5000180,5000181,5000182,5000183,5000185,5000180,5000180,5000181,5000182,5000183,5000185,5000180,5000180,5000181,5000183,5000182,5000183,5000185,5000180,5000180,5000181,5000182,5000183,5000185,5000180,5000180,5000181,5000182,5000185,5000180,5000180,5000181,5000182,5000185,5000180,5000180,5000181,5000183,5000182,5000180,5000180,5000181,5000182,5000180,5000180,5000181,5000182,5000180,5000180,5000181,5000180,5000180,5000181,5000180,5000180,5000181,5000180,5000180,5000181,5000183,5000180,5000180,5000181,5000180,5000180,5000181,5000180,5000180,5000181,5000180,5000180,5000181,5000180,5000180,5000181,5000180,5000181,5000181,5000181,5000181,5000181</t>
         </is>
       </c>
       <c r="D22" s="3" t="n">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="F22" s="0" t="inlineStr">
         <is>
-          <t>L1 W19/25; N=278; EHP=41973.372707; variants:5 (counts doubled, hp x1.5/x2.0) | wavebuff-20261029</t>
+          <t>L1 W19/25; N=581; EHP=136996.277523 | wavebuff2-20261029 (counts x2 again, hp stacked) | gold20-20261029: killGold=0 | ground5-20261030: ground +25 (5%)</t>
         </is>
       </c>
     </row>
@@ -1557,18 +1557,18 @@
       </c>
       <c r="C23" s="0" t="inlineStr">
         <is>
-          <t>5000190,5000190,5000191,5000192,5000193,5000195,5000190,5000190,5000191,5000192,5000193,5000195,5000190,5000190,5000191,5000192,5000193,5000195,5000190,5000190,5000191,5000192,5000193,5000195,5000190,5000190,5000191,5000192,5000193,5000195,5000190,5000190,5000191,5000192,5000193,5000195,5000190,5000190,5000191,5000192,5000193,5000195,5000190,5000190,5000191,5000192,5000193,5000195,5000190,5000190,5000191,5000192,5000193,5000195,5000190,5000190,5000191,5000192,5000193,5000195,5000190,5000190,5000191,5000192,5000193,5000195,5000190,5000190,5000191,5000192,5000193,5000195,5000190,5000190,5000191,5000192,5000193,5000195,5000190,5000190,5000191,5000192,5000193,5000195,5000190,5000190,5000191,5000192,5000193,5000195,5000190,5000190,5000191,5000192,5000195,5000190,5000190,5000191,5000192,5000195,5000190,5000190,5000191,5000192,5000190,5000190,5000191,5000192,5000190,5000190,5000191,5000192,5000190,5000190,5000191,5000190,5000190,5000191,5000190,5000190,5000191,5000190,5000190,5000191,5000190,5000190,5000191,5000190,5000190,5000191,5000190,5000190,5000191,5000190,5000190,5000191,5000190,5000190,5000191,5000190,5000191,5000191,5000191,5000191,5000191,5000190,5000190,5000191,5000192,5000193,5000195,5000190,5000190,5000191,5000192,5000193,5000195,5000190,5000190,5000191,5000192,5000193,5000195,5000190,5000190,5000191,5000192,5000193,5000195,5000190,5000190,5000191,5000192,5000193,5000195,5000190,5000190,5000191,5000192,5000193,5000195,5000190,5000190,5000191,5000192,5000193,5000195,5000190,5000190,5000191,5000192,5000193,5000195,5000190,5000190,5000191,5000192,5000193,5000195,5000190,5000190,5000191,5000192,5000193,5000195,5000190,5000190,5000191,5000192,5000193,5000195,5000190,5000190,5000191,5000192,5000193,5000195,5000190,5000190,5000191,5000192,5000193,5000195,5000190,5000190,5000191,5000192,5000193,5000195,5000190,5000190,5000191,5000192,5000193,5000195,5000190,5000190,5000191,5000192,5000195,5000190,5000190,5000191,5000192,5000195,5000190,5000190,5000191,5000192,5000190,5000190,5000191,5000192,5000190,5000190,5000191,5000192,5000190,5000190,5000191,5000190,5000190,5000191,5000190,5000190,5000191,5000190,5000190,5000191,5000190,5000190,5000191,5000190,5000190,5000191,5000190,5000190,5000191,5000190,5000190,5000191,5000190,5000190,5000191,5000190,5000191,5000191,5000191,5000191,5000191</t>
+          <t>5000190,5000190,5000191,5000192,5000193,5000195,5000190,5000190,5000191,5000192,5000193,5000195,5000190,5000190,5000191,5000192,5000193,5000195,5000190,5000190,5000191,5000192,5000190,5000193,5000195,5000190,5000190,5000191,5000192,5000193,5000195,5000190,5000190,5000191,5000192,5000193,5000195,5000190,5000190,5000191,5000192,5000193,5000195,5000190,5000190,5000190,5000191,5000192,5000193,5000195,5000190,5000190,5000191,5000192,5000193,5000195,5000190,5000190,5000191,5000192,5000193,5000195,5000190,5000190,5000191,5000192,5000193,5000190,5000195,5000190,5000190,5000191,5000192,5000193,5000195,5000190,5000190,5000191,5000192,5000193,5000195,5000190,5000190,5000191,5000192,5000193,5000195,5000190,5000190,5000190,5000191,5000192,5000193,5000195,5000190,5000190,5000191,5000192,5000195,5000190,5000190,5000191,5000192,5000195,5000190,5000190,5000191,5000192,5000190,5000190,5000191,5000192,5000190,5000190,5000190,5000191,5000192,5000190,5000190,5000191,5000190,5000190,5000191,5000190,5000190,5000191,5000190,5000190,5000191,5000190,5000190,5000191,5000190,5000190,5000190,5000191,5000190,5000190,5000191,5000190,5000190,5000191,5000190,5000190,5000191,5000190,5000191,5000191,5000191,5000191,5000191,5000190,5000190,5000191,5000192,5000193,5000195,5000190,5000190,5000190,5000191,5000192,5000193,5000195,5000190,5000190,5000191,5000192,5000193,5000195,5000190,5000190,5000191,5000192,5000193,5000195,5000190,5000190,5000191,5000190,5000192,5000193,5000195,5000190,5000190,5000191,5000192,5000193,5000195,5000190,5000190,5000191,5000192,5000193,5000195,5000190,5000190,5000191,5000192,5000193,5000195,5000190,5000190,5000190,5000191,5000192,5000193,5000195,5000190,5000190,5000191,5000192,5000193,5000195,5000190,5000190,5000191,5000192,5000193,5000195,5000190,5000190,5000191,5000192,5000190,5000193,5000195,5000190,5000190,5000191,5000192,5000193,5000195,5000190,5000190,5000191,5000192,5000193,5000195,5000190,5000190,5000191,5000192,5000193,5000195,5000190,5000190,5000190,5000191,5000192,5000195,5000190,5000190,5000191,5000192,5000195,5000190,5000190,5000191,5000192,5000190,5000190,5000191,5000192,5000190,5000190,5000191,5000192,5000190,5000190,5000190,5000191,5000190,5000190,5000191,5000190,5000190,5000191,5000190,5000190,5000191,5000190,5000190,5000191,5000190,5000190,5000191,5000190,5000190,5000191,5000190,5000190,5000191,5000191,5000190,5000190,5000191,5000190,5000191,5000191,5000191,5000191,5000191,5000190,5000190,5000191,5000192,5000193,5000195,5000190,5000190,5000191,5000192,5000193,5000191,5000195,5000190,5000190,5000191,5000192,5000193,5000195,5000190,5000190,5000191,5000192,5000193,5000195,5000190,5000190,5000191,5000192,5000193,5000195,5000190,5000190,5000191,5000191,5000192,5000193,5000195,5000190,5000190,5000191,5000192,5000193,5000195,5000190,5000190,5000191,5000192,5000193,5000195,5000190,5000190,5000191,5000192,5000193,5000195,5000191,5000190,5000190,5000191,5000192,5000193,5000195,5000190,5000190,5000191,5000192,5000193,5000195,5000190,5000190,5000191,5000192,5000193,5000195,5000190,5000190,5000191,5000192,5000191,5000193,5000195,5000190,5000190,5000191,5000192,5000193,5000195,5000190,5000190,5000191,5000192,5000193,5000195,5000190,5000190,5000191,5000192,5000195,5000190,5000190,5000191,5000191,5000192,5000195,5000190,5000190,5000191,5000192,5000190,5000190,5000191,5000192,5000190,5000190,5000191,5000192,5000190,5000190,5000191,5000190,5000190,5000191,5000190,5000191,5000190,5000191,5000190,5000190,5000191,5000190,5000190,5000191,5000190,5000190,5000191,5000190,5000190,5000191,5000190,5000190,5000191,5000190,5000190,5000191,5000190,5000192,5000191,5000191,5000191,5000191,5000191,5000190,5000190,5000191,5000192,5000193,5000195,5000190,5000190,5000191,5000192,5000193,5000195,5000190,5000190,5000191,5000192,5000193,5000192,5000195,5000190,5000190,5000191,5000192,5000193,5000195,5000190,5000190,5000191,5000192,5000193,5000195,5000190,5000190,5000191,5000192,5000193,5000195,5000190,5000190,5000192,5000191,5000192,5000193,5000195,5000190,5000190,5000191,5000192,5000193,5000195,5000190,5000190,5000191,5000192,5000193,5000195,5000190,5000190,5000191,5000192,5000193,5000195,5000192,5000190,5000190,5000191,5000192,5000193,5000195,5000190,5000190,5000191,5000192,5000193,5000195,5000190,5000190,5000191,5000192,5000193,5000195,5000190,5000190,5000191,5000193,5000192,5000193,5000195,5000190,5000190,5000191,5000192,5000193,5000195,5000190,5000190,5000191,5000192,5000195,5000190,5000190,5000191,5000192,5000195,5000190,5000190,5000191,5000193,5000192,5000190,5000190,5000191,5000192,5000190,5000190,5000191,5000192,5000190,5000190,5000191,5000190,5000190,5000191,5000190,5000190,5000191,5000190,5000190,5000191,5000193,5000190,5000190,5000191,5000190,5000190,5000191,5000190,5000190,5000191,5000190,5000190,5000191,5000190,5000190,5000191,5000190,5000191,5000191,5000191,5000191,5000191</t>
         </is>
       </c>
       <c r="D23" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E23" s="0" t="n">
-        <v>147</v>
+        <v>150.15</v>
       </c>
       <c r="F23" s="0" t="inlineStr">
         <is>
-          <t>L1 W20/25; N=290; EHP=70500.504819; variants:5 (counts doubled, hp x1.5/x2.0) | wavebuff-20261029</t>
+          <t>L1 W20/25; N=606; EHP=177927.123756 | wavebuff2-20261029 (counts x2 again, hp stacked) | gold20-20261029: killGold=0 | w20soften-20261029: interval 150.15ms | ground5-20261030: ground +26 (5%)</t>
         </is>
       </c>
     </row>
@@ -1578,7 +1578,7 @@
       </c>
       <c r="C24" s="0" t="inlineStr">
         <is>
-          <t>5000200,5000200,5000201,5000202,5000203,5000205,5000200,5000200,5000201,5000202,5000203,5000205,5000200,5000200,5000201,5000202,5000203,5000205,5000200,5000200,5000201,5000202,5000203,5000205,5000200,5000200,5000201,5000202,5000203,5000205,5000200,5000200,5000201,5000202,5000203,5000205,5000200,5000200,5000201,5000202,5000203,5000205,5000200,5000200,5000201,5000202,5000203,5000205,5000200,5000200,5000201,5000202,5000203,5000205,5000200,5000200,5000201,5000202,5000203,5000205,5000200,5000200,5000201,5000202,5000203,5000205,5000200,5000200,5000201,5000202,5000203,5000205,5000200,5000200,5000201,5000202,5000203,5000205,5000200,5000200,5000201,5000202,5000203,5000205,5000200,5000200,5000201,5000202,5000203,5000205,5000200,5000200,5000201,5000202,5000205,5000200,5000200,5000201,5000202,5000205,5000200,5000200,5000201,5000202,5000205,5000200,5000200,5000201,5000202,5000200,5000200,5000201,5000202,5000200,5000200,5000201,5000202,5000200,5000200,5000201,5000200,5000200,5000201,5000200,5000200,5000201,5000200,5000200,5000201,5000200,5000200,5000201,5000200,5000200,5000201,5000200,5000200,5000201,5000200,5000200,5000201,5000200,5000200,5000201,5000200,5000200,5000201,5000201,5000201,5000201,5000201,5000200,5000200,5000201,5000202,5000203,5000205,5000200,5000200,5000201,5000202,5000203,5000205,5000200,5000200,5000201,5000202,5000203,5000205,5000200,5000200,5000201,5000202,5000203,5000205,5000200,5000200,5000201,5000202,5000203,5000205,5000200,5000200,5000201,5000202,5000203,5000205,5000200,5000200,5000201,5000202,5000203,5000205,5000200,5000200,5000201,5000202,5000203,5000205,5000200,5000200,5000201,5000202,5000203,5000205,5000200,5000200,5000201,5000202,5000203,5000205,5000200,5000200,5000201,5000202,5000203,5000205,5000200,5000200,5000201,5000202,5000203,5000205,5000200,5000200,5000201,5000202,5000203,5000205,5000200,5000200,5000201,5000202,5000203,5000205,5000200,5000200,5000201,5000202,5000203,5000205,5000200,5000200,5000201,5000202,5000205,5000200,5000200,5000201,5000202,5000205,5000200,5000200,5000201,5000202,5000205,5000200,5000200,5000201,5000202,5000200,5000200,5000201,5000202,5000200,5000200,5000201,5000202,5000200,5000200,5000201,5000200,5000200,5000201,5000200,5000200,5000201,5000200,5000200,5000201,5000200,5000200,5000201,5000200,5000200,5000201,5000200,5000200,5000201,5000200,5000200,5000201,5000200,5000200,5000201,5000200,5000200,5000201,5000201,5000201,5000201,5000201</t>
+          <t>5000200,5000200,5000201,5000202,5000203,5000205,5000200,5000200,5000201,5000202,5000203,5000205,5000200,5000200,5000201,5000202,5000203,5000205,5000200,5000200,5000201,5000202,5000200,5000203,5000205,5000200,5000200,5000201,5000202,5000203,5000205,5000200,5000200,5000201,5000202,5000203,5000205,5000200,5000200,5000201,5000202,5000203,5000205,5000200,5000200,5000200,5000201,5000202,5000203,5000205,5000200,5000200,5000201,5000202,5000203,5000205,5000200,5000200,5000201,5000202,5000203,5000205,5000200,5000200,5000201,5000202,5000203,5000200,5000205,5000200,5000200,5000201,5000202,5000203,5000205,5000200,5000200,5000201,5000202,5000203,5000205,5000200,5000200,5000201,5000202,5000203,5000205,5000200,5000200,5000200,5000201,5000202,5000203,5000205,5000200,5000200,5000201,5000202,5000205,5000200,5000200,5000201,5000202,5000205,5000200,5000200,5000201,5000202,5000205,5000200,5000200,5000200,5000201,5000202,5000200,5000200,5000201,5000202,5000200,5000200,5000201,5000202,5000200,5000200,5000201,5000200,5000200,5000201,5000200,5000200,5000201,5000200,5000200,5000201,5000200,5000200,5000200,5000201,5000200,5000200,5000201,5000200,5000200,5000201,5000200,5000200,5000201,5000200,5000200,5000201,5000200,5000200,5000201,5000201,5000201,5000201,5000200,5000201,5000200,5000200,5000201,5000202,5000203,5000205,5000200,5000200,5000201,5000202,5000203,5000205,5000200,5000200,5000201,5000202,5000203,5000205,5000200,5000200,5000201,5000200,5000202,5000203,5000205,5000200,5000200,5000201,5000202,5000203,5000205,5000200,5000200,5000201,5000202,5000203,5000205,5000200,5000200,5000201,5000202,5000203,5000205,5000200,5000200,5000200,5000201,5000202,5000203,5000205,5000200,5000200,5000201,5000202,5000203,5000205,5000200,5000200,5000201,5000202,5000203,5000205,5000200,5000200,5000201,5000200,5000202,5000203,5000205,5000200,5000200,5000201,5000202,5000203,5000205,5000200,5000200,5000201,5000202,5000203,5000205,5000200,5000200,5000201,5000202,5000203,5000205,5000200,5000200,5000200,5000201,5000202,5000203,5000205,5000200,5000200,5000201,5000202,5000205,5000200,5000200,5000201,5000202,5000205,5000200,5000200,5000201,5000202,5000205,5000200,5000200,5000200,5000201,5000202,5000200,5000200,5000201,5000202,5000200,5000200,5000201,5000202,5000200,5000200,5000201,5000200,5000200,5000201,5000200,5000200,5000201,5000200,5000200,5000200,5000201,5000200,5000200,5000201,5000200,5000200,5000201,5000200,5000200,5000201,5000200,5000200,5000201,5000200,5000200,5000201,5000200,5000200,5000201,5000201,5000201,5000201,5000201,5000201,5000200,5000200,5000201,5000202,5000203,5000205,5000200,5000200,5000201,5000202,5000203,5000205,5000200,5000200,5000201,5000202,5000203,5000205,5000200,5000201,5000200,5000201,5000202,5000203,5000205,5000200,5000200,5000201,5000202,5000203,5000205,5000200,5000200,5000201,5000202,5000203,5000205,5000200,5000200,5000201,5000202,5000203,5000201,5000205,5000200,5000200,5000201,5000202,5000203,5000205,5000200,5000200,5000201,5000202,5000203,5000205,5000200,5000200,5000201,5000202,5000203,5000205,5000200,5000200,5000201,5000201,5000202,5000203,5000205,5000200,5000200,5000201,5000202,5000203,5000205,5000200,5000200,5000201,5000202,5000203,5000205,5000200,5000200,5000201,5000202,5000203,5000205,5000201,5000200,5000200,5000201,5000202,5000203,5000205,5000200,5000200,5000201,5000202,5000205,5000200,5000200,5000201,5000202,5000205,5000200,5000200,5000201,5000202,5000205,5000201,5000200,5000200,5000201,5000202,5000200,5000200,5000201,5000202,5000200,5000200,5000201,5000202,5000200,5000200,5000201,5000200,5000200,5000201,5000200,5000200,5000201,5000201,5000200,5000200,5000201,5000200,5000200,5000201,5000200,5000200,5000201,5000200,5000200,5000201,5000200,5000200,5000201,5000200,5000200,5000201,5000200,5000200,5000201,5000201,5000202,5000201,5000201,5000201,5000200,5000200,5000201,5000202,5000203,5000205,5000200,5000200,5000201,5000202,5000203,5000205,5000200,5000200,5000201,5000202,5000203,5000205,5000202,5000200,5000200,5000201,5000202,5000203,5000205,5000200,5000200,5000201,5000202,5000203,5000205,5000200,5000200,5000201,5000202,5000203,5000205,5000200,5000200,5000201,5000202,5000202,5000203,5000205,5000200,5000200,5000201,5000202,5000203,5000205,5000200,5000200,5000201,5000202,5000203,5000205,5000200,5000200,5000201,5000202,5000203,5000205,5000200,5000202,5000200,5000201,5000202,5000203,5000205,5000200,5000200,5000201,5000202,5000203,5000205,5000200,5000200,5000201,5000202,5000203,5000205,5000200,5000200,5000201,5000202,5000203,5000203,5000200,5000200,5000201,5000202,5000203,5000200,5000200,5000201,5000202,5000200,5000200,5000201,5000202,5000200,5000200,5000201,5000202,5000200,5000200,5000201,5000202,5000203,5000200,5000200,5000201,5000202,5000200,5000200,5000201,5000202,5000200,5000200,5000201,5000200,5000200,5000201,5000200,5000200,5000201,5000200,5000200,5000201,5000200,5000203,5000200,5000201,5000200,5000200,5000201,5000200,5000200,5000201,5000200,5000200,5000201,5000200,5000200,5000201,5000200,5000200,5000201,5000201,5000201,5000201,5000201</t>
         </is>
       </c>
       <c r="D24" s="0" t="n">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="F24" s="0" t="inlineStr">
         <is>
-          <t>L1 W21/25; N=302; EHP=71980.354364; variants:5 (counts doubled, hp x1.5/x2.0) | wavebuff-20261029</t>
+          <t>L1 W21/25; N=626; EHP=230501.598406 | wavebuff2-20261029 (counts x2 again, hp stacked) | gold20-20261029: killGold=0 | wavegold-air-20261029: air -5, air hp x0.95 | ground5-20261030: ground +27 (5%)</t>
         </is>
       </c>
     </row>
@@ -1599,7 +1599,7 @@
       </c>
       <c r="C25" s="0" t="inlineStr">
         <is>
-          <t>5000210,5000210,5000211,5000212,5000213,5000215,5000210,5000210,5000211,5000212,5000213,5000215,5000210,5000210,5000211,5000212,5000213,5000215,5000210,5000210,5000211,5000212,5000213,5000215,5000210,5000210,5000211,5000212,5000213,5000215,5000210,5000210,5000211,5000212,5000213,5000215,5000210,5000210,5000211,5000212,5000213,5000215,5000210,5000210,5000211,5000212,5000213,5000215,5000210,5000210,5000211,5000212,5000213,5000215,5000210,5000210,5000211,5000212,5000213,5000215,5000210,5000210,5000211,5000212,5000213,5000215,5000210,5000210,5000211,5000212,5000213,5000215,5000210,5000210,5000211,5000212,5000213,5000215,5000210,5000210,5000211,5000212,5000213,5000215,5000210,5000210,5000211,5000212,5000213,5000215,5000210,5000210,5000211,5000212,5000213,5000215,5000210,5000210,5000211,5000212,5000215,5000210,5000210,5000211,5000212,5000215,5000210,5000210,5000211,5000212,5000215,5000210,5000210,5000211,5000212,5000210,5000210,5000211,5000212,5000210,5000210,5000211,5000212,5000210,5000210,5000211,5000210,5000210,5000211,5000210,5000210,5000211,5000210,5000210,5000211,5000210,5000210,5000211,5000210,5000210,5000211,5000210,5000210,5000211,5000210,5000210,5000211,5000210,5000210,5000211,5000210,5000211,5000211,5000211,5000211,5000211,5000211,5000210,5000210,5000211,5000212,5000213,5000215,5000210,5000210,5000211,5000212,5000213,5000215,5000210,5000210,5000211,5000212,5000213,5000215,5000210,5000210,5000211,5000212,5000213,5000215,5000210,5000210,5000211,5000212,5000213,5000215,5000210,5000210,5000211,5000212,5000213,5000215,5000210,5000210,5000211,5000212,5000213,5000215,5000210,5000210,5000211,5000212,5000213,5000215,5000210,5000210,5000211,5000212,5000213,5000215,5000210,5000210,5000211,5000212,5000213,5000215,5000210,5000210,5000211,5000212,5000213,5000215,5000210,5000210,5000211,5000212,5000213,5000215,5000210,5000210,5000211,5000212,5000213,5000215,5000210,5000210,5000211,5000212,5000213,5000215,5000210,5000210,5000211,5000212,5000213,5000215,5000210,5000210,5000211,5000212,5000213,5000215,5000210,5000210,5000211,5000212,5000215,5000210,5000210,5000211,5000212,5000215,5000210,5000210,5000211,5000212,5000215,5000210,5000210,5000211,5000212,5000210,5000210,5000211,5000212,5000210,5000210,5000211,5000212,5000210,5000210,5000211,5000210,5000210,5000211,5000210,5000210,5000211,5000210,5000210,5000211,5000210,5000210,5000211,5000210,5000210,5000211,5000210,5000210,5000211,5000210,5000210,5000211,5000210,5000210,5000211,5000210,5000211,5000211,5000211,5000211,5000211,5000211</t>
+          <t>5000210,5000210,5000211,5000212,5000213,5000215,5000210,5000210,5000211,5000212,5000213,5000215,5000210,5000210,5000211,5000212,5000213,5000215,5000210,5000210,5000211,5000212,5000210,5000213,5000215,5000210,5000210,5000211,5000212,5000213,5000215,5000210,5000210,5000211,5000212,5000213,5000215,5000210,5000210,5000211,5000212,5000213,5000215,5000210,5000210,5000210,5000211,5000212,5000213,5000215,5000210,5000210,5000211,5000212,5000213,5000215,5000210,5000210,5000211,5000212,5000213,5000215,5000210,5000210,5000211,5000212,5000213,5000210,5000215,5000210,5000210,5000211,5000212,5000213,5000215,5000210,5000210,5000211,5000212,5000213,5000215,5000210,5000210,5000211,5000212,5000213,5000215,5000210,5000210,5000210,5000211,5000212,5000213,5000215,5000210,5000210,5000211,5000212,5000213,5000215,5000210,5000210,5000211,5000212,5000215,5000210,5000210,5000211,5000212,5000215,5000210,5000210,5000210,5000211,5000212,5000215,5000210,5000210,5000211,5000212,5000210,5000210,5000211,5000212,5000210,5000210,5000211,5000212,5000210,5000210,5000211,5000210,5000210,5000211,5000210,5000210,5000210,5000211,5000210,5000210,5000211,5000210,5000210,5000211,5000210,5000210,5000211,5000210,5000210,5000211,5000210,5000210,5000211,5000210,5000210,5000211,5000210,5000210,5000211,5000211,5000211,5000211,5000211,5000211,5000210,5000210,5000211,5000212,5000213,5000215,5000210,5000210,5000211,5000212,5000213,5000215,5000210,5000210,5000211,5000210,5000212,5000213,5000215,5000210,5000210,5000211,5000212,5000213,5000215,5000210,5000210,5000211,5000212,5000213,5000215,5000210,5000210,5000211,5000212,5000213,5000215,5000210,5000210,5000210,5000211,5000212,5000213,5000215,5000210,5000210,5000211,5000212,5000213,5000215,5000210,5000210,5000211,5000212,5000213,5000215,5000210,5000210,5000211,5000212,5000210,5000213,5000215,5000210,5000210,5000211,5000212,5000213,5000215,5000210,5000210,5000211,5000212,5000213,5000215,5000210,5000210,5000211,5000212,5000213,5000215,5000210,5000210,5000210,5000211,5000212,5000213,5000215,5000210,5000210,5000211,5000212,5000213,5000215,5000210,5000210,5000211,5000212,5000213,5000215,5000210,5000210,5000211,5000212,5000215,5000210,5000210,5000210,5000211,5000212,5000215,5000210,5000210,5000211,5000212,5000215,5000210,5000210,5000211,5000212,5000210,5000210,5000211,5000212,5000210,5000210,5000211,5000212,5000210,5000210,5000210,5000211,5000210,5000210,5000211,5000210,5000210,5000211,5000210,5000210,5000211,5000210,5000210,5000211,5000210,5000210,5000211,5000210,5000210,5000211,5000211,5000210,5000210,5000211,5000210,5000210,5000211,5000210,5000211,5000211,5000211,5000211,5000211,5000211,5000210,5000210,5000211,5000212,5000213,5000215,5000210,5000210,5000211,5000211,5000212,5000213,5000215,5000210,5000210,5000211,5000212,5000213,5000215,5000210,5000210,5000211,5000212,5000213,5000215,5000210,5000210,5000211,5000212,5000213,5000215,5000211,5000210,5000210,5000211,5000212,5000213,5000215,5000210,5000210,5000211,5000212,5000213,5000215,5000210,5000210,5000211,5000212,5000213,5000215,5000210,5000210,5000211,5000212,5000211,5000213,5000215,5000210,5000210,5000211,5000212,5000213,5000215,5000210,5000210,5000211,5000212,5000213,5000215,5000210,5000210,5000211,5000212,5000213,5000215,5000210,5000211,5000210,5000211,5000212,5000213,5000215,5000210,5000210,5000211,5000212,5000213,5000215,5000210,5000210,5000211,5000212,5000213,5000215,5000210,5000210,5000211,5000212,5000213,5000211,5000215,5000210,5000210,5000211,5000212,5000215,5000210,5000210,5000211,5000212,5000215,5000210,5000210,5000211,5000212,5000215,5000210,5000210,5000211,5000212,5000210,5000211,5000210,5000211,5000212,5000210,5000210,5000211,5000212,5000210,5000210,5000211,5000210,5000210,5000211,5000210,5000210,5000211,5000210,5000210,5000211,5000210,5000210,5000211,5000211,5000210,5000210,5000211,5000210,5000210,5000211,5000210,5000210,5000211,5000210,5000210,5000211,5000210,5000211,5000211,5000211,5000211,5000211,5000211,5000210,5000210,5000212,5000211,5000212,5000213,5000215,5000210,5000210,5000211,5000212,5000213,5000215,5000210,5000210,5000211,5000212,5000213,5000215,5000210,5000210,5000211,5000212,5000213,5000215,5000212,5000210,5000210,5000211,5000212,5000213,5000215,5000210,5000210,5000211,5000212,5000213,5000215,5000210,5000210,5000211,5000212,5000213,5000215,5000210,5000210,5000211,5000212,5000212,5000213,5000215,5000210,5000210,5000211,5000212,5000213,5000215,5000210,5000210,5000211,5000212,5000213,5000215,5000210,5000210,5000211,5000212,5000213,5000215,5000210,5000212,5000210,5000211,5000212,5000213,5000215,5000210,5000210,5000211,5000212,5000213,5000215,5000210,5000210,5000211,5000212,5000213,5000215,5000210,5000210,5000211,5000212,5000213,5000213,5000210,5000210,5000211,5000212,5000213,5000210,5000210,5000211,5000212,5000210,5000210,5000211,5000212,5000210,5000210,5000211,5000212,5000210,5000210,5000211,5000212,5000213,5000210,5000210,5000211,5000212,5000210,5000210,5000211,5000212,5000210,5000210,5000211,5000210,5000210,5000211,5000210,5000210,5000211,5000210,5000210,5000211,5000210,5000213,5000210,5000211,5000210,5000210,5000211,5000210,5000210,5000211,5000210,5000210,5000211,5000210,5000210,5000211,5000210,5000211,5000211,5000211,5000211,5000211,5000211</t>
         </is>
       </c>
       <c r="D25" s="0" t="n">
@@ -1610,7 +1610,7 @@
       </c>
       <c r="F25" s="0" t="inlineStr">
         <is>
-          <t>L1 W22/25; N=314; EHP=73459.340624; variants:5 (counts doubled, hp x1.5/x2.0) | wavebuff-20261029</t>
+          <t>L1 W22/25; N=651; EHP=235161.123708 | wavebuff2-20261029 (counts x2 again, hp stacked) | gold20-20261029: killGold=0 | wavegold-air-20261029: air -5, air hp x0.95 | ground5-20261030: ground +28 (5%)</t>
         </is>
       </c>
     </row>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="C26" s="0" t="inlineStr">
         <is>
-          <t>5000220,5000220,5000221,5000222,5000223,5000225,5000220,5000220,5000221,5000222,5000223,5000225,5000220,5000220,5000221,5000222,5000223,5000225,5000220,5000220,5000221,5000222,5000223,5000225,5000220,5000220,5000221,5000222,5000223,5000225,5000220,5000220,5000221,5000222,5000223,5000225,5000220,5000220,5000221,5000222,5000223,5000225,5000220,5000220,5000221,5000222,5000223,5000225,5000220,5000220,5000221,5000222,5000223,5000225,5000220,5000220,5000221,5000222,5000223,5000225,5000220,5000220,5000221,5000222,5000223,5000225,5000220,5000220,5000221,5000222,5000223,5000225,5000220,5000220,5000221,5000222,5000223,5000225,5000220,5000220,5000221,5000222,5000223,5000225,5000220,5000220,5000221,5000222,5000223,5000225,5000220,5000220,5000221,5000222,5000223,5000225,5000220,5000220,5000221,5000222,5000223,5000225,5000220,5000220,5000221,5000222,5000225,5000220,5000220,5000221,5000222,5000225,5000220,5000220,5000221,5000222,5000225,5000220,5000220,5000221,5000222,5000220,5000220,5000221,5000222,5000220,5000220,5000221,5000220,5000220,5000221,5000220,5000220,5000221,5000220,5000220,5000221,5000220,5000220,5000221,5000220,5000220,5000221,5000220,5000220,5000221,5000220,5000220,5000221,5000220,5000220,5000221,5000220,5000220,5000221,5000220,5000220,5000221,5000221,5000221,5000221,5000221,5000221,5000220,5000220,5000221,5000222,5000223,5000225,5000220,5000220,5000221,5000222,5000223,5000225,5000220,5000220,5000221,5000222,5000223,5000225,5000220,5000220,5000221,5000222,5000223,5000225,5000220,5000220,5000221,5000222,5000223,5000225,5000220,5000220,5000221,5000222,5000223,5000225,5000220,5000220,5000221,5000222,5000223,5000225,5000220,5000220,5000221,5000222,5000223,5000225,5000220,5000220,5000221,5000222,5000223,5000225,5000220,5000220,5000221,5000222,5000223,5000225,5000220,5000220,5000221,5000222,5000223,5000225,5000220,5000220,5000221,5000222,5000223,5000225,5000220,5000220,5000221,5000222,5000223,5000225,5000220,5000220,5000221,5000222,5000223,5000225,5000220,5000220,5000221,5000222,5000223,5000225,5000220,5000220,5000221,5000222,5000223,5000225,5000220,5000220,5000221,5000222,5000223,5000225,5000220,5000220,5000221,5000222,5000225,5000220,5000220,5000221,5000222,5000225,5000220,5000220,5000221,5000222,5000225,5000220,5000220,5000221,5000222,5000220,5000220,5000221,5000222,5000220,5000220,5000221,5000220,5000220,5000221,5000220,5000220,5000221,5000220,5000220,5000221,5000220,5000220,5000221,5000220,5000220,5000221,5000220,5000220,5000221,5000220,5000220,5000221,5000220,5000220,5000221,5000220,5000220,5000221,5000220,5000220,5000221,5000221,5000221,5000221,5000221,5000221</t>
+          <t>5000220,5000220,5000221,5000222,5000223,5000225,5000220,5000220,5000221,5000222,5000223,5000225,5000220,5000220,5000221,5000222,5000223,5000225,5000220,5000220,5000221,5000222,5000220,5000223,5000225,5000220,5000220,5000221,5000222,5000223,5000225,5000220,5000220,5000221,5000222,5000223,5000225,5000220,5000220,5000221,5000222,5000223,5000225,5000220,5000220,5000220,5000221,5000222,5000223,5000225,5000220,5000220,5000221,5000222,5000223,5000225,5000220,5000220,5000221,5000222,5000223,5000225,5000220,5000220,5000221,5000222,5000223,5000220,5000225,5000220,5000220,5000221,5000222,5000223,5000225,5000220,5000220,5000221,5000222,5000223,5000225,5000220,5000220,5000221,5000222,5000223,5000225,5000220,5000220,5000221,5000220,5000222,5000223,5000225,5000220,5000220,5000221,5000222,5000223,5000225,5000220,5000220,5000221,5000222,5000223,5000225,5000220,5000220,5000221,5000222,5000225,5000220,5000220,5000220,5000221,5000222,5000225,5000220,5000220,5000221,5000222,5000225,5000220,5000220,5000221,5000222,5000220,5000220,5000221,5000222,5000220,5000220,5000221,5000220,5000220,5000220,5000221,5000220,5000220,5000221,5000220,5000220,5000221,5000220,5000220,5000221,5000220,5000220,5000221,5000220,5000220,5000221,5000220,5000220,5000221,5000220,5000220,5000220,5000221,5000220,5000220,5000221,5000220,5000220,5000221,5000221,5000221,5000221,5000221,5000221,5000220,5000220,5000221,5000222,5000223,5000225,5000220,5000220,5000221,5000222,5000220,5000223,5000225,5000220,5000220,5000221,5000222,5000223,5000225,5000220,5000220,5000221,5000222,5000223,5000225,5000220,5000220,5000221,5000222,5000223,5000225,5000220,5000220,5000220,5000221,5000222,5000223,5000225,5000220,5000220,5000221,5000222,5000223,5000225,5000220,5000220,5000221,5000222,5000223,5000225,5000220,5000220,5000221,5000222,5000223,5000220,5000225,5000220,5000220,5000221,5000222,5000223,5000225,5000220,5000220,5000221,5000222,5000223,5000225,5000220,5000220,5000221,5000222,5000223,5000225,5000220,5000220,5000221,5000220,5000222,5000223,5000225,5000220,5000220,5000221,5000222,5000223,5000225,5000220,5000220,5000221,5000222,5000223,5000225,5000220,5000220,5000221,5000222,5000223,5000225,5000220,5000220,5000220,5000221,5000222,5000223,5000225,5000220,5000220,5000221,5000222,5000225,5000220,5000220,5000221,5000222,5000225,5000220,5000220,5000221,5000222,5000225,5000220,5000220,5000220,5000221,5000222,5000220,5000220,5000221,5000222,5000220,5000220,5000221,5000220,5000220,5000221,5000220,5000220,5000221,5000220,5000220,5000221,5000220,5000220,5000221,5000221,5000220,5000220,5000221,5000220,5000220,5000221,5000220,5000220,5000221,5000220,5000220,5000221,5000220,5000220,5000221,5000220,5000220,5000221,5000221,5000221,5000221,5000221,5000221,5000221,5000220,5000220,5000221,5000222,5000223,5000225,5000220,5000220,5000221,5000222,5000223,5000225,5000220,5000220,5000221,5000222,5000223,5000225,5000220,5000220,5000221,5000221,5000222,5000223,5000225,5000220,5000220,5000221,5000222,5000223,5000225,5000220,5000220,5000221,5000222,5000223,5000225,5000220,5000220,5000221,5000222,5000223,5000221,5000225,5000220,5000220,5000221,5000222,5000223,5000225,5000220,5000220,5000221,5000222,5000223,5000225,5000220,5000220,5000221,5000222,5000223,5000225,5000220,5000220,5000221,5000221,5000222,5000223,5000225,5000220,5000220,5000221,5000222,5000223,5000225,5000220,5000220,5000221,5000222,5000223,5000225,5000220,5000220,5000221,5000222,5000223,5000225,5000221,5000220,5000220,5000221,5000222,5000223,5000225,5000220,5000220,5000221,5000222,5000223,5000225,5000220,5000220,5000221,5000222,5000223,5000225,5000220,5000220,5000221,5000222,5000221,5000225,5000220,5000220,5000221,5000222,5000225,5000220,5000220,5000221,5000222,5000225,5000220,5000220,5000221,5000222,5000220,5000220,5000221,5000222,5000220,5000220,5000221,5000221,5000220,5000220,5000221,5000220,5000220,5000221,5000220,5000220,5000221,5000220,5000220,5000221,5000220,5000220,5000221,5000220,5000220,5000221,5000220,5000220,5000221,5000222,5000220,5000220,5000221,5000220,5000220,5000221,5000220,5000220,5000221,5000221,5000221,5000221,5000221,5000221,5000220,5000220,5000221,5000222,5000223,5000225,5000220,5000220,5000222,5000221,5000222,5000223,5000225,5000220,5000220,5000221,5000222,5000223,5000225,5000220,5000220,5000221,5000222,5000223,5000225,5000220,5000220,5000221,5000222,5000223,5000222,5000225,5000220,5000220,5000221,5000222,5000223,5000225,5000220,5000220,5000221,5000222,5000223,5000225,5000220,5000220,5000221,5000222,5000223,5000225,5000220,5000220,5000221,5000222,5000222,5000223,5000225,5000220,5000220,5000221,5000222,5000223,5000225,5000220,5000220,5000221,5000222,5000223,5000225,5000220,5000220,5000221,5000222,5000223,5000225,5000222,5000220,5000220,5000221,5000222,5000223,5000225,5000220,5000220,5000221,5000222,5000223,5000225,5000220,5000220,5000221,5000222,5000223,5000225,5000220,5000220,5000221,5000222,5000223,5000223,5000220,5000220,5000221,5000222,5000223,5000220,5000220,5000221,5000222,5000220,5000220,5000221,5000222,5000220,5000220,5000221,5000222,5000220,5000220,5000221,5000223,5000222,5000220,5000220,5000221,5000222,5000220,5000220,5000221,5000220,5000220,5000221,5000220,5000220,5000221,5000220,5000220,5000221,5000220,5000220,5000221,5000220,5000220,5000223,5000221,5000220,5000220,5000221,5000220,5000220,5000221,5000220,5000220,5000221,5000220,5000220,5000221,5000220,5000220,5000221,5000221,5000221,5000221,5000221,5000221</t>
         </is>
       </c>
       <c r="D26" s="0" t="n">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="F26" s="0" t="inlineStr">
         <is>
-          <t>L1 W23/25; N=326; EHP=74969.412363; variants:5 (counts doubled, hp x1.5/x2.0) | wavebuff-20261029</t>
+          <t>L1 W23/25; N=676; EHP=240288.625876 | wavebuff2-20261029 (counts x2 again, hp stacked) | gold20-20261029: killGold=0 | wavegold-air-20261029: air -5, air hp x0.95 | ground5-20261030: ground +29 (5%)</t>
         </is>
       </c>
     </row>
@@ -1641,7 +1641,7 @@
       </c>
       <c r="C27" s="0" t="inlineStr">
         <is>
-          <t>5000230,5000230,5000231,5000232,5000233,5000235,5000230,5000230,5000231,5000232,5000233,5000235,5000230,5000230,5000231,5000232,5000233,5000235,5000230,5000230,5000231,5000232,5000233,5000235,5000230,5000230,5000231,5000232,5000233,5000235,5000230,5000230,5000231,5000232,5000233,5000235,5000230,5000230,5000231,5000232,5000233,5000235,5000230,5000230,5000231,5000232,5000233,5000235,5000230,5000230,5000231,5000232,5000233,5000235,5000230,5000230,5000231,5000232,5000233,5000235,5000230,5000230,5000231,5000232,5000233,5000235,5000230,5000230,5000231,5000232,5000233,5000235,5000230,5000230,5000231,5000232,5000233,5000235,5000230,5000230,5000231,5000232,5000233,5000235,5000230,5000230,5000231,5000232,5000233,5000235,5000230,5000230,5000231,5000232,5000233,5000235,5000230,5000230,5000231,5000232,5000233,5000235,5000230,5000230,5000231,5000232,5000235,5000230,5000230,5000231,5000232,5000235,5000230,5000230,5000231,5000232,5000235,5000230,5000230,5000231,5000232,5000235,5000230,5000230,5000231,5000232,5000230,5000230,5000231,5000232,5000230,5000230,5000231,5000230,5000230,5000231,5000230,5000230,5000231,5000230,5000230,5000231,5000230,5000230,5000231,5000230,5000230,5000231,5000230,5000230,5000231,5000230,5000230,5000231,5000230,5000230,5000231,5000230,5000230,5000231,5000230,5000230,5000231,5000230,5000231,5000231,5000231,5000231,5000231,5000230,5000230,5000231,5000232,5000233,5000235,5000230,5000230,5000231,5000232,5000233,5000235,5000230,5000230,5000231,5000232,5000233,5000235,5000230,5000230,5000231,5000232,5000233,5000235,5000230,5000230,5000231,5000232,5000233,5000235,5000230,5000230,5000231,5000232,5000233,5000235,5000230,5000230,5000231,5000232,5000233,5000235,5000230,5000230,5000231,5000232,5000233,5000235,5000230,5000230,5000231,5000232,5000233,5000235,5000230,5000230,5000231,5000232,5000233,5000235,5000230,5000230,5000231,5000232,5000233,5000235,5000230,5000230,5000231,5000232,5000233,5000235,5000230,5000230,5000231,5000232,5000233,5000235,5000230,5000230,5000231,5000232,5000233,5000235,5000230,5000230,5000231,5000232,5000233,5000235,5000230,5000230,5000231,5000232,5000233,5000235,5000230,5000230,5000231,5000232,5000233,5000235,5000230,5000230,5000231,5000232,5000235,5000230,5000230,5000231,5000232,5000235,5000230,5000230,5000231,5000232,5000235,5000230,5000230,5000231,5000232,5000235,5000230,5000230,5000231,5000232,5000230,5000230,5000231,5000232,5000230,5000230,5000231,5000230,5000230,5000231,5000230,5000230,5000231,5000230,5000230,5000231,5000230,5000230,5000231,5000230,5000230,5000231,5000230,5000230,5000231,5000230,5000230,5000231,5000230,5000230,5000231,5000230,5000230,5000231,5000230,5000230,5000231,5000230,5000231,5000231,5000231,5000231,5000231</t>
+          <t>5000230,5000230,5000231,5000232,5000233,5000235,5000230,5000230,5000231,5000232,5000233,5000235,5000230,5000230,5000231,5000232,5000233,5000235,5000230,5000230,5000231,5000232,5000230,5000233,5000235,5000230,5000230,5000231,5000232,5000233,5000235,5000230,5000230,5000231,5000232,5000233,5000235,5000230,5000230,5000231,5000232,5000233,5000235,5000230,5000230,5000230,5000231,5000232,5000233,5000235,5000230,5000230,5000231,5000232,5000233,5000235,5000230,5000230,5000231,5000232,5000233,5000235,5000230,5000230,5000231,5000232,5000233,5000230,5000235,5000230,5000230,5000231,5000232,5000233,5000235,5000230,5000230,5000231,5000232,5000233,5000235,5000230,5000230,5000231,5000232,5000233,5000235,5000230,5000230,5000231,5000230,5000232,5000233,5000235,5000230,5000230,5000231,5000232,5000233,5000235,5000230,5000230,5000231,5000232,5000233,5000235,5000230,5000230,5000231,5000232,5000235,5000230,5000230,5000230,5000231,5000232,5000235,5000230,5000230,5000231,5000232,5000235,5000230,5000230,5000231,5000232,5000235,5000230,5000230,5000231,5000232,5000230,5000230,5000231,5000232,5000230,5000230,5000230,5000231,5000230,5000230,5000231,5000230,5000230,5000231,5000230,5000230,5000231,5000230,5000230,5000231,5000230,5000230,5000231,5000230,5000230,5000231,5000230,5000230,5000230,5000231,5000230,5000230,5000231,5000230,5000230,5000231,5000230,5000230,5000231,5000230,5000231,5000231,5000231,5000231,5000231,5000230,5000230,5000231,5000232,5000233,5000230,5000235,5000230,5000230,5000231,5000232,5000233,5000235,5000230,5000230,5000231,5000232,5000233,5000235,5000230,5000230,5000231,5000232,5000233,5000235,5000230,5000230,5000230,5000231,5000232,5000233,5000235,5000230,5000230,5000231,5000232,5000233,5000235,5000230,5000230,5000231,5000232,5000233,5000235,5000230,5000230,5000231,5000232,5000233,5000235,5000230,5000230,5000230,5000231,5000232,5000233,5000235,5000230,5000230,5000231,5000232,5000233,5000235,5000230,5000230,5000231,5000232,5000233,5000235,5000230,5000230,5000231,5000232,5000230,5000233,5000235,5000230,5000230,5000231,5000232,5000233,5000235,5000230,5000230,5000231,5000232,5000233,5000235,5000230,5000230,5000231,5000232,5000233,5000235,5000230,5000230,5000230,5000231,5000232,5000233,5000235,5000230,5000230,5000231,5000232,5000233,5000235,5000230,5000230,5000231,5000232,5000235,5000230,5000230,5000231,5000232,5000235,5000230,5000230,5000230,5000231,5000232,5000235,5000230,5000230,5000231,5000232,5000235,5000230,5000230,5000231,5000232,5000230,5000230,5000231,5000232,5000230,5000230,5000231,5000230,5000230,5000230,5000231,5000230,5000230,5000231,5000230,5000230,5000231,5000230,5000230,5000231,5000230,5000230,5000231,5000230,5000230,5000231,5000230,5000230,5000231,5000230,5000230,5000231,5000231,5000230,5000230,5000231,5000230,5000230,5000231,5000230,5000231,5000231,5000231,5000231,5000231,5000230,5000230,5000231,5000232,5000233,5000235,5000230,5000230,5000231,5000231,5000232,5000233,5000235,5000230,5000230,5000231,5000232,5000233,5000235,5000230,5000230,5000231,5000232,5000233,5000235,5000230,5000230,5000231,5000232,5000233,5000235,5000231,5000230,5000230,5000231,5000232,5000233,5000235,5000230,5000230,5000231,5000232,5000233,5000235,5000230,5000230,5000231,5000232,5000233,5000235,5000230,5000230,5000231,5000232,5000231,5000233,5000235,5000230,5000230,5000231,5000232,5000233,5000235,5000230,5000230,5000231,5000232,5000233,5000235,5000230,5000230,5000231,5000232,5000233,5000235,5000230,5000230,5000231,5000231,5000232,5000233,5000235,5000230,5000230,5000231,5000232,5000233,5000235,5000230,5000230,5000231,5000232,5000233,5000235,5000230,5000230,5000231,5000232,5000233,5000231,5000235,5000230,5000230,5000231,5000232,5000233,5000235,5000230,5000230,5000231,5000232,5000235,5000230,5000230,5000231,5000232,5000235,5000230,5000230,5000231,5000232,5000235,5000231,5000230,5000230,5000231,5000232,5000235,5000230,5000230,5000231,5000232,5000230,5000230,5000231,5000232,5000230,5000230,5000231,5000230,5000230,5000231,5000230,5000230,5000231,5000231,5000230,5000230,5000231,5000230,5000230,5000231,5000230,5000230,5000231,5000230,5000230,5000231,5000230,5000230,5000231,5000230,5000230,5000231,5000230,5000230,5000231,5000232,5000230,5000230,5000231,5000230,5000231,5000231,5000231,5000231,5000231,5000230,5000230,5000231,5000232,5000233,5000235,5000230,5000230,5000231,5000232,5000233,5000235,5000230,5000232,5000230,5000231,5000232,5000233,5000235,5000230,5000230,5000231,5000232,5000233,5000235,5000230,5000230,5000231,5000232,5000233,5000235,5000230,5000230,5000231,5000232,5000233,5000232,5000235,5000230,5000230,5000231,5000232,5000233,5000235,5000230,5000230,5000231,5000232,5000233,5000235,5000230,5000230,5000231,5000232,5000233,5000235,5000230,5000230,5000232,5000231,5000232,5000233,5000235,5000230,5000230,5000231,5000232,5000233,5000235,5000230,5000230,5000231,5000232,5000233,5000235,5000230,5000230,5000231,5000232,5000233,5000235,5000232,5000230,5000230,5000231,5000232,5000233,5000235,5000230,5000230,5000231,5000232,5000233,5000235,5000230,5000230,5000231,5000232,5000233,5000235,5000230,5000230,5000231,5000232,5000233,5000233,5000230,5000230,5000231,5000232,5000230,5000230,5000231,5000232,5000230,5000230,5000231,5000232,5000230,5000230,5000231,5000232,5000230,5000230,5000231,5000232,5000233,5000230,5000230,5000231,5000232,5000230,5000230,5000231,5000230,5000230,5000231,5000230,5000230,5000231,5000230,5000230,5000231,5000230,5000230,5000231,5000230,5000230,5000231,5000233,5000230,5000230,5000231,5000230,5000230,5000231,5000230,5000230,5000231,5000230,5000230,5000231,5000230,5000230,5000231,5000230,5000231,5000231,5000231,5000231,5000231</t>
         </is>
       </c>
       <c r="D27" s="0" t="n">
@@ -1652,7 +1652,7 @@
       </c>
       <c r="F27" s="0" t="inlineStr">
         <is>
-          <t>L1 W24/25; N=338; EHP=80301.915228; variants:5 (counts doubled, hp x1.5/x2.0) | wavebuff-20261029</t>
+          <t>L1 W24/25; N=701; EHP=257560.220166 | wavebuff2-20261029 (counts x2 again, hp stacked) | gold20-20261029: killGold=1932 | wavegold-air-20261029: air -5, air hp x0.95 | ground5-20261030: ground +30 (5%)</t>
         </is>
       </c>
     </row>
@@ -1662,18 +1662,18 @@
       </c>
       <c r="C28" s="0" t="inlineStr">
         <is>
-          <t>5000240,5000240,5000241,5000242,5000243,5000244,5000245,5000240,5000240,5000241,5000242,5000243,5000244,5000245,5000240,5000240,5000241,5000242,5000243,5000244,5000245,5000240,5000240,5000241,5000242,5000243,5000245,5000240,5000240,5000241,5000242,5000243,5000245,5000240,5000240,5000241,5000242,5000243,5000245,5000240,5000240,5000241,5000242,5000243,5000245,5000240,5000240,5000241,5000242,5000243,5000245,5000240,5000240,5000241,5000242,5000243,5000245,5000240,5000240,5000241,5000242,5000243,5000245,5000240,5000240,5000241,5000242,5000243,5000245,5000240,5000240,5000241,5000242,5000243,5000245,5000240,5000240,5000241,5000242,5000243,5000245,5000240,5000240,5000241,5000242,5000243,5000245,5000240,5000240,5000241,5000242,5000243,5000245,5000240,5000240,5000241,5000242,5000243,5000245,5000240,5000240,5000241,5000242,5000243,5000245,5000240,5000240,5000241,5000242,5000243,5000245,5000240,5000240,5000241,5000242,5000243,5000245,5000240,5000240,5000241,5000242,5000243,5000245,5000240,5000240,5000241,5000242,5000243,5000245,5000240,5000240,5000241,5000242,5000245,5000240,5000240,5000241,5000242,5000240,5000240,5000241,5000242,5000240,5000240,5000241,5000240,5000240,5000241,5000240,5000240,5000241,5000240,5000240,5000241,5000240,5000240,5000241,5000240,5000240,5000241,5000240,5000240,5000241,5000240,5000240,5000241,5000240,5000240,5000241,5000241,5000241,5000241,5000241,5000241,5000241,5000240,5000240,5000241,5000242,5000243,5000244,5000245,5000240,5000240,5000241,5000242,5000243,5000244,5000245,5000240,5000240,5000241,5000242,5000243,5000244,5000245,5000240,5000240,5000241,5000242,5000243,5000245,5000240,5000240,5000241,5000242,5000243,5000245,5000240,5000240,5000241,5000242,5000243,5000245,5000240,5000240,5000241,5000242,5000243,5000245,5000240,5000240,5000241,5000242,5000243,5000245,5000240,5000240,5000241,5000242,5000243,5000245,5000240,5000240,5000241,5000242,5000243,5000245,5000240,5000240,5000241,5000242,5000243,5000245,5000240,5000240,5000241,5000242,5000243,5000245,5000240,5000240,5000241,5000242,5000243,5000245,5000240,5000240,5000241,5000242,5000243,5000245,5000240,5000240,5000241,5000242,5000243,5000245,5000240,5000240,5000241,5000242,5000243,5000245,5000240,5000240,5000241,5000242,5000243,5000245,5000240,5000240,5000241,5000242,5000243,5000245,5000240,5000240,5000241,5000242,5000243,5000245,5000240,5000240,5000241,5000242,5000243,5000245,5000240,5000240,5000241,5000242,5000243,5000245,5000240,5000240,5000241,5000242,5000245,5000240,5000240,5000241,5000242,5000240,5000240,5000241,5000242,5000240,5000240,5000241,5000240,5000240,5000241,5000240,5000240,5000241,5000240,5000240,5000241,5000240,5000240,5000241,5000240,5000240,5000241,5000240,5000240,5000241,5000240,5000240,5000241,5000240,5000240,5000241,5000241,5000241,5000241,5000241,5000241,5000241</t>
+          <t>5000240,5000240,5000241,5000242,5000243,5000244,5000245,5000240,5000240,5000241,5000242,5000243,5000244,5000245,5000240,5000240,5000241,5000242,5000243,5000244,5000245,5000240,5000240,5000240,5000241,5000242,5000243,5000245,5000240,5000240,5000241,5000242,5000243,5000245,5000240,5000240,5000241,5000242,5000243,5000245,5000240,5000240,5000241,5000242,5000243,5000240,5000245,5000240,5000240,5000241,5000242,5000243,5000245,5000240,5000240,5000241,5000242,5000243,5000245,5000240,5000240,5000241,5000242,5000243,5000245,5000240,5000240,5000241,5000240,5000242,5000243,5000245,5000240,5000240,5000241,5000242,5000243,5000245,5000240,5000240,5000241,5000242,5000243,5000245,5000240,5000240,5000241,5000242,5000243,5000245,5000240,5000240,5000240,5000241,5000242,5000243,5000245,5000240,5000240,5000241,5000242,5000243,5000245,5000240,5000240,5000241,5000242,5000243,5000245,5000240,5000240,5000241,5000242,5000240,5000243,5000245,5000240,5000240,5000241,5000242,5000243,5000245,5000240,5000240,5000241,5000242,5000243,5000245,5000240,5000240,5000241,5000242,5000243,5000245,5000240,5000240,5000240,5000241,5000242,5000245,5000240,5000240,5000241,5000242,5000240,5000240,5000241,5000242,5000240,5000240,5000241,5000240,5000240,5000241,5000240,5000240,5000241,5000240,5000240,5000240,5000241,5000240,5000240,5000241,5000240,5000240,5000241,5000240,5000240,5000241,5000240,5000240,5000241,5000240,5000240,5000241,5000241,5000241,5000241,5000241,5000241,5000240,5000241,5000240,5000240,5000241,5000242,5000243,5000244,5000245,5000240,5000240,5000241,5000242,5000243,5000244,5000245,5000240,5000240,5000241,5000242,5000243,5000244,5000245,5000240,5000240,5000240,5000241,5000242,5000243,5000245,5000240,5000240,5000241,5000242,5000243,5000245,5000240,5000240,5000241,5000242,5000243,5000245,5000240,5000240,5000241,5000242,5000240,5000243,5000245,5000240,5000240,5000241,5000242,5000243,5000245,5000240,5000240,5000241,5000242,5000243,5000245,5000240,5000240,5000241,5000242,5000243,5000245,5000240,5000240,5000240,5000241,5000242,5000243,5000245,5000240,5000240,5000241,5000242,5000243,5000245,5000240,5000240,5000241,5000242,5000243,5000245,5000240,5000240,5000241,5000242,5000243,5000240,5000245,5000240,5000240,5000241,5000242,5000243,5000245,5000240,5000240,5000241,5000242,5000243,5000245,5000240,5000240,5000241,5000242,5000243,5000245,5000240,5000240,5000241,5000240,5000242,5000243,5000245,5000240,5000240,5000241,5000242,5000243,5000245,5000240,5000240,5000241,5000242,5000243,5000245,5000240,5000240,5000241,5000242,5000243,5000245,5000240,5000241,5000240,5000241,5000242,5000245,5000240,5000240,5000241,5000242,5000240,5000240,5000241,5000242,5000240,5000240,5000241,5000240,5000240,5000241,5000240,5000240,5000241,5000241,5000240,5000240,5000241,5000240,5000240,5000241,5000240,5000240,5000241,5000240,5000240,5000241,5000240,5000240,5000241,5000240,5000240,5000241,5000241,5000241,5000241,5000241,5000241,5000241,5000241,5000240,5000240,5000241,5000242,5000243,5000244,5000245,5000240,5000240,5000241,5000242,5000243,5000244,5000245,5000240,5000240,5000241,5000242,5000243,5000244,5000241,5000245,5000240,5000240,5000241,5000242,5000243,5000245,5000240,5000240,5000241,5000242,5000243,5000245,5000240,5000240,5000241,5000242,5000243,5000245,5000240,5000240,5000241,5000241,5000242,5000243,5000245,5000240,5000240,5000241,5000242,5000243,5000245,5000240,5000240,5000241,5000242,5000243,5000245,5000240,5000240,5000241,5000242,5000243,5000245,5000241,5000240,5000240,5000241,5000242,5000243,5000245,5000240,5000240,5000241,5000242,5000243,5000245,5000240,5000240,5000241,5000242,5000243,5000245,5000240,5000240,5000241,5000242,5000241,5000243,5000245,5000240,5000240,5000241,5000242,5000243,5000245,5000240,5000240,5000241,5000242,5000243,5000245,5000240,5000240,5000241,5000242,5000243,5000245,5000240,5000240,5000241,5000241,5000242,5000243,5000245,5000240,5000240,5000241,5000242,5000243,5000245,5000240,5000240,5000241,5000242,5000243,5000245,5000240,5000240,5000241,5000242,5000243,5000242,5000245,5000240,5000240,5000241,5000242,5000245,5000240,5000240,5000241,5000242,5000240,5000240,5000241,5000242,5000240,5000240,5000241,5000240,5000240,5000241,5000240,5000240,5000242,5000241,5000240,5000240,5000241,5000240,5000240,5000241,5000240,5000240,5000241,5000240,5000240,5000241,5000240,5000240,5000241,5000240,5000240,5000241,5000241,5000241,5000241,5000242,5000241,5000241,5000241,5000240,5000240,5000241,5000242,5000243,5000244,5000245,5000240,5000240,5000241,5000242,5000243,5000244,5000245,5000240,5000240,5000241,5000242,5000242,5000243,5000244,5000245,5000240,5000240,5000241,5000242,5000243,5000245,5000240,5000240,5000241,5000242,5000243,5000245,5000240,5000240,5000241,5000242,5000243,5000245,5000240,5000242,5000240,5000241,5000242,5000243,5000245,5000240,5000240,5000241,5000242,5000243,5000245,5000240,5000240,5000241,5000242,5000243,5000245,5000240,5000240,5000241,5000242,5000243,5000243,5000245,5000240,5000240,5000241,5000242,5000243,5000245,5000240,5000240,5000241,5000242,5000243,5000245,5000240,5000240,5000241,5000242,5000243,5000245,5000240,5000240,5000241,5000243,5000242,5000243,5000245,5000240,5000240,5000241,5000242,5000243,5000245,5000240,5000240,5000241,5000242,5000243,5000245,5000240,5000240,5000241,5000242,5000243,5000245,5000243,5000240,5000240,5000241,5000242,5000243,5000240,5000240,5000241,5000242,5000243,5000240,5000240,5000241,5000242,5000243,5000240,5000240,5000241,5000242,5000243,5000240,5000240,5000243,5000241,5000242,5000240,5000240,5000241,5000242,5000240,5000240,5000241,5000242,5000240,5000240,5000241,5000240,5000240,5000241,5000240,5000240,5000241,5000240,5000240,5000241,5000244,5000240,5000240,5000241,5000240,5000240,5000241,5000240,5000240,5000241,5000240,5000240,5000241,5000240,5000240,5000241,5000241,5000241,5000241,5000241,5000241,5000241</t>
         </is>
       </c>
       <c r="D28" s="0" t="n">
         <v>0</v>
       </c>
       <c r="E28" s="0" t="n">
-        <v>215</v>
+        <v>236.5</v>
       </c>
       <c r="F28" s="0" t="inlineStr">
         <is>
-          <t>L1 W25/25; N=350; EHP=159766.309670; variants:6 (counts doubled, hp x1.5/x2.0) | wavebuff-20261029</t>
+          <t>L1 W25/25; N=726; EHP=410396.243063 | wavebuff2-20261029 (counts x2 again, hp stacked) | gold20-20261029: killGold=0 | wavegold-air-20261029: air -5, air hp x0.95 | w25soften-20261030: hp x0.80, interval x1.10 | ground5-20261030: ground +31 (5%)</t>
         </is>
       </c>
     </row>

--- a/Luban/Config/Datas/Levels/L01/EnemyList.xlsx
+++ b/Luban/Config/Datas/Levels/L01/EnemyList.xlsx
@@ -1253,7 +1253,7 @@
       </c>
       <c r="F8" s="0" t="inlineStr">
         <is>
-          <t>L1 W5/25; N=231; EHP=10280.709008 | wavebuff2-20261029 (counts x2 again, hp stacked) | gold20-20261029: killGold=60 | ground5-20261030: ground +11 (5%)</t>
+          <t>L1 W5/25; N=231; EHP=10280.709008 | wavebuff2-20261029 (counts x2 again, hp stacked) | gold20-20261029: killGold=60 | ground5-20261030: ground +11 (5%) | hp-20261030: ground x1.25, air x1.05 (EHP=12715.927720) | hp2-20261030: ground x1.55, air x1.05 (EHP=19355.421641)</t>
         </is>
       </c>
     </row>
@@ -1274,7 +1274,7 @@
       </c>
       <c r="F9" s="0" t="inlineStr">
         <is>
-          <t>L1 W6/25; N=256; EHP=10548.512992 | wavebuff2-20261029 (counts x2 again, hp stacked) | gold20-20261029: killGold=80 | ground5-20261030: ground +12 (5%)</t>
+          <t>L1 W6/25; N=256; EHP=10548.512992 | wavebuff2-20261029 (counts x2 again, hp stacked) | gold20-20261029: killGold=80 | ground5-20261030: ground +12 (5%) | hp-20261030: ground x1.25, air x1.05 (EHP=12999.661926) | hp2-20261030: ground x1.55, air x1.05 (EHP=19661.280402)</t>
         </is>
       </c>
     </row>
@@ -1295,7 +1295,7 @@
       </c>
       <c r="F10" s="0" t="inlineStr">
         <is>
-          <t>L1 W7/25; N=281; EHP=12410.951006 | wavebuff2-20261029 (counts x2 again, hp stacked) | gold20-20261029: killGold=132 | ground5-20261030: ground +13 (5%)</t>
+          <t>L1 W7/25; N=281; EHP=12410.951006 | wavebuff2-20261029 (counts x2 again, hp stacked) | gold20-20261029: killGold=132 | ground5-20261030: ground +13 (5%) | hp-20261030: ground x1.25, air x1.05 (EHP=15251.001434) | hp2-20261030: ground x1.55, air x1.05 (EHP=22949.498000)</t>
         </is>
       </c>
     </row>
@@ -1316,7 +1316,7 @@
       </c>
       <c r="F11" s="0" t="inlineStr">
         <is>
-          <t>L1 W8/25; N=306; EHP=16280.767458 | wavebuff2-20261029 (counts x2 again, hp stacked) | gold20-20261029: killGold=20 | ground5-20261030: ground +14 (5%)</t>
+          <t>L1 W8/25; N=306; EHP=16280.767458 | wavebuff2-20261029 (counts x2 again, hp stacked) | gold20-20261029: killGold=20 | ground5-20261030: ground +14 (5%) | hp-20261030: ground x1.25, air x1.05 (EHP=19958.799291) | hp2-20261030: ground x1.55, air x1.05 (EHP=29906.718932)</t>
         </is>
       </c>
     </row>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="F12" s="0" t="inlineStr">
         <is>
-          <t>L1 W9/25; N=331; EHP=20961.699193 | wavebuff2-20261029 (counts x2 again, hp stacked) | gold20-20261029: killGold=24 | ground5-20261030: ground +15 (5%)</t>
+          <t>L1 W9/25; N=331; EHP=20961.699193 | wavebuff2-20261029 (counts x2 again, hp stacked) | gold20-20261029: killGold=24 | ground5-20261030: ground +15 (5%) | hp-20261030: ground x1.25, air x1.05 (EHP=25646.617235) | hp2-20261030: ground x1.55, air x1.05 (EHP=38294.051560)</t>
         </is>
       </c>
     </row>
@@ -1358,7 +1358,7 @@
       </c>
       <c r="F13" s="0" t="inlineStr">
         <is>
-          <t>L1 W10/25; N=356; EHP=38896.801214 | wavebuff2-20261029 (counts x2 again, hp stacked) | gold20-20261029: killGold=0 | ground5-20261030: ground +16 (5%)</t>
+          <t>L1 W10/25; N=356; EHP=38896.801214 | wavebuff2-20261029 (counts x2 again, hp stacked) | gold20-20261029: killGold=0 | ground5-20261030: ground +16 (5%) | hp-20261030: ground x1.25, air x1.05 (EHP=47506.064618) | hp2-20261030: ground x1.55, air x1.05 (EHP=70707.690742) | hp3-20261030: W10 ground x0.85 (EHP=61023.450632)</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="F14" s="0" t="inlineStr">
         <is>
-          <t>L1 W11/25; N=381; EHP=39385.756064 | wavebuff2-20261029 (counts x2 again, hp stacked) | gold20-20261029: killGold=0 | ground5-20261030: ground +17 (5%)</t>
+          <t>L1 W11/25; N=381; EHP=39385.756064 | wavebuff2-20261029 (counts x2 again, hp stacked) | gold20-20261029: killGold=0 | ground5-20261030: ground +17 (5%) | hp-20261030: ground x1.25, air x1.05 (EHP=48261.649622) | hp2-20261030: ground x1.55, air x1.05 (EHP=72257.875232) | hp3-20261030: W11-25 ground x0.85 (EHP=62221.713680)</t>
         </is>
       </c>
     </row>
@@ -1400,7 +1400,7 @@
       </c>
       <c r="F15" s="0" t="inlineStr">
         <is>
-          <t>L1 W12/25; N=406; EHP=40809.085638 | wavebuff2-20261029 (counts x2 again, hp stacked) | gold20-20261029: killGold=0 | ground5-20261030: ground +18 (5%)</t>
+          <t>L1 W12/25; N=406; EHP=40809.085638 | wavebuff2-20261029 (counts x2 again, hp stacked) | gold20-20261029: killGold=0 | ground5-20261030: ground +18 (5%) | hp-20261030: ground x1.25, air x1.05 (EHP=49962.887487) | hp2-20261030: ground x1.55, air x1.05 (EHP=74690.242898) | hp3-20261030: W11-25 ground x0.85 (EHP=64353.659659)</t>
         </is>
       </c>
     </row>
@@ -1421,7 +1421,7 @@
       </c>
       <c r="F16" s="0" t="inlineStr">
         <is>
-          <t>L1 W13/25; N=431; EHP=49843.475103 | wavebuff2-20261029 (counts x2 again, hp stacked) | gold20-20261029: killGold=0 | ground5-20261030: ground +19 (5%)</t>
+          <t>L1 W13/25; N=431; EHP=49843.475103 | wavebuff2-20261029 (counts x2 again, hp stacked) | gold20-20261029: killGold=0 | ground5-20261030: ground +19 (5%) | hp-20261030: ground x1.25, air x1.05 (EHP=60968.050676) | hp2-20261030: ground x1.55, air x1.05 (EHP=90992.709032) | hp3-20261030: W11-25 ground x0.85 (EHP=78448.750064)</t>
         </is>
       </c>
     </row>
@@ -1442,7 +1442,7 @@
       </c>
       <c r="F17" s="0" t="inlineStr">
         <is>
-          <t>L1 W14/25; N=456; EHP=60354.909159 | wavebuff2-20261029 (counts x2 again, hp stacked) | gold20-20261029: killGold=0 | ground5-20261030: ground +20 (5%)</t>
+          <t>L1 W14/25; N=456; EHP=60354.909159 | wavebuff2-20261029 (counts x2 again, hp stacked) | gold20-20261029: killGold=0 | ground5-20261030: ground +20 (5%) | hp-20261030: ground x1.25, air x1.05 (EHP=73749.252381) | hp2-20261030: ground x1.55, air x1.05 (EHP=109863.583107) | hp3-20261030: W11-25 ground x0.85 (EHP=94785.089377)</t>
         </is>
       </c>
     </row>
@@ -1463,7 +1463,7 @@
       </c>
       <c r="F18" s="0" t="inlineStr">
         <is>
-          <t>L1 W15/25; N=481; EHP=105348.214470 | wavebuff2-20261029 (counts x2 again, hp stacked) | gold20-20261029: killGold=0 | ground5-20261030: ground +21 (5%)</t>
+          <t>L1 W15/25; N=481; EHP=105348.214470 | wavebuff2-20261029 (counts x2 again, hp stacked) | gold20-20261029: killGold=0 | ground5-20261030: ground +21 (5%) | hp-20261030: ground x1.25, air x1.05 (EHP=128657.153862) | hp2-20261030: ground x1.55, air x1.05 (EHP=191469.788353) | hp3-20261030: W11-25 ground x0.85 (EHP=165253.192249) | hp4-20261030: W15-25 ground x0.9 (EHP=150397.121094) | hp5-20261030: W15-25 ground x0.95 (EHP=143711.889001)</t>
         </is>
       </c>
     </row>
@@ -1484,7 +1484,7 @@
       </c>
       <c r="F19" s="0" t="inlineStr">
         <is>
-          <t>L1 W16/25; N=506; EHP=107875.827726 | wavebuff2-20261029 (counts x2 again, hp stacked) | gold20-20261029: killGold=200 | ground5-20261030: ground +22 (5%)</t>
+          <t>L1 W16/25; N=506; EHP=107875.827726 | wavebuff2-20261029 (counts x2 again, hp stacked) | gold20-20261029: killGold=200 | ground5-20261030: ground +22 (5%) | hp-20261030: ground x1.25, air x1.05 (EHP=131628.851020) | hp2-20261030: ground x1.55, air x1.05 (EHP=195582.893030) | hp3-20261030: W11-25 ground x0.85 (EHP=168904.634175) | hp4-20261030: W15-25 ground x0.9 (EHP=153786.954303) | hp5-20261030: W15-25 ground x0.95 (EHP=146983.998175)</t>
         </is>
       </c>
     </row>
@@ -1505,7 +1505,7 @@
       </c>
       <c r="F20" s="0" t="inlineStr">
         <is>
-          <t>L1 W17/25; N=531; EHP=110419.889399 | wavebuff2-20261029 (counts x2 again, hp stacked) | gold20-20261029: killGold=0 | ground5-20261030: ground +23 (5%)</t>
+          <t>L1 W17/25; N=531; EHP=110419.889399 | wavebuff2-20261029 (counts x2 again, hp stacked) | gold20-20261029: killGold=0 | ground5-20261030: ground +23 (5%) | hp-20261030: ground x1.25, air x1.05 (EHP=134691.009753) | hp2-20261030: ground x1.55, air x1.05 (EHP=200019.704037) | hp3-20261030: W11-25 ground x0.85 (EHP=172773.427208) | hp4-20261030: W15-25 ground x0.9 (EHP=157333.870210) | hp5-20261030: W15-25 ground x0.95 (EHP=150386.069593)</t>
         </is>
       </c>
     </row>
@@ -1526,7 +1526,7 @@
       </c>
       <c r="F21" s="0" t="inlineStr">
         <is>
-          <t>L1 W18/25; N=556; EHP=118103.089258 | wavebuff2-20261029 (counts x2 again, hp stacked) | gold20-20261029: killGold=0 | ground5-20261030: ground +24 (5%)</t>
+          <t>L1 W18/25; N=556; EHP=118103.089258 | wavebuff2-20261029 (counts x2 again, hp stacked) | gold20-20261029: killGold=0 | ground5-20261030: ground +24 (5%) | hp-20261030: ground x1.25, air x1.05 (EHP=143992.735276) | hp2-20261030: ground x1.55, air x1.05 (EHP=213643.908064) | hp3-20261030: W11-25 ground x0.85 (EHP=184603.943879) | hp4-20261030: W15-25 ground x0.9 (EHP=168147.964119) | hp5-20261030: W15-25 ground x0.95 (EHP=160742.773339)</t>
         </is>
       </c>
     </row>
@@ -1547,7 +1547,7 @@
       </c>
       <c r="F22" s="0" t="inlineStr">
         <is>
-          <t>L1 W19/25; N=581; EHP=136996.277523 | wavebuff2-20261029 (counts x2 again, hp stacked) | gold20-20261029: killGold=0 | ground5-20261030: ground +25 (5%)</t>
+          <t>L1 W19/25; N=581; EHP=136996.277523 | wavebuff2-20261029 (counts x2 again, hp stacked) | gold20-20261029: killGold=0 | ground5-20261030: ground +25 (5%) | hp-20261030: ground x1.25, air x1.05 (EHP=166904.954756) | hp2-20261030: ground x1.55, air x1.05 (EHP=247309.150300) | hp3-20261030: W11-25 ground x0.85 (EHP=213801.739511) | hp4-20261030: W15-25 ground x0.9 (EHP=194814.206795) | hp5-20261030: W15-25 ground x0.95 (EHP=186269.817149)</t>
         </is>
       </c>
     </row>
@@ -1568,7 +1568,7 @@
       </c>
       <c r="F23" s="0" t="inlineStr">
         <is>
-          <t>L1 W20/25; N=606; EHP=177927.123756 | wavebuff2-20261029 (counts x2 again, hp stacked) | gold20-20261029: killGold=0 | w20soften-20261029: interval 150.15ms | ground5-20261030: ground +26 (5%)</t>
+          <t>L1 W20/25; N=606; EHP=177927.123756 | wavebuff2-20261029 (counts x2 again, hp stacked) | gold20-20261029: killGold=0 | w20soften-20261029: interval 150.15ms | ground5-20261030: ground +26 (5%) | hp-20261030: ground x1.25, air x1.05 (EHP=216711.151795) | hp2-20261030: ground x1.55, air x1.05 (EHP=320945.684398) | hp3-20261030: W11-25 ground x0.85 (EHP=277515.160921) | hp4-20261030: W15-25 ground x0.9 (EHP=252904.531093) | hp5-20261030: W15-25 ground x0.95 (EHP=241829.747662)</t>
         </is>
       </c>
     </row>
@@ -1589,7 +1589,7 @@
       </c>
       <c r="F24" s="0" t="inlineStr">
         <is>
-          <t>L1 W21/25; N=626; EHP=230501.598406 | wavebuff2-20261029 (counts x2 again, hp stacked) | gold20-20261029: killGold=0 | wavegold-air-20261029: air -5, air hp x0.95 | ground5-20261030: ground +27 (5%)</t>
+          <t>L1 W21/25; N=626; EHP=230501.598406 | wavebuff2-20261029 (counts x2 again, hp stacked) | gold20-20261029: killGold=0 | wavegold-air-20261029: air -5, air hp x0.95 | ground5-20261030: ground +27 (5%) | hp-20261030: ground x1.25, air x1.05 (EHP=281325.347015) | hp2-20261030: ground x1.55, air x1.05 (EHP=418199.954202) | hp3-20261030: W11-25 ground x0.85 (EHP=361094.076087) | hp4-20261030: W15-25 ground x0.9 (EHP=328734.078678) | hp5-20261030: W15-25 ground x0.95 (EHP=314172.079845)</t>
         </is>
       </c>
     </row>
@@ -1610,7 +1610,7 @@
       </c>
       <c r="F25" s="0" t="inlineStr">
         <is>
-          <t>L1 W22/25; N=651; EHP=235161.123708 | wavebuff2-20261029 (counts x2 again, hp stacked) | gold20-20261029: killGold=0 | wavegold-air-20261029: air -5, air hp x0.95 | ground5-20261030: ground +28 (5%)</t>
+          <t>L1 W22/25; N=651; EHP=235161.123708 | wavebuff2-20261029 (counts x2 again, hp stacked) | gold20-20261029: killGold=0 | wavegold-air-20261029: air -5, air hp x0.95 | ground5-20261030: ground +28 (5%) | hp-20261030: ground x1.25, air x1.05 (EHP=286918.597490) | hp2-20261030: ground x1.55, air x1.05 (EHP=426262.706818) | hp3-20261030: W11-25 ground x0.85 (EHP=368138.553364) | hp4-20261030: W15-25 ground x0.9 (EHP=335201.533046) | hp5-20261030: W15-25 ground x0.95 (EHP=320379.873777)</t>
         </is>
       </c>
     </row>
@@ -1631,7 +1631,7 @@
       </c>
       <c r="F26" s="0" t="inlineStr">
         <is>
-          <t>L1 W23/25; N=676; EHP=240288.625876 | wavebuff2-20261029 (counts x2 again, hp stacked) | gold20-20261029: killGold=0 | wavegold-air-20261029: air -5, air hp x0.95 | ground5-20261030: ground +29 (5%)</t>
+          <t>L1 W23/25; N=676; EHP=240288.625876 | wavebuff2-20261029 (counts x2 again, hp stacked) | gold20-20261029: killGold=0 | wavegold-air-20261029: air -5, air hp x0.95 | ground5-20261030: ground +29 (5%) | hp-20261030: ground x1.25, air x1.05 (EHP=293077.856897) | hp2-20261030: ground x1.55, air x1.05 (EHP=435152.998855) | hp3-20261030: W11-25 ground x0.85 (EHP=375902.118041) | hp4-20261030: W15-25 ground x0.9 (EHP=342326.619003) | hp5-20261030: W15-25 ground x0.95 (EHP=327217.644319)</t>
         </is>
       </c>
     </row>
@@ -1652,7 +1652,7 @@
       </c>
       <c r="F27" s="0" t="inlineStr">
         <is>
-          <t>L1 W24/25; N=701; EHP=257560.220166 | wavebuff2-20261029 (counts x2 again, hp stacked) | gold20-20261029: killGold=1932 | wavegold-air-20261029: air -5, air hp x0.95 | ground5-20261030: ground +30 (5%)</t>
+          <t>L1 W24/25; N=701; EHP=257560.220166 | wavebuff2-20261029 (counts x2 again, hp stacked) | gold20-20261029: killGold=1932 | wavegold-air-20261029: air -5, air hp x0.95 | ground5-20261030: ground +30 (5%) | hp-20261030: ground x1.25, air x1.05 (EHP=313979.492776) | hp2-20261030: ground x1.55, air x1.05 (EHP=465744.909990) | hp3-20261030: W11-25 ground x0.85 (EHP=402474.014181) | hp4-20261030: W15-25 ground x0.9 (EHP=366620.506662) | hp5-20261030: W15-25 ground x0.95 (EHP=350486.428135)</t>
         </is>
       </c>
     </row>
@@ -1673,7 +1673,7 @@
       </c>
       <c r="F28" s="0" t="inlineStr">
         <is>
-          <t>L1 W25/25; N=726; EHP=410396.243063 | wavebuff2-20261029 (counts x2 again, hp stacked) | gold20-20261029: killGold=0 | wavegold-air-20261029: air -5, air hp x0.95 | w25soften-20261030: hp x0.80, interval x1.10 | ground5-20261030: ground +31 (5%)</t>
+          <t>L1 W25/25; N=726; EHP=410396.243063 | wavebuff2-20261029 (counts x2 again, hp stacked) | gold20-20261029: killGold=0 | wavegold-air-20261029: air -5, air hp x0.95 | w25soften-20261030: hp x0.80, interval x1.10 | ground5-20261030: ground +31 (5%) | hp-20261030: ground x1.25, air x1.05 (EHP=501458.981782) | hp2-20261030: ground x1.55, air x1.05 (EHP=746978.576572) | hp3-20261030: W11-25 ground x0.85 (EHP=644470.886396) | hp4-20261030: W15-25 ground x0.9 (EHP=586383.195455) | hp5-20261030: W15-25 ground x0.95 (EHP=560243.734591)</t>
         </is>
       </c>
     </row>

--- a/Luban/Config/Datas/Levels/L01/EnemyList.xlsx
+++ b/Luban/Config/Datas/Levels/L01/EnemyList.xlsx
@@ -1568,7 +1568,7 @@
       </c>
       <c r="F23" s="0" t="inlineStr">
         <is>
-          <t>L1 W20/25; N=606; EHP=177927.123756 | wavebuff2-20261029 (counts x2 again, hp stacked) | gold20-20261029: killGold=0 | w20soften-20261029: interval 150.15ms | ground5-20261030: ground +26 (5%) | hp-20261030: ground x1.25, air x1.05 (EHP=216711.151795) | hp2-20261030: ground x1.55, air x1.05 (EHP=320945.684398) | hp3-20261030: W11-25 ground x0.85 (EHP=277515.160921) | hp4-20261030: W15-25 ground x0.9 (EHP=252904.531093) | hp5-20261030: W15-25 ground x0.95 (EHP=241829.747662)</t>
+          <t>L1 W20/25; N=606; EHP=177927.123756 | wavebuff2-20261029 (counts x2 again, hp stacked) | gold20-20261029: killGold=0 | w20soften-20261029: interval 150.15ms | ground5-20261030: ground +26 (5%) | hp-20261030: ground x1.25, air x1.05 (EHP=216711.151795) | hp2-20261030: ground x1.55, air x1.05 (EHP=320945.684398) | hp3-20261030: W11-25 ground x0.85 (EHP=277515.160921) | hp4-20261030: W15-25 ground x0.9 (EHP=252904.531093) | hp5-20261030: W15-25 ground x0.95 (EHP=241829.747662) | airhp-20261031: W20 air x0.95 (EHP=240259.304594)</t>
         </is>
       </c>
     </row>
@@ -1589,7 +1589,7 @@
       </c>
       <c r="F24" s="0" t="inlineStr">
         <is>
-          <t>L1 W21/25; N=626; EHP=230501.598406 | wavebuff2-20261029 (counts x2 again, hp stacked) | gold20-20261029: killGold=0 | wavegold-air-20261029: air -5, air hp x0.95 | ground5-20261030: ground +27 (5%) | hp-20261030: ground x1.25, air x1.05 (EHP=281325.347015) | hp2-20261030: ground x1.55, air x1.05 (EHP=418199.954202) | hp3-20261030: W11-25 ground x0.85 (EHP=361094.076087) | hp4-20261030: W15-25 ground x0.9 (EHP=328734.078678) | hp5-20261030: W15-25 ground x0.95 (EHP=314172.079845)</t>
+          <t>L1 W21/25; N=626; EHP=230501.598406 | wavebuff2-20261029 (counts x2 again, hp stacked) | gold20-20261029: killGold=0 | wavegold-air-20261029: air -5, air hp x0.95 | ground5-20261030: ground +27 (5%) | hp-20261030: ground x1.25, air x1.05 (EHP=281325.347015) | hp2-20261030: ground x1.55, air x1.05 (EHP=418199.954202) | hp3-20261030: W11-25 ground x0.85 (EHP=361094.076087) | hp4-20261030: W15-25 ground x0.9 (EHP=328734.078678) | hp5-20261030: W15-25 ground x0.95 (EHP=314172.079845) | airhp-20261031: W21 air x0.95 (EHP=312297.374821) | airhp2-20261031: W21 air x0.95 again (EHP=310516.405075) | airhp3-20261031: W21 air x0.95 (third) (EHP=308824.483756) | airhp4-20261031: W21 air x0.95 (fourth) (EHP=307217.158513)</t>
         </is>
       </c>
     </row>

--- a/Luban/Config/Datas/Levels/L01/EnemyList.xlsx
+++ b/Luban/Config/Datas/Levels/L01/EnemyList.xlsx
@@ -1610,7 +1610,7 @@
       </c>
       <c r="F25" s="0" t="inlineStr">
         <is>
-          <t>L1 W22/25; N=651; EHP=235161.123708 | wavebuff2-20261029 (counts x2 again, hp stacked) | gold20-20261029: killGold=0 | wavegold-air-20261029: air -5, air hp x0.95 | ground5-20261030: ground +28 (5%) | hp-20261030: ground x1.25, air x1.05 (EHP=286918.597490) | hp2-20261030: ground x1.55, air x1.05 (EHP=426262.706818) | hp3-20261030: W11-25 ground x0.85 (EHP=368138.553364) | hp4-20261030: W15-25 ground x0.9 (EHP=335201.533046) | hp5-20261030: W15-25 ground x0.95 (EHP=320379.873777)</t>
+          <t>L1 W22/25; N=651; EHP=235161.123708 | wavebuff2-20261029 (counts x2 again, hp stacked) | gold20-20261029: killGold=0 | wavegold-air-20261029: air -5, air hp x0.95 | ground5-20261030: ground +28 (5%) | hp-20261030: ground x1.25, air x1.05 (EHP=286918.597490) | hp2-20261030: ground x1.55, air x1.05 (EHP=426262.706818) | hp3-20261030: W11-25 ground x0.85 (EHP=368138.553364) | hp4-20261030: W15-25 ground x0.9 (EHP=335201.533046) | hp5-20261030: W15-25 ground x0.95 (EHP=320379.873777) | airhp-20261101: W22 air x0.90 (EHP=316503.038767)</t>
         </is>
       </c>
     </row>
@@ -1673,7 +1673,7 @@
       </c>
       <c r="F28" s="0" t="inlineStr">
         <is>
-          <t>L1 W25/25; N=726; EHP=410396.243063 | wavebuff2-20261029 (counts x2 again, hp stacked) | gold20-20261029: killGold=0 | wavegold-air-20261029: air -5, air hp x0.95 | w25soften-20261030: hp x0.80, interval x1.10 | ground5-20261030: ground +31 (5%) | hp-20261030: ground x1.25, air x1.05 (EHP=501458.981782) | hp2-20261030: ground x1.55, air x1.05 (EHP=746978.576572) | hp3-20261030: W11-25 ground x0.85 (EHP=644470.886396) | hp4-20261030: W15-25 ground x0.9 (EHP=586383.195455) | hp5-20261030: W15-25 ground x0.95 (EHP=560243.734591)</t>
+          <t>L1 W25/25; N=726; EHP=535411.246654 | wavebuff2-20261029 (counts x2 again, hp stacked) | gold20-20261029: killGold=0 | wavegold-air-20261029: air -5, air hp x0.95 | w25soften-20261030: hp x0.80, interval x1.10 | ground5-20261030: ground +31 (5%) | hp-20261030: ground x1.25, air x1.05 (EHP=501458.981782) | hp2-20261030: ground x1.55, air x1.05 (EHP=746978.576572) | hp3-20261030: W11-25 ground x0.85 (EHP=644470.886396) | hp4-20261030: W15-25 ground x0.9 (EHP=586383.195455) | hp5-20261030: W15-25 ground x0.95 (EHP=560243.734591) | hp6-20261101: W25 ground x0.95 [EHP 行首汇总原值 410396.243063 为历史遗留未同步，本次按当前 hp/armor 重算]</t>
         </is>
       </c>
     </row>

--- a/Luban/Config/Datas/Levels/L01/EnemyList.xlsx
+++ b/Luban/Config/Datas/Levels/L01/EnemyList.xlsx
@@ -1274,7 +1274,7 @@
       </c>
       <c r="F9" s="0" t="inlineStr">
         <is>
-          <t>L1 W6/25; N=256; EHP=10548.512992 | wavebuff2-20261029 (counts x2 again, hp stacked) | gold20-20261029: killGold=80 | ground5-20261030: ground +12 (5%) | hp-20261030: ground x1.25, air x1.05 (EHP=12999.661926) | hp2-20261030: ground x1.55, air x1.05 (EHP=19661.280402)</t>
+          <t>L1 W6/25; N=256; EHP=10548.512992 | wavebuff2-20261029 (counts x2 again, hp stacked) | gold20-20261029: killGold=80 | ground5-20261030: ground +12 (5%) | hp-20261030: ground x1.25, air x1.05 (EHP=12999.661926) | hp2-20261030: ground x1.55, air x1.05 (EHP=19661.280402) | goldhp-20261101: ground x1.12 (EHP=21897.608748)</t>
         </is>
       </c>
     </row>
@@ -1295,7 +1295,7 @@
       </c>
       <c r="F10" s="0" t="inlineStr">
         <is>
-          <t>L1 W7/25; N=281; EHP=12410.951006 | wavebuff2-20261029 (counts x2 again, hp stacked) | gold20-20261029: killGold=132 | ground5-20261030: ground +13 (5%) | hp-20261030: ground x1.25, air x1.05 (EHP=15251.001434) | hp2-20261030: ground x1.55, air x1.05 (EHP=22949.498000)</t>
+          <t>L1 W7/25; N=281; EHP=12410.951006 | wavebuff2-20261029 (counts x2 again, hp stacked) | gold20-20261029: killGold=132 | ground5-20261030: ground +13 (5%) | hp-20261030: ground x1.25, air x1.05 (EHP=15251.001434) | hp2-20261030: ground x1.55, air x1.05 (EHP=22949.498000) | goldhp-20261101: ground x1.12 (EHP=25529.670088)</t>
         </is>
       </c>
     </row>
@@ -1316,7 +1316,7 @@
       </c>
       <c r="F11" s="0" t="inlineStr">
         <is>
-          <t>L1 W8/25; N=306; EHP=16280.767458 | wavebuff2-20261029 (counts x2 again, hp stacked) | gold20-20261029: killGold=20 | ground5-20261030: ground +14 (5%) | hp-20261030: ground x1.25, air x1.05 (EHP=19958.799291) | hp2-20261030: ground x1.55, air x1.05 (EHP=29906.718932)</t>
+          <t>L1 W8/25; N=306; EHP=16280.767458 | wavebuff2-20261029 (counts x2 again, hp stacked) | gold20-20261029: killGold=20 | ground5-20261030: ground +14 (5%) | hp-20261030: ground x1.25, air x1.05 (EHP=19958.799291) | hp2-20261030: ground x1.55, air x1.05 (EHP=29906.718932) | goldhp-20261101: ground x1.12 (EHP=33236.111349)</t>
         </is>
       </c>
     </row>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="F12" s="0" t="inlineStr">
         <is>
-          <t>L1 W9/25; N=331; EHP=20961.699193 | wavebuff2-20261029 (counts x2 again, hp stacked) | gold20-20261029: killGold=24 | ground5-20261030: ground +15 (5%) | hp-20261030: ground x1.25, air x1.05 (EHP=25646.617235) | hp2-20261030: ground x1.55, air x1.05 (EHP=38294.051560)</t>
+          <t>L1 W9/25; N=331; EHP=20961.699193 | wavebuff2-20261029 (counts x2 again, hp stacked) | gold20-20261029: killGold=24 | ground5-20261030: ground +15 (5%) | hp-20261030: ground x1.25, air x1.05 (EHP=25646.617235) | hp2-20261030: ground x1.55, air x1.05 (EHP=38294.051560) | goldhp-20261101: ground x1.12 (EHP=42521.869942)</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="F14" s="0" t="inlineStr">
         <is>
-          <t>L1 W11/25; N=381; EHP=39385.756064 | wavebuff2-20261029 (counts x2 again, hp stacked) | gold20-20261029: killGold=0 | ground5-20261030: ground +17 (5%) | hp-20261030: ground x1.25, air x1.05 (EHP=48261.649622) | hp2-20261030: ground x1.55, air x1.05 (EHP=72257.875232) | hp3-20261030: W11-25 ground x0.85 (EHP=62221.713680)</t>
+          <t>L1 W11/25; N=381; EHP=39385.756064 | wavebuff2-20261029 (counts x2 again, hp stacked) | gold20-20261029: killGold=0 | ground5-20261030: ground +17 (5%) | hp-20261030: ground x1.25, air x1.05 (EHP=48261.649622) | hp2-20261030: ground x1.55, air x1.05 (EHP=72257.875232) | hp3-20261030: W11-25 ground x0.85 (EHP=62221.713680) | goldhp-20261101: ground x1.12 (EHP=69046.303574)</t>
         </is>
       </c>
     </row>
@@ -1400,7 +1400,7 @@
       </c>
       <c r="F15" s="0" t="inlineStr">
         <is>
-          <t>L1 W12/25; N=406; EHP=40809.085638 | wavebuff2-20261029 (counts x2 again, hp stacked) | gold20-20261029: killGold=0 | ground5-20261030: ground +18 (5%) | hp-20261030: ground x1.25, air x1.05 (EHP=49962.887487) | hp2-20261030: ground x1.55, air x1.05 (EHP=74690.242898) | hp3-20261030: W11-25 ground x0.85 (EHP=64353.659659)</t>
+          <t>L1 W12/25; N=406; EHP=40809.085638 | wavebuff2-20261029 (counts x2 again, hp stacked) | gold20-20261029: killGold=0 | ground5-20261030: ground +18 (5%) | hp-20261030: ground x1.25, air x1.05 (EHP=49962.887487) | hp2-20261030: ground x1.55, air x1.05 (EHP=74690.242898) | hp3-20261030: W11-25 ground x0.85 (EHP=64353.659659) | goldhp-20261101: ground x1.12 (EHP=71382.536179)</t>
         </is>
       </c>
     </row>
@@ -1421,7 +1421,7 @@
       </c>
       <c r="F16" s="0" t="inlineStr">
         <is>
-          <t>L1 W13/25; N=431; EHP=49843.475103 | wavebuff2-20261029 (counts x2 again, hp stacked) | gold20-20261029: killGold=0 | ground5-20261030: ground +19 (5%) | hp-20261030: ground x1.25, air x1.05 (EHP=60968.050676) | hp2-20261030: ground x1.55, air x1.05 (EHP=90992.709032) | hp3-20261030: W11-25 ground x0.85 (EHP=78448.750064)</t>
+          <t>L1 W13/25; N=431; EHP=49843.475103 | wavebuff2-20261029 (counts x2 again, hp stacked) | gold20-20261029: killGold=0 | ground5-20261030: ground +19 (5%) | hp-20261030: ground x1.25, air x1.05 (EHP=60968.050676) | hp2-20261030: ground x1.55, air x1.05 (EHP=90992.709032) | hp3-20261030: W11-25 ground x0.85 (EHP=78448.750064) | goldhp-20261101: ground x1.12 (EHP=86978.642151)</t>
         </is>
       </c>
     </row>
@@ -1442,7 +1442,7 @@
       </c>
       <c r="F17" s="0" t="inlineStr">
         <is>
-          <t>L1 W14/25; N=456; EHP=60354.909159 | wavebuff2-20261029 (counts x2 again, hp stacked) | gold20-20261029: killGold=0 | ground5-20261030: ground +20 (5%) | hp-20261030: ground x1.25, air x1.05 (EHP=73749.252381) | hp2-20261030: ground x1.55, air x1.05 (EHP=109863.583107) | hp3-20261030: W11-25 ground x0.85 (EHP=94785.089377)</t>
+          <t>L1 W14/25; N=456; EHP=60354.909159 | wavebuff2-20261029 (counts x2 again, hp stacked) | gold20-20261029: killGold=0 | ground5-20261030: ground +20 (5%) | hp-20261030: ground x1.25, air x1.05 (EHP=73749.252381) | hp2-20261030: ground x1.55, air x1.05 (EHP=109863.583107) | hp3-20261030: W11-25 ground x0.85 (EHP=94785.089377) | goldhp-20261101: ground x1.12 (EHP=105038.465156)</t>
         </is>
       </c>
     </row>
@@ -1484,7 +1484,7 @@
       </c>
       <c r="F19" s="0" t="inlineStr">
         <is>
-          <t>L1 W16/25; N=506; EHP=107875.827726 | wavebuff2-20261029 (counts x2 again, hp stacked) | gold20-20261029: killGold=200 | ground5-20261030: ground +22 (5%) | hp-20261030: ground x1.25, air x1.05 (EHP=131628.851020) | hp2-20261030: ground x1.55, air x1.05 (EHP=195582.893030) | hp3-20261030: W11-25 ground x0.85 (EHP=168904.634175) | hp4-20261030: W15-25 ground x0.9 (EHP=153786.954303) | hp5-20261030: W15-25 ground x0.95 (EHP=146983.998175)</t>
+          <t>L1 W16/25; N=506; EHP=107875.827726 | wavebuff2-20261029 (counts x2 again, hp stacked) | gold20-20261029: killGold=200 | ground5-20261030: ground +22 (5%) | hp-20261030: ground x1.25, air x1.05 (EHP=131628.851020) | hp2-20261030: ground x1.55, air x1.05 (EHP=195582.893030) | hp3-20261030: W11-25 ground x0.85 (EHP=168904.634175) | hp4-20261030: W15-25 ground x0.9 (EHP=153786.954303) | hp5-20261030: W15-25 ground x0.95 (EHP=146983.998175) | goldhp-20261101: ground x1.12 (EHP=162494.737895)</t>
         </is>
       </c>
     </row>
@@ -1505,7 +1505,7 @@
       </c>
       <c r="F20" s="0" t="inlineStr">
         <is>
-          <t>L1 W17/25; N=531; EHP=110419.889399 | wavebuff2-20261029 (counts x2 again, hp stacked) | gold20-20261029: killGold=0 | ground5-20261030: ground +23 (5%) | hp-20261030: ground x1.25, air x1.05 (EHP=134691.009753) | hp2-20261030: ground x1.55, air x1.05 (EHP=200019.704037) | hp3-20261030: W11-25 ground x0.85 (EHP=172773.427208) | hp4-20261030: W15-25 ground x0.9 (EHP=157333.870210) | hp5-20261030: W15-25 ground x0.95 (EHP=150386.069593)</t>
+          <t>L1 W17/25; N=531; EHP=110419.889399 | wavebuff2-20261029 (counts x2 again, hp stacked) | gold20-20261029: killGold=0 | ground5-20261030: ground +23 (5%) | hp-20261030: ground x1.25, air x1.05 (EHP=134691.009753) | hp2-20261030: ground x1.55, air x1.05 (EHP=200019.704037) | hp3-20261030: W11-25 ground x0.85 (EHP=172773.427208) | hp4-20261030: W15-25 ground x0.9 (EHP=157333.870210) | hp5-20261030: W15-25 ground x0.95 (EHP=150386.069593) | goldhp-20261101: ground x1.12 (EHP=166227.054866)</t>
         </is>
       </c>
     </row>
@@ -1526,7 +1526,7 @@
       </c>
       <c r="F21" s="0" t="inlineStr">
         <is>
-          <t>L1 W18/25; N=556; EHP=118103.089258 | wavebuff2-20261029 (counts x2 again, hp stacked) | gold20-20261029: killGold=0 | ground5-20261030: ground +24 (5%) | hp-20261030: ground x1.25, air x1.05 (EHP=143992.735276) | hp2-20261030: ground x1.55, air x1.05 (EHP=213643.908064) | hp3-20261030: W11-25 ground x0.85 (EHP=184603.943879) | hp4-20261030: W15-25 ground x0.9 (EHP=168147.964119) | hp5-20261030: W15-25 ground x0.95 (EHP=160742.773339)</t>
+          <t>L1 W18/25; N=556; EHP=118103.089258 | wavebuff2-20261029 (counts x2 again, hp stacked) | gold20-20261029: killGold=0 | ground5-20261030: ground +24 (5%) | hp-20261030: ground x1.25, air x1.05 (EHP=143992.735276) | hp2-20261030: ground x1.55, air x1.05 (EHP=213643.908064) | hp3-20261030: W11-25 ground x0.85 (EHP=184603.943879) | hp4-20261030: W15-25 ground x0.9 (EHP=168147.964119) | hp5-20261030: W15-25 ground x0.95 (EHP=160742.773339) | goldhp-20261101: ground x1.12 (EHP=177626.608669)</t>
         </is>
       </c>
     </row>
@@ -1547,7 +1547,7 @@
       </c>
       <c r="F22" s="0" t="inlineStr">
         <is>
-          <t>L1 W19/25; N=581; EHP=136996.277523 | wavebuff2-20261029 (counts x2 again, hp stacked) | gold20-20261029: killGold=0 | ground5-20261030: ground +25 (5%) | hp-20261030: ground x1.25, air x1.05 (EHP=166904.954756) | hp2-20261030: ground x1.55, air x1.05 (EHP=247309.150300) | hp3-20261030: W11-25 ground x0.85 (EHP=213801.739511) | hp4-20261030: W15-25 ground x0.9 (EHP=194814.206795) | hp5-20261030: W15-25 ground x0.95 (EHP=186269.817149)</t>
+          <t>L1 W19/25; N=581; EHP=136996.277523 | wavebuff2-20261029 (counts x2 again, hp stacked) | gold20-20261029: killGold=0 | ground5-20261030: ground +25 (5%) | hp-20261030: ground x1.25, air x1.05 (EHP=166904.954756) | hp2-20261030: ground x1.55, air x1.05 (EHP=247309.150300) | hp3-20261030: W11-25 ground x0.85 (EHP=213801.739511) | hp4-20261030: W15-25 ground x0.9 (EHP=194814.206795) | hp5-20261030: W15-25 ground x0.95 (EHP=186269.817149) | goldhp-20261101: ground x1.12 (EHP=205751.025890)</t>
         </is>
       </c>
     </row>
@@ -1589,7 +1589,7 @@
       </c>
       <c r="F24" s="0" t="inlineStr">
         <is>
-          <t>L1 W21/25; N=626; EHP=230501.598406 | wavebuff2-20261029 (counts x2 again, hp stacked) | gold20-20261029: killGold=0 | wavegold-air-20261029: air -5, air hp x0.95 | ground5-20261030: ground +27 (5%) | hp-20261030: ground x1.25, air x1.05 (EHP=281325.347015) | hp2-20261030: ground x1.55, air x1.05 (EHP=418199.954202) | hp3-20261030: W11-25 ground x0.85 (EHP=361094.076087) | hp4-20261030: W15-25 ground x0.9 (EHP=328734.078678) | hp5-20261030: W15-25 ground x0.95 (EHP=314172.079845) | airhp-20261031: W21 air x0.95 (EHP=312297.374821) | airhp2-20261031: W21 air x0.95 again (EHP=310516.405075) | airhp3-20261031: W21 air x0.95 (third) (EHP=308824.483756) | airhp4-20261031: W21 air x0.95 (fourth) (EHP=307217.158513)</t>
+          <t>L1 W21/25; N=626; EHP=230501.598406 | wavebuff2-20261029 (counts x2 again, hp stacked) | gold20-20261029: killGold=0 | wavegold-air-20261029: air -5, air hp x0.95 | ground5-20261030: ground +27 (5%) | hp-20261030: ground x1.25, air x1.05 (EHP=281325.347015) | hp2-20261030: ground x1.55, air x1.05 (EHP=418199.954202) | hp3-20261030: W11-25 ground x0.85 (EHP=361094.076087) | hp4-20261030: W15-25 ground x0.9 (EHP=328734.078678) | hp5-20261030: W15-25 ground x0.95 (EHP=314172.079845) | airhp-20261031: W21 air x0.95 (EHP=312297.374821) | airhp2-20261031: W21 air x0.95 again (EHP=310516.405075) | airhp3-20261031: W21 air x0.95 (third) (EHP=308824.483756) | airhp4-20261031: W21 air x0.95 (fourth) (EHP=307217.158513) | goldhp-20261101: ground x1.12 (EHP=340418.515970)</t>
         </is>
       </c>
     </row>
@@ -1610,7 +1610,7 @@
       </c>
       <c r="F25" s="0" t="inlineStr">
         <is>
-          <t>L1 W22/25; N=651; EHP=235161.123708 | wavebuff2-20261029 (counts x2 again, hp stacked) | gold20-20261029: killGold=0 | wavegold-air-20261029: air -5, air hp x0.95 | ground5-20261030: ground +28 (5%) | hp-20261030: ground x1.25, air x1.05 (EHP=286918.597490) | hp2-20261030: ground x1.55, air x1.05 (EHP=426262.706818) | hp3-20261030: W11-25 ground x0.85 (EHP=368138.553364) | hp4-20261030: W15-25 ground x0.9 (EHP=335201.533046) | hp5-20261030: W15-25 ground x0.95 (EHP=320379.873777) | airhp-20261101: W22 air x0.90 (EHP=316503.038767)</t>
+          <t>L1 W22/25; N=651; EHP=235161.123708 | wavebuff2-20261029 (counts x2 again, hp stacked) | gold20-20261029: killGold=0 | wavegold-air-20261029: air -5, air hp x0.95 | ground5-20261030: ground +28 (5%) | hp-20261030: ground x1.25, air x1.05 (EHP=286918.597490) | hp2-20261030: ground x1.55, air x1.05 (EHP=426262.706818) | hp3-20261030: W11-25 ground x0.85 (EHP=368138.553364) | hp4-20261030: W15-25 ground x0.9 (EHP=335201.533046) | hp5-20261030: W15-25 ground x0.95 (EHP=320379.873777) | airhp-20261101: W22 air x0.90 (EHP=316503.038767) | goldhp-20261101: ground x1.12 (EHP=350296.421506)</t>
         </is>
       </c>
     </row>
@@ -1631,7 +1631,7 @@
       </c>
       <c r="F26" s="0" t="inlineStr">
         <is>
-          <t>L1 W23/25; N=676; EHP=240288.625876 | wavebuff2-20261029 (counts x2 again, hp stacked) | gold20-20261029: killGold=0 | wavegold-air-20261029: air -5, air hp x0.95 | ground5-20261030: ground +29 (5%) | hp-20261030: ground x1.25, air x1.05 (EHP=293077.856897) | hp2-20261030: ground x1.55, air x1.05 (EHP=435152.998855) | hp3-20261030: W11-25 ground x0.85 (EHP=375902.118041) | hp4-20261030: W15-25 ground x0.9 (EHP=342326.619003) | hp5-20261030: W15-25 ground x0.95 (EHP=327217.644319)</t>
+          <t>L1 W23/25; N=676; EHP=240288.625876 | wavebuff2-20261029 (counts x2 again, hp stacked) | gold20-20261029: killGold=0 | wavegold-air-20261029: air -5, air hp x0.95 | ground5-20261030: ground +29 (5%) | hp-20261030: ground x1.25, air x1.05 (EHP=293077.856897) | hp2-20261030: ground x1.55, air x1.05 (EHP=435152.998855) | hp3-20261030: W11-25 ground x0.85 (EHP=375902.118041) | hp4-20261030: W15-25 ground x0.9 (EHP=342326.619003) | hp5-20261030: W15-25 ground x0.95 (EHP=327217.644319) | goldhp-20261101: ground x1.12 (EHP=361666.106490)</t>
         </is>
       </c>
     </row>
@@ -1652,7 +1652,7 @@
       </c>
       <c r="F27" s="0" t="inlineStr">
         <is>
-          <t>L1 W24/25; N=701; EHP=257560.220166 | wavebuff2-20261029 (counts x2 again, hp stacked) | gold20-20261029: killGold=1932 | wavegold-air-20261029: air -5, air hp x0.95 | ground5-20261030: ground +30 (5%) | hp-20261030: ground x1.25, air x1.05 (EHP=313979.492776) | hp2-20261030: ground x1.55, air x1.05 (EHP=465744.909990) | hp3-20261030: W11-25 ground x0.85 (EHP=402474.014181) | hp4-20261030: W15-25 ground x0.9 (EHP=366620.506662) | hp5-20261030: W15-25 ground x0.95 (EHP=350486.428135)</t>
+          <t>L1 W24/25; N=701; EHP=257560.220166 | wavebuff2-20261029 (counts x2 again, hp stacked) | gold20-20261029: killGold=1932 | wavegold-air-20261029: air -5, air hp x0.95 | ground5-20261030: ground +30 (5%) | hp-20261030: ground x1.25, air x1.05 (EHP=313979.492776) | hp2-20261030: ground x1.55, air x1.05 (EHP=465744.909990) | hp3-20261030: W11-25 ground x0.85 (EHP=402474.014181) | hp4-20261030: W15-25 ground x0.9 (EHP=366620.506662) | hp5-20261030: W15-25 ground x0.95 (EHP=350486.428135) | goldhp-20261101: ground x1.12 (EHP=387272.126958)</t>
         </is>
       </c>
     </row>
@@ -1673,7 +1673,7 @@
       </c>
       <c r="F28" s="0" t="inlineStr">
         <is>
-          <t>L1 W25/25; N=726; EHP=535411.246654 | wavebuff2-20261029 (counts x2 again, hp stacked) | gold20-20261029: killGold=0 | wavegold-air-20261029: air -5, air hp x0.95 | w25soften-20261030: hp x0.80, interval x1.10 | ground5-20261030: ground +31 (5%) | hp-20261030: ground x1.25, air x1.05 (EHP=501458.981782) | hp2-20261030: ground x1.55, air x1.05 (EHP=746978.576572) | hp3-20261030: W11-25 ground x0.85 (EHP=644470.886396) | hp4-20261030: W15-25 ground x0.9 (EHP=586383.195455) | hp5-20261030: W15-25 ground x0.95 (EHP=560243.734591) | hp6-20261101: W25 ground x0.95 [EHP 行首汇总原值 410396.243063 为历史遗留未同步，本次按当前 hp/armor 重算]</t>
+          <t>L1 W25/25; N=726; EHP=513728.202320 | wavebuff2-20261029 (counts x2 again, hp stacked) | gold20-20261029: killGold=0 | wavegold-air-20261029: air -5, air hp x0.95 | w25soften-20261030: hp x0.80, interval x1.10 | ground5-20261030: ground +31 (5%) | hp-20261030: ground x1.25, air x1.05 (EHP=501458.981782) | hp2-20261030: ground x1.55, air x1.05 (EHP=746978.576572) | hp3-20261030: W11-25 ground x0.85 (EHP=644470.886396) | hp4-20261030: W15-25 ground x0.9 (EHP=586383.195455) | hp5-20261030: W15-25 ground x0.95 (EHP=560243.734591) | hp6-20261101: W25 ground x0.95 [EHP 行首汇总原值 410396.243063 为历史遗留未同步，本次按当前 hp/armor 重算] | w25hp2-20261101: 地面 x0.95, 空中 x1.03 (EHP=513728.202320)</t>
         </is>
       </c>
     </row>
